--- a/Sajjad data/by_country_and_state/Canada/ON.xlsx
+++ b/Sajjad data/by_country_and_state/Canada/ON.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="994">
   <si>
     <t>Business Name</t>
   </si>
@@ -881,6 +881,2118 @@
   </si>
   <si>
     <t>2026-10-26T04:22:46.713Z</t>
+  </si>
+  <si>
+    <t>Dr H J McIsaac &amp; Associates</t>
+  </si>
+  <si>
+    <t>+1 905-525-8272</t>
+  </si>
+  <si>
+    <t>212 James St S, Hamilton, ON L8P 3A9, Canada</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+H+J+McIsaac+%26+Associates/data=!4m7!3m6!1s0x882c9b9e79448be7:0x8f0ea94892fc1055!8m2!3d43.2503441!4d-79.8721792!16s%2Fg%2F1v2gfdc3!19sChIJ54tEeZ6bLIgRVRD8kkipDo8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:52:08.883Z</t>
+  </si>
+  <si>
+    <t>UPPER JAMES DENTURE CLINIC</t>
+  </si>
+  <si>
+    <t>+1 905-574-8874</t>
+  </si>
+  <si>
+    <t>Denture care center</t>
+  </si>
+  <si>
+    <t>644 Upper James St, Hamilton, ON L9C 2Z2, Canada</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>MondayOpen 24 hours; TuesdayOpen 24 hours; WednesdayOpen 24 hours; ThursdayOpen 24 hours; FridayOpen 24 hours; SaturdayOpen 24 hours; SundayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/UPPER+JAMES+DENTURE+CLINIC/data=!4m7!3m6!1s0x882c9b089e455555:0xb928405769ecb2e0!8m2!3d43.2369163!4d-79.878466!16s%2Fg%2F11grqvct0m!19sChIJVVVFngibLIgR4LLsaVdAKLk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:52:56.047Z</t>
+  </si>
+  <si>
+    <t>Hygienic Smiles</t>
+  </si>
+  <si>
+    <t>+1 905-538-7315</t>
+  </si>
+  <si>
+    <t>515 Upper Sherman Ave, Hamilton, ON L8V 3L7, Canada</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hygienic+Smiles/data=!4m7!3m6!1s0x882c9bc36105b641:0x15be692d9ea249ed!8m2!3d43.232424!4d-79.8468398!16s%2Fg%2F1tlgylcf!19sChIJQbYFYcObLIgR7Umini1pvhU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:53:35.869Z</t>
+  </si>
+  <si>
+    <t>Harper David Dr</t>
+  </si>
+  <si>
+    <t>+1 905-318-5888</t>
+  </si>
+  <si>
+    <t>883 Upper Wentworth St, Hamilton, ON L9A 4Y6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Harper+David+Dr/data=!4m7!3m6!1s0x882c9a4e0ff70f71:0xce97d48857b4f11e!8m2!3d43.2204626!4d-79.8625725!16s%2Fg%2F1tdzrsky!19sChIJcQ_3D06aLIgRHvG0V4jUl84?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:53:44.538Z</t>
+  </si>
+  <si>
+    <t>Central Family Dentistry</t>
+  </si>
+  <si>
+    <t>+1 519-673-0870</t>
+  </si>
+  <si>
+    <t>484 Central Ave, London, ON N6B 2G1, Canada</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>Monday7:30 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Central+Family+Dentistry/data=!4m7!3m6!1s0x405bc8d1e6455655:0x81e61b39ae9197ce!8m2!3d42.9937016!4d-81.2393832!16s%2Fg%2F11bbsz3fll!19sChIJVVZF5tHIW0ARzpeRrjkb5oE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:53:57.120Z</t>
+  </si>
+  <si>
+    <t>Pine Valley Dental</t>
+  </si>
+  <si>
+    <t>+1 519-686-9006</t>
+  </si>
+  <si>
+    <t>151 Pine Valley Blvd #1, London, ON N6K 3T6, Canada</t>
+  </si>
+  <si>
+    <t>Monday12–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pine+Valley+Dental/data=!4m7!3m6!1s0x882ef13d670af2f1:0x6ef160fb417c32cd!8m2!3d42.9392242!4d-81.2837551!16s%2Fg%2F1tfsch56!19sChIJ8fIKZz3xLogRzTJ8Qftg8W4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:54:09.674Z</t>
+  </si>
+  <si>
+    <t>Dr Marek Gasiorowski DDS</t>
+  </si>
+  <si>
+    <t>+1 519-680-7707</t>
+  </si>
+  <si>
+    <t>280 Wharncliffe Rd S, London, ON N6J 2L5, Canada</t>
+  </si>
+  <si>
+    <t>Monday12–8:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Marek+Gasiorowski+DDS/data=!4m7!3m6!1s0x882ef18fc878973b:0x22bc1444abd250e6!8m2!3d42.968463!4d-81.261531!16s%2Fg%2F1tfgkg5z!19sChIJO5d4yI_xLogR5lDSq0QUvCI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:55:55.623Z</t>
+  </si>
+  <si>
+    <t>Dr. Tassi &amp; Dr. Foley Orthodontics</t>
+  </si>
+  <si>
+    <t>+1 519-673-6500</t>
+  </si>
+  <si>
+    <t>4496 Colonel Talbot Rd, London, ON N6P 1B6, Canada</t>
+  </si>
+  <si>
+    <t>MondayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tassi+%26+Dr.+Foley+Orthodontics/data=!4m7!3m6!1s0x882eedf0db786689:0x64daa05238962ca8!8m2!3d42.9044838!4d-81.2973434!16s%2Fg%2F1tfsnmzk!19sChIJiWZ42_DtLogRqCyWOFKg2mQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:55:57.608Z</t>
+  </si>
+  <si>
+    <t>Dr. J. Douglas Awde &amp; Dr. Spenser Gibbs</t>
+  </si>
+  <si>
+    <t>+1 519-672-5260</t>
+  </si>
+  <si>
+    <t>101 Cherryhill Blvd, London, ON N6H 4S4, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+J.+Douglas+Awde+%26+Dr.+Spenser+Gibbs/data=!4m7!3m6!1s0x882ef1dcfe43b26f:0xb8258e92b99699f1!8m2!3d42.9889869!4d-81.277441!16s%2Fg%2F1td33pmb!19sChIJb7JD_tzxLogR8ZmWuZKOJbg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:57:06.547Z</t>
+  </si>
+  <si>
+    <t>London Periodontics</t>
+  </si>
+  <si>
+    <t>+1 519-963-3131</t>
+  </si>
+  <si>
+    <t>Byron (West, 305 Boler Rd Unit #3, London, ON N6K 2K1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/London+Periodontics/data=!4m7!3m6!1s0x882ef086ea46562f:0x504f6ae73edb3394!8m2!3d42.9591011!4d-81.3329472!16s%2Fg%2F11wmhlf9bl!19sChIJL1ZG6obwLogRlDPbPudqT1A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:57:08.526Z</t>
+  </si>
+  <si>
+    <t>Markham Dentistry</t>
+  </si>
+  <si>
+    <t>+1 905-940-9898</t>
+  </si>
+  <si>
+    <t>7750 Kennedy Rd Unit 8, Markham, ON L3R 0A7, Canada</t>
+  </si>
+  <si>
+    <t>Markham</t>
+  </si>
+  <si>
+    <t>Monday9 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Markham+Dentistry/data=!4m7!3m6!1s0x89d4d5c7c1b6ab67:0x94a21037eb99d1c6!8m2!3d43.8428594!4d-79.3060851!16s%2Fg%2F11f5pvzqd6!19sChIJZ6u2wcfV1IkRxtGZ6zcQopQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:57:30.759Z</t>
+  </si>
+  <si>
+    <t>Dr Wong Markham Dental</t>
+  </si>
+  <si>
+    <t>+1 905-604-5822</t>
+  </si>
+  <si>
+    <t>3255 Hwy 7 Unit 68, Markham, ON L3R 3P9, Canada</t>
+  </si>
+  <si>
+    <t>Monday10:30 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Wong+Markham+Dental/data=!4m7!3m6!1s0x89d4d5423e07a421:0xc90afd93f4ff62d9!8m2!3d43.8492514!4d-79.3472911!16s%2Fg%2F11h6blkwxh!19sChIJIaQHPkLV1IkR2WL_9JP9Csk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:57:53.019Z</t>
+  </si>
+  <si>
+    <t>M&amp;J Dental: Dr. Miranda Li 华西苑牙医诊所</t>
+  </si>
+  <si>
+    <t>+1 905-305-8484</t>
+  </si>
+  <si>
+    <t>8241 Woodbine Ave Unit 16, Markham, ON L3R 8Z5, Canada</t>
+  </si>
+  <si>
+    <t>Monday10 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/M%26J+Dental:+Dr.+Miranda+Li+%E5%8D%8E%E8%A5%BF%E8%8B%91%E7%89%99%E5%8C%BB%E8%AF%8A%E6%89%80/data=!4m7!3m6!1s0x89d4d4970bb8b2af:0x27fe2d330ffdb1bc!8m2!3d43.843858!4d-79.3548386!16s%2Fg%2F11b6_wg1p0!19sChIJr7K4C5fU1IkRvLH9DzMt_ic?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:58:07.268Z</t>
+  </si>
+  <si>
+    <t>Woodbine-Steeles Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 905-479-9390</t>
+  </si>
+  <si>
+    <t>7155 Woodbine Ave, Markham, ON L3R 1A3, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Woodbine-Steeles+Dental+Clinic/data=!4m7!3m6!1s0x89d4d365707da04d:0x54fd0288f836197f!8m2!3d43.8178841!4d-79.3494106!16s%2Fg%2F1tjdh5gb!19sChIJTaB9cGXT1IkRfxk2-IgC_VQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:58:17.541Z</t>
+  </si>
+  <si>
+    <t>M And S Dental Care</t>
+  </si>
+  <si>
+    <t>+1 905-201-7888</t>
+  </si>
+  <si>
+    <t>7393 Markham Rd, Markham, ON L3S 0B5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/M+And+S+Dental+Care/data=!4m7!3m6!1s0x89d4d6fa4b7f5c21:0xe8474fba2812c69e!8m2!3d43.8484539!4d-79.2533468!16s%2Fg%2F1tkp5zg9!19sChIJIVx_S_rW1IkRnsYSKLpPR-g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:58:21.826Z</t>
+  </si>
+  <si>
+    <t>Markham Dental Ctr</t>
+  </si>
+  <si>
+    <t>+1 905-477-6220</t>
+  </si>
+  <si>
+    <t>182 Main St Unionville, Unionville, ON L3R 2G9, Canada</t>
+  </si>
+  <si>
+    <t>Unionville</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Markham+Dental+Ctr/data=!4m7!3m6!1s0x89d4d5c82d434403:0xf0389cecaca7f38!8m2!3d43.8674791!4d-79.312204!16s%2Fg%2F11b5wlcwxj!19sChIJA0RDLcjV1IkROH_Kys6JAw8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:59:10.775Z</t>
+  </si>
+  <si>
+    <t>Markham Java Dental</t>
+  </si>
+  <si>
+    <t>+1 905-604-9189</t>
+  </si>
+  <si>
+    <t>28 South Unionville Ave #2081, Unionville, ON L3R 4P9, Canada</t>
+  </si>
+  <si>
+    <t>Monday10 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Markham+Java+Dental/data=!4m7!3m6!1s0x89d4d4325743408f:0xe8d6b7cb4e52b6a6!8m2!3d43.8558682!4d-79.304031!16s%2Fg%2F11clwm9ltp!19sChIJj0BDVzLU1IkRprZSTsu31ug?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:59:12.586Z</t>
+  </si>
+  <si>
+    <t>Unity Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 905-477-0007</t>
+  </si>
+  <si>
+    <t>411 Manhattan Dr Unit 1, Unionville, ON L3P 7P4, Canada</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Monday11 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Unity+Dental+Centre/data=!4m7!3m6!1s0x89d4d60a236bcacf:0x9a57a3382b5c3a16!8m2!3d43.8811679!4d-79.2884807!16s%2Fg%2F11b7819grh!19sChIJz8prIwrW1IkRFjpcKzijV5o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:59:32.173Z</t>
+  </si>
+  <si>
+    <t>Dentistry Family and Cosmetics</t>
+  </si>
+  <si>
+    <t>+1 905-472-5858</t>
+  </si>
+  <si>
+    <t>7720 Markham Rd, Markham, ON L3S 4S1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentistry+Family+and+Cosmetics/data=!4m7!3m6!1s0x89d4d7c91019f52b:0x23fd2507f08fe8f5!8m2!3d43.8536542!4d-79.2559176!16s%2Fg%2F11k1j6kjk6!19sChIJK_UZEMnX1IkR9eiP8Acl_SM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:59:55.269Z</t>
+  </si>
+  <si>
+    <t>Lasertots</t>
+  </si>
+  <si>
+    <t>+1 647-492-7059</t>
+  </si>
+  <si>
+    <t>3980 14th Ave Unit 10, Markham, ON L3R 0B1, Canada</t>
+  </si>
+  <si>
+    <t>Closed · Opens 9 AM · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lasertots/data=!4m7!3m6!1s0x882b2f8549657c5f:0x478878e75719bded!8m2!3d43.8404188!4d-79.3215077!16s%2Fg%2F1tgf3vdn!19sChIJX3xlSYUvK4gR7b0ZV-d4iEc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:00:29.263Z</t>
+  </si>
+  <si>
+    <t>Alexander Chung</t>
+  </si>
+  <si>
+    <t>+1 905-258-0478</t>
+  </si>
+  <si>
+    <t>H-60 S Town Centre Blvd, Markham, ON L6G 0C5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alexander+Chung/data=!4m7!3m6!1s0x89d4d5c9fddbaadd:0xa54cc78771eff144!8m2!3d43.8532061!4d-79.3389334!16s%2Fg%2F11h1b1tq5!19sChIJ3arb_cnV1IkRRPHvcYfHTKU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:01:01.012Z</t>
+  </si>
+  <si>
+    <t>Sunmark Dental Ctr</t>
+  </si>
+  <si>
+    <t>+1 905-472-2454</t>
+  </si>
+  <si>
+    <t>9275 Markham Rd, Markham, ON L6E 1A1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sunmark+Dental+Ctr/data=!4m7!3m6!1s0x89d529c286c73717:0x6b67b7e7209b30f8!8m2!3d43.8936859!4d-79.2630117!16s%2Fg%2F11b5wrc2lm!19sChIJFzfHhsIp1YkR-DCbIOe3Z2s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:01:39.188Z</t>
+  </si>
+  <si>
+    <t>Whole Heart Dental</t>
+  </si>
+  <si>
+    <t>+1 905-604-5675</t>
+  </si>
+  <si>
+    <t>5221 Hwy 7 #1000, Unionville, ON L3R 1N3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Whole+Heart+Dental/data=!4m7!3m6!1s0x89d4d72968803481:0x883f4d3490d49a5!8m2!3d43.8659458!4d-79.2860482!16s%2Fg%2F11fmmmfr_d!19sChIJgTSAaCnX1IkRpUkNSdP0gwg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:01:43.754Z</t>
+  </si>
+  <si>
+    <t>Quick White Smile Markham</t>
+  </si>
+  <si>
+    <t>+1 647-966-8944</t>
+  </si>
+  <si>
+    <t>7393 Markham Rd Unit 93, Markham, ON L3S 0B5, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–9 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quick+White+Smile+Markham/data=!4m7!3m6!1s0x89d4d742ea87f597:0xe6c4b82773d32f4f!8m2!3d43.8485967!4d-79.2533523!16s%2Fg%2F11ny2rdsmn!19sChIJl_WH6kLX1IkRTy_Tcye4xOY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:02:28.890Z</t>
+  </si>
+  <si>
+    <t>Richmond Hill Periodontics</t>
+  </si>
+  <si>
+    <t>+1 905-737-6891</t>
+  </si>
+  <si>
+    <t>9631 Yonge St Unit 201, Richmond Hill, ON L4C 0M5, Canada</t>
+  </si>
+  <si>
+    <t>Richmond Hill</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–1 PM; SaturdayClosed; SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Richmond+Hill+Periodontics/data=!4m7!3m6!1s0x405736d0923c212d:0x990deca2d0a42a9d!8m2!3d43.8626395!4d-79.4341394!16s%2Fg%2F1q66sq1bt!19sChIJLSE8ktA2V0ARnSqk0KLsDZk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:02:47.172Z</t>
+  </si>
+  <si>
+    <t>Markham Village Dental</t>
+  </si>
+  <si>
+    <t>+1 905-294-4114</t>
+  </si>
+  <si>
+    <t>3 Centre St Ste 201, Markham, ON L3P 3P9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Markham+Village+Dental/data=!4m7!3m6!1s0x89d4d638ee13dcc7:0xf00e2655a65a36ca!8m2!3d43.8758467!4d-79.2599328!16s%2Fg%2F119wpxv5q!19sChIJx9wT7jjW1IkRyjZaplUmDvA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:02:49.025Z</t>
+  </si>
+  <si>
+    <t>Vaughan Dental Care</t>
+  </si>
+  <si>
+    <t>+1 905-669-0613</t>
+  </si>
+  <si>
+    <t>L4K 5Y6, Canada, Ontario, Concord, Rutherford Rd</t>
+  </si>
+  <si>
+    <t>Concord</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vaughan+Dental+Care/data=!4m7!3m6!1s0x882b2f29cb74cbfd:0x6e73f6b38b5e137!8m2!3d43.8288321!4d-79.5394893!16s%2Fg%2F1vs5xby1!19sChIJ_ct0yykvK4gRN-G1OGs_5wY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:03:50.393Z</t>
+  </si>
+  <si>
+    <t>Mejery Family Dentistry</t>
+  </si>
+  <si>
+    <t>+1 905-417-3600</t>
+  </si>
+  <si>
+    <t>10055 Keele St, Maple, ON L6A 1G3, Canada</t>
+  </si>
+  <si>
+    <t>Maple</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mejery+Family+Dentistry/data=!4m7!3m6!1s0x882b2920d8110703:0x312459846be8b5d3!8m2!3d43.8560897!4d-79.5123465!16s%2Fg%2F1tdp12l2!19sChIJAwcR2CApK4gR07Xoa4RZJDE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:05:00.114Z</t>
+  </si>
+  <si>
+    <t>Tuscany Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 905-660-5188</t>
+  </si>
+  <si>
+    <t>3255 Rutherford Rd Unit 36, Concord, ON L4K 5Y5, Canada</t>
+  </si>
+  <si>
+    <t>Monday10 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tuscany+Dental+Centre/data=!4m7!3m6!1s0x882b2f412249674d:0x6f2920a5955a980b!8m2!3d43.8274771!4d-79.5409406!16s%2Fg%2F1v7pz2_9!19sChIJTWdJIkEvK4gRC5halaUgKW8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:05:32.613Z</t>
+  </si>
+  <si>
+    <t>Bayview Hill Orthodontics</t>
+  </si>
+  <si>
+    <t>+1 905-237-6453</t>
+  </si>
+  <si>
+    <t>31 Disera Dr Unit 240, Thornhill, ON L4J 0A7, Canada</t>
+  </si>
+  <si>
+    <t>Monday10 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bayview+Hill+Orthodontics/data=!4m7!3m6!1s0x882b2b1d3cce27b5:0x6504fb55c17ae81f!8m2!3d43.811731!4d-79.4536948!16s%2Fg%2F1tc_998c!19sChIJtSfOPB0rK4gRH-h6wVX7BGU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:05:55.349Z</t>
+  </si>
+  <si>
+    <t>Optometrist - Orthodontics</t>
+  </si>
+  <si>
+    <t>+1 416-534-8333</t>
+  </si>
+  <si>
+    <t>3175 Rutherford Rd Unit 3, Concord, ON L4K 5Y6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Optometrist+-+Orthodontics/data=!4m7!3m6!1s0x882b2fa0482c256f:0x4fa9c46876a37721!8m2!3d43.8291439!4d-79.5359804!16s%2Fg%2F11fk41_k79!19sChIJbyUsSKAvK4gRIXejdmjEqU8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:05:57.170Z</t>
+  </si>
+  <si>
+    <t>Icey teeth whitening</t>
+  </si>
+  <si>
+    <t>+1 437-243-5563</t>
+  </si>
+  <si>
+    <t>8600 Keele St Unit 3, Concord, ON L4K 4H8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Icey+teeth+whitening/data=!4m7!3m6!1s0x882b2f4b54e2b459:0xe3c20620e2f4fc9f!8m2!3d43.8220604!4d-79.5058892!16s%2Fg%2F11h7w7xbqz!19sChIJWbTiVEsvK4gRn_z04iAGwuM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:07:27.834Z</t>
+  </si>
+  <si>
+    <t>Aura Dental Hygiene</t>
+  </si>
+  <si>
+    <t>+1 289-622-6065</t>
+  </si>
+  <si>
+    <t>Pieta Pl, Vaughan, ON L4H 3G2, Canada</t>
+  </si>
+  <si>
+    <t>Vaughan</t>
+  </si>
+  <si>
+    <t>Monday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aura+Dental+Hygiene/data=!4m7!3m6!1s0x882b25c16e2a8873:0x7abeffbff27c44a4!8m2!3d43.8229187!4d-79.5744271!16s%2Fg%2F11nc6zb643!19sChIJc4gqbsElK4gRpER88r__vno?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:07:36.622Z</t>
+  </si>
+  <si>
+    <t>Perry Shievitz &amp; Assoc</t>
+  </si>
+  <si>
+    <t>+1 905-850-9864</t>
+  </si>
+  <si>
+    <t>7777 Weston Rd Unit 214, Vaughan, ON L4L 0G8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Perry+Shievitz+%26+Assoc/data=!4m7!3m6!1s0x882b254440ed9ff3:0xed11475b4f698f28!8m2!3d43.7907595!4d-79.5469228!16s%2Fg%2F11b5wls8hj!19sChIJ85_tQEQlK4gRKI9pT1tHEe0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:08:06.169Z</t>
+  </si>
+  <si>
+    <t>Dr. Khatchatourov</t>
+  </si>
+  <si>
+    <t>+1 905-882-8042</t>
+  </si>
+  <si>
+    <t>1118 Centre St #14, Thornhill, ON L4J 3M8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Khatchatourov/data=!4m7!3m6!1s0x882b2c25a865754b:0x658c9b0a49d5ee0c!8m2!3d43.8096145!4d-79.4620543!16s%2Fg%2F1vfzfs_v!19sChIJS3VlqCUsK4gRDO7VSQqbjGU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:08:11.713Z</t>
+  </si>
+  <si>
+    <t>Mackenzie Keele Dental Care</t>
+  </si>
+  <si>
+    <t>+1 905-832-2571</t>
+  </si>
+  <si>
+    <t>2535 Major Mackenzie Dr W #217, Maple, ON L6A 1G5, Canada</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mackenzie+Keele+Dental+Care/data=!4m7!3m6!1s0x882b28da1d1e00a1:0x1f3785f31a1572b6!8m2!3d43.852234!4d-79.521174!16s%2Fg%2F11c1szsnl1!19sChIJoQAeHdooK4gRtnIVGvOFNx8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:08:13.877Z</t>
+  </si>
+  <si>
+    <t>Williamsburg Family Dentistry</t>
+  </si>
+  <si>
+    <t>+1 519-743-1740</t>
+  </si>
+  <si>
+    <t>325 Max Becker Dr Unit 107a, Kitchener, ON N2E 4H5, Canada</t>
+  </si>
+  <si>
+    <t>Kitchener</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Williamsburg+Family+Dentistry/data=!4m7!3m6!1s0x882bf5dbafce42df:0xb88ff096098f4a48!8m2!3d43.4047584!4d-80.500796!16s%2Fg%2F11tfnhc8xg!19sChIJ30LOr9v1K4gRSEqPCZbwj7g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:08:26.941Z</t>
+  </si>
+  <si>
+    <t>Dr Baier Krista</t>
+  </si>
+  <si>
+    <t>+1 519-578-7100</t>
+  </si>
+  <si>
+    <t>65 Glasgow St, Kitchener, ON N2G 2G8, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–4 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Baier+Krista/data=!4m7!3m6!1s0x882bf442a3d4b309:0x784869fc2501d3c4!8m2!3d43.4537795!4d-80.5111289!16s%2Fg%2F1tdfcr7y!19sChIJCbPUo0L0K4gRxNMBJfxpSHg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:10:31.314Z</t>
+  </si>
+  <si>
+    <t>Dentistry On King</t>
+  </si>
+  <si>
+    <t>+1 519-579-1899</t>
+  </si>
+  <si>
+    <t>679 King St W, Kitchener, ON N2G 1C9, Canada</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentistry+On+King/data=!4m7!3m6!1s0x882bf460ca4f2547:0xcb9c31364473869!8m2!3d43.4546467!4d-80.5044944!16s%2Fg%2F1tfwk_gh!19sChIJRyVPymD0K4gRaThHZBPDuQw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:10:46.191Z</t>
+  </si>
+  <si>
+    <t>Dentistry-While You Sleep</t>
+  </si>
+  <si>
+    <t>+1 519-749-9981</t>
+  </si>
+  <si>
+    <t>155 Ardelt Ave, Kitchener, ON N2C 2E1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentistry-While+You+Sleep/data=!4m7!3m6!1s0x882bf522f9bf475f:0x6a14ba655e3cb5a2!8m2!3d43.4244817!4d-80.4749668!16s%2Fg%2F11b5wlw9t7!19sChIJX0e_-SL1K4gRorU8XmW6FGo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:11:41.570Z</t>
+  </si>
+  <si>
+    <t>Lumi’s Dental Hygiene Care</t>
+  </si>
+  <si>
+    <t>+1 226-444-5001</t>
+  </si>
+  <si>
+    <t>1770 King St E, Kitchener, ON N2G 2P1, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lumi%E2%80%99s+Dental+Hygiene+Care/data=!4m7!3m6!1s0x882bf4c4b39668d7:0x8465afaf256e6c25!8m2!3d43.4378039!4d-80.4600604!16s%2Fg%2F11ddx4t2wt!19sChIJ12iWs8T0K4gRJWxuJa-vZYQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:11:53.854Z</t>
+  </si>
+  <si>
+    <t>Emessa Dental clinic</t>
+  </si>
+  <si>
+    <t>+1 519-253-2555</t>
+  </si>
+  <si>
+    <t>460 Erie St E Unit 5, Windsor, ON N9A 3X4, Canada</t>
+  </si>
+  <si>
+    <t>Windsor</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emessa+Dental+clinic/data=!4m7!3m6!1s0x883b2dfa0a0a879f:0xaa16c88558b56054!8m2!3d42.3116097!4d-83.0267887!16s%2Fg%2F11pcb_vldy!19sChIJn4cKCvotO4gRVGC1WIXIFqo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:13:35.396Z</t>
+  </si>
+  <si>
+    <t>Walker Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 519-985-6988</t>
+  </si>
+  <si>
+    <t>1390 Walker Rd, Windsor, ON N8Y 4T9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Walker+Dental+Clinic/data=!4m7!3m6!1s0x883b2df76608862d:0xe693aedc90e730c6!8m2!3d42.3124771!4d-83.0005035!16s%2Fg%2F11r9vxtrky!19sChIJLYYIZvctO4gRxjDnkNyuk-Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:13:46.874Z</t>
+  </si>
+  <si>
+    <t>Dr Kristyn Hope, Periodontist</t>
+  </si>
+  <si>
+    <t>+1 519-256-0833</t>
+  </si>
+  <si>
+    <t>2224 Walker Rd #100, Windsor, ON N8W 3K5, Canada</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Kristyn+Hope,+Periodontist/data=!4m7!3m6!1s0x883b2b7fd0bc6c6f:0x8fde95822ec70e23!8m2!3d42.3013516!4d-82.9931679!16s%2Fg%2F1tfxypy9!19sChIJb2y80H8rO4gRIw7HLoKV3o8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:14:51.303Z</t>
+  </si>
+  <si>
+    <t>Siara Monique A Dr</t>
+  </si>
+  <si>
+    <t>+1 519-258-1270</t>
+  </si>
+  <si>
+    <t>3475 North Service Rd E Unit d, Windsor, ON N8W 5R7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Siara+Monique+A+Dr/data=!4m7!3m6!1s0x883b2b568621b47d:0x36583457f76fe3eb!8m2!3d42.2867229!4d-82.9704018!16s%2Fg%2F1vl9s4qt!19sChIJfbQhhlYrO4gR6-Nv91c0WDY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:14:52.903Z</t>
+  </si>
+  <si>
+    <t>Barresi Mario Dr</t>
+  </si>
+  <si>
+    <t>+1 519-944-5000</t>
+  </si>
+  <si>
+    <t>3506 Tecumseh Rd E, Windsor, ON N8W 1H6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Barresi+Mario+Dr/data=!4m7!3m6!1s0x883b2b7066bb76ab:0x2415bc52c793a72b!8m2!3d42.3050204!4d-82.9816578!16s%2Fg%2F1tcx_hmk!19sChIJq3a7ZnArO4gRK6eTx1K8FSQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:14:55.132Z</t>
+  </si>
+  <si>
+    <t>Dupuis Kelly Dr</t>
+  </si>
+  <si>
+    <t>+1 519-252-7911</t>
+  </si>
+  <si>
+    <t>500 Ouellette Ave #706, Windsor, ON N9A 1B3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dupuis+Kelly+Dr/data=!4m7!3m6!1s0x883b2d1de11ed0a7:0x789ecb2954b071a6!8m2!3d42.3151329!4d-83.0370141!16s%2Fg%2F1tgc0frf!19sChIJp9Ae4R0tO4gRpnGwVCnLnng?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:14:56.856Z</t>
+  </si>
+  <si>
+    <t>Haramic Joseph Dr</t>
+  </si>
+  <si>
+    <t>+1 519-258-5919</t>
+  </si>
+  <si>
+    <t>700 Tecumseh Rd W, Windsor, ON N8X 4T2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Haramic+Joseph+Dr/data=!4m7!3m6!1s0x883b2df6cb015013:0xe52e65309eeb826a!8m2!3d42.2984698!4d-83.0145699!16s%2Fg%2F11rq3zz414!19sChIJE1ABy_YtO4gRaoLrnjBlLuU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:14:58.627Z</t>
+  </si>
+  <si>
+    <t>Brode D M Dr</t>
+  </si>
+  <si>
+    <t>+1 519-735-6063</t>
+  </si>
+  <si>
+    <t>3075 Forest Glade Dr, Windsor, ON N8R 1W6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brode+D+M+Dr/data=!4m7!3m6!1s0x883b2a9b51dc79f9:0x2840b7025d43c0d!8m2!3d42.3062097!4d-82.9147394!16s%2Fg%2F1tcy9ktk!19sChIJ-XncUZsqO4gRDTzUJXALhAI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:15:00.536Z</t>
+  </si>
+  <si>
+    <t>West Grand Dental Ctr</t>
+  </si>
+  <si>
+    <t>+1 519-972-4868</t>
+  </si>
+  <si>
+    <t>2950 Dougall Ave, Windsor, ON N9E 1S2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Grand+Dental+Ctr/data=!4m7!3m6!1s0x883b2c161a4b1809:0x678f295edd6220aa!8m2!3d42.2737773!4d-83.0141437!16s%2Fg%2F11b5wl0kb7!19sChIJCRhLGhYsO4gRqiBi3V4pj2c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:15:02.237Z</t>
+  </si>
+  <si>
+    <t>Trifonopoulos Dental Center</t>
+  </si>
+  <si>
+    <t>+1 519-966-3577</t>
+  </si>
+  <si>
+    <t>3790 Dougall Ave, Windsor, ON N9E 1T7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Trifonopoulos+Dental+Center/data=!4m7!3m6!1s0x883b2ea87d9494eb:0xd0d28d841e3bb544!8m2!3d42.2577434!4d-83.0037736!16s%2Fg%2F1hc7hxt_1!19sChIJ65SUfaguO4gRRLU7HoSN0tA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:15:04.345Z</t>
+  </si>
+  <si>
+    <t>Ljeti Snjezana Dr</t>
+  </si>
+  <si>
+    <t>+1 519-948-0101</t>
+  </si>
+  <si>
+    <t>2825 Lauzon Pkwy, Windsor, ON N8T 3H5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ljeti+Snjezana+Dr/data=!4m7!3m6!1s0x883b2aedd5f2391d:0x4ae70b84178a9633!8m2!3d42.3062239!4d-82.9339861!16s%2Fg%2F1v1vdw45!19sChIJHTny1e0qO4gRM5aKF4QL50o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:15:06.242Z</t>
+  </si>
+  <si>
+    <t>Westminster Dental</t>
+  </si>
+  <si>
+    <t>+1 519-944-1050</t>
+  </si>
+  <si>
+    <t>5105 Tecumseh Rd E, Windsor, ON N8T 1C2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Westminster+Dental/data=!4m7!3m6!1s0x4c7faeac843d728b:0x49cd22fe121efdad!8m2!3d42.3078182!4d-82.9636179!16s%2Fg%2F11v0tmblmz!19sChIJi3I9hKyuf0wRrf0eEv4izUk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:15:41.525Z</t>
+  </si>
+  <si>
+    <t>Richmond Hill Dentist</t>
+  </si>
+  <si>
+    <t>+1 905-884-0652</t>
+  </si>
+  <si>
+    <t>10825 Yonge St #202, Richmond Hill, ON L4C 3E3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Richmond+Hill+Dentist/data=!4m7!3m6!1s0x882b2a69e15f3f13:0x47adb3b15150e457!8m2!3d43.8916185!4d-79.4411984!16s%2Fg%2F11f9hvvg6m!19sChIJEz9f4WkqK4gRV-RQUbGzrUc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:17:49.139Z</t>
+  </si>
+  <si>
+    <t>Beaver Family Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 905-771-6356</t>
+  </si>
+  <si>
+    <t>155 East Beaver Creek Rd, Richmond Hill, ON L4B 2N1, Canada</t>
+  </si>
+  <si>
+    <t>Monday9:30 AM–5:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Beaver+Family+Dental+Centre/data=!4m7!3m6!1s0x89d4d4ca8949caf9:0xc29fe52faeb6658f!8m2!3d43.8491229!4d-79.3781998!16s%2Fg%2F1thsscdt!19sChIJ-cpJicrU1IkRj2W2ri_ln8I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:18:06.433Z</t>
+  </si>
+  <si>
+    <t>ArtDent Family Dentistry</t>
+  </si>
+  <si>
+    <t>+1 905-237-7842</t>
+  </si>
+  <si>
+    <t>9301 Bathurst St Unit4, Richmond Hill, ON L4C 9S2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ArtDent+Family+Dentistry/data=!4m7!3m6!1s0x882b2bc9fa433ee1:0x6c9c506e854f55c!8m2!3d43.8487581!4d-79.4579323!16s%2Fg%2F1pp2tz97g!19sChIJ4T5D-skrK4gRXPVU6AbFyQY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:18:16.740Z</t>
+  </si>
+  <si>
+    <t>Springhill Dental</t>
+  </si>
+  <si>
+    <t>+1 905-773-7733</t>
+  </si>
+  <si>
+    <t>13237 Yonge St b8, Richmond Hill, ON L4E 3L2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Springhill+Dental/data=!4m7!3m6!1s0x882ad4332166f433:0x1432f509c81649ce!8m2!3d43.951525!4d-79.4547477!16s%2Fg%2F11cmcmykb7!19sChIJM_RmITPUKogRzkkWyAn1MhQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:18:20.024Z</t>
+  </si>
+  <si>
+    <t>Dr. Marco Fazari, Dental Office - Complete Family Care</t>
+  </si>
+  <si>
+    <t>+1 905-737-9707</t>
+  </si>
+  <si>
+    <t>10909 Yonge Street, Richmond Hill, ON L4C 3E3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Marco+Fazari,+Dental+Office+-+Complete+Family+Care/data=!4m7!3m6!1s0x882b2a69ac62beed:0x6af693b37b1607e8!8m2!3d43.8945569!4d-79.4416331!16s%2Fg%2F11bby5hdr5!19sChIJ7b5irGkqK4gR6AcWe7OT9mo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:18:39.979Z</t>
+  </si>
+  <si>
+    <t>Children's Dental Office</t>
+  </si>
+  <si>
+    <t>+1 905-709-3888</t>
+  </si>
+  <si>
+    <t>300 West Beaver Creek Rd, Richmond Hill, ON L4B 3Z1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Children%27s+Dental+Office/data=!4m7!3m6!1s0x882b2b449ddd69c1:0x2ac84aa58da7bda0!8m2!3d43.8438426!4d-79.3872839!16s%2Fg%2F11b6y_y_q2!19sChIJwWndnUQrK4gRoL2njaVKyCo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:19:02.338Z</t>
+  </si>
+  <si>
+    <t>Michelberger Orthodontics</t>
+  </si>
+  <si>
+    <t>+1 905-773-4456</t>
+  </si>
+  <si>
+    <t>12820 Yonge St #101, Richmond Hill, ON L4E 4H1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michelberger+Orthodontics/data=!4m7!3m6!1s0x882ad5cf53da0161:0x7c90d60bf3aa9b06!8m2!3d43.9401319!4d-79.4540095!16s%2Fg%2F1tdx0519!19sChIJYQHaU8_VKogRBpuq8wvWkHw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:19:14.799Z</t>
+  </si>
+  <si>
+    <t>Dr.Larry Parker Orthodontist</t>
+  </si>
+  <si>
+    <t>+1 905-884-4161</t>
+  </si>
+  <si>
+    <t>9350 Yonge St Ste 216, Richmond Hill, ON L4C 5G2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.Larry+Parker+Orthodontist/data=!4m7!3m6!1s0x882b2ba2c5555555:0x6ddec39cd1c9972f!8m2!3d43.855137!4d-79.4371873!16s%2Fg%2F1hc2704l5!19sChIJVVVVxaIrK4gRL5fJ0ZzD3m0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:19:16.994Z</t>
+  </si>
+  <si>
+    <t>Montis F Dr</t>
+  </si>
+  <si>
+    <t>+1 905-884-0783</t>
+  </si>
+  <si>
+    <t>10350 Yonge St, Richmond Hill, ON L4C 3B8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Montis+F+Dr/data=!4m7!3m6!1s0x882b2a4fa86f447f:0x4877f26e5ff877b7!8m2!3d43.8797943!4d-79.4398058!16s%2Fg%2F1vy7h64y!19sChIJf0RvqE8qK4gRt3f4X27yd0g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:19:18.662Z</t>
+  </si>
+  <si>
+    <t>Dr. Maziar Shahzad Dowlatshahi, Dental Surgeon</t>
+  </si>
+  <si>
+    <t>+1 416-887-6987</t>
+  </si>
+  <si>
+    <t>Dental implants provider</t>
+  </si>
+  <si>
+    <t>10909 Yonge St #34, Richmond Hill, ON L4C 3E3, Canada</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Maziar+Shahzad+Dowlatshahi,+Dental+Surgeon/data=!4m7!3m6!1s0x882b2b87615d10af:0xc4dd8b252f298ccc!8m2!3d43.8939083!4d-79.4417757!16s%2Fg%2F11thcgk6pp!19sChIJrxBdYYcrK4gRzIwpLyWL3cQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:19:31.835Z</t>
+  </si>
+  <si>
+    <t>Royal Dental Care Richmond Hill</t>
+  </si>
+  <si>
+    <t>+1 437-998-2885</t>
+  </si>
+  <si>
+    <t>11860 Yonge St Unit 9, Richmond Hill, ON L4E 4Y2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Royal+Dental+Care+Richmond+Hill/data=!4m7!3m6!1s0x882ad5def43418e5:0xddc840501438fe48!8m2!3d43.9158267!4d-79.4483!16s%2Fg%2F11lz6lytf3!19sChIJ5Rg09N7VKogRSP44FFBAyN0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:20:00.422Z</t>
+  </si>
+  <si>
+    <t>Smile Star Dental Hygiene Clinic</t>
+  </si>
+  <si>
+    <t>+1 647-969-7572</t>
+  </si>
+  <si>
+    <t>92 Pine Bough Manor, Richmond Hill, ON L4S 1A5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smile+Star+Dental+Hygiene+Clinic/data=!4m7!3m6!1s0x882b2b006d322333:0xa7643c6a543681c6!8m2!3d43.9040621!4d-79.4325659!16s%2Fg%2F11vr_b0l0n!19sChIJMyMybQArK4gRxoE2VGo8ZKc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:20:01.947Z</t>
+  </si>
+  <si>
+    <t>EPICITI - Mobile Dental Care</t>
+  </si>
+  <si>
+    <t>+1 905-237-8422</t>
+  </si>
+  <si>
+    <t>561 Edward Ave #15, Richmond Hill, ON L4C 9W6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/EPICITI+-+Mobile+Dental+Care/data=!4m7!3m6!1s0x882b2a6308947ed5:0xbfd8a4746a852728!8m2!3d43.8978123!4d-79.4277332!16s%2Fg%2F1xtf25ts!19sChIJ1X6UCGMqK4gRKCeFanSk2L8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:20:04.083Z</t>
+  </si>
+  <si>
+    <t>Diamond dental</t>
+  </si>
+  <si>
+    <t>+1 647-539-1644</t>
+  </si>
+  <si>
+    <t>10243 Yonge St, Richmond Hill, ON L4C 3B2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Diamond+dental/data=!4m7!3m6!1s0x882b2b7d35eaf303:0xf03ebbd073e3804d!8m2!3d43.8772623!4d-79.438171!16s%2Fg%2F11jv4mhnqk!19sChIJA_PqNX0rK4gRTYDjc9C7PvA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:20:17.000Z</t>
+  </si>
+  <si>
+    <t>Glick Edward Dr</t>
+  </si>
+  <si>
+    <t>+1 905-764-1313</t>
+  </si>
+  <si>
+    <t>7191 Yonge St, Thornhill, ON L4J 1V8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Glick+Edward+Dr/data=!4m7!3m6!1s0x882b2d0f98ba73ff:0xcdcbcfd224d835f2!8m2!3d43.803492!4d-79.4209027!16s%2Fg%2F1tcyln_3!19sChIJ_3O6mA8tK4gR8jXYJNLPy80?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:20:53.249Z</t>
+  </si>
+  <si>
+    <t>16th &amp; Bayview Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 905-370-2220</t>
+  </si>
+  <si>
+    <t>675 16th Ave, Richmond Hill, ON L4C 7A8, Canada</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Monday9 AM–6:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/16th+%26+Bayview+Dental+Clinic/data=!4m7!3m6!1s0x882b2b11c42e64ef:0x545036407b043084!8m2!3d43.8568516!4d-79.4130682!16s%2Fg%2F1tctg785!19sChIJ72QuxBErK4gRhDAEe0A2UFQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:20:55.294Z</t>
+  </si>
+  <si>
+    <t>Oak Dentistry</t>
+  </si>
+  <si>
+    <t>+1 437-324-4444</t>
+  </si>
+  <si>
+    <t>4 Marvin Ave, Oakville, ON L6H 0Z8, Canada</t>
+  </si>
+  <si>
+    <t>Oakville</t>
+  </si>
+  <si>
+    <t>Monday9 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Oak+Dentistry/data=!4m7!3m6!1s0x6f5daffc1ca5ebd5:0x7e761aec39298784!8m2!3d43.4874773!4d-79.7396542!16s%2Fg%2F11yycwnm7j!19sChIJ1eulHPyvXW8RhIcpOewadn4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:21:13.462Z</t>
+  </si>
+  <si>
+    <t>Speers Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 905-844-8454</t>
+  </si>
+  <si>
+    <t>225 Speers Rd Unit 2, Oakville, ON L6K 0J4, Canada</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Speers+Dental+Centre/data=!4m7!3m6!1s0x882b5cfeab67c6b5:0x863d63781ddd11b!8m2!3d43.4439597!4d-79.6907774!16s%2Fg%2F11dfkn97nw!19sChIJtcZnq_5cK4gRG9HdgTfWYwg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:21:29.385Z</t>
+  </si>
+  <si>
+    <t>White Oaks Family Dental Care</t>
+  </si>
+  <si>
+    <t>+1 905-338-6499</t>
+  </si>
+  <si>
+    <t>Oakville, ON L6H 3P1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/White+Oaks+Family+Dental+Care/data=!4m7!3m6!1s0x882b5cd9e990bc13:0x567da63c6358c364!8m2!3d43.4675386!4d-79.6907505!16s%2Fg%2F11gr3txmw4!19sChIJE7yQ6dlcK4gRZMNYYzymfVY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:22:54.670Z</t>
+  </si>
+  <si>
+    <t>Town Centre Orthodontics</t>
+  </si>
+  <si>
+    <t>+1 905-849-1717</t>
+  </si>
+  <si>
+    <t>243 North Service Rd W, Oakville, ON L6M 3E5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Town+Centre+Orthodontics/data=!4m7!3m6!1s0x882b5d0572815c2d:0x9876175b238ac2dd!8m2!3d43.4488716!4d-79.7054709!16s%2Fg%2F11b5wqblw4!19sChIJLVyBcgVdK4gR3cKKI1sXdpg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:23:49.334Z</t>
+  </si>
+  <si>
+    <t>Oakville Invisalign Orthodontist</t>
+  </si>
+  <si>
+    <t>+1 905-849-7067</t>
+  </si>
+  <si>
+    <t>2983 Westoak Trails Blvd #2, Oakville, ON L6M 5E4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Oakville+Invisalign+Orthodontist/data=!4m7!3m6!1s0x882b671508cbf7a3:0x97c8e48ba9c51abf!8m2!3d43.4290924!4d-79.7648898!16s%2Fg%2F11grtvhqgh!19sChIJo_fLCBVnK4gRvxrFqYvkyJc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:23:51.150Z</t>
+  </si>
+  <si>
+    <t>Upper Glen Abbey Dental</t>
+  </si>
+  <si>
+    <t>+1 905-257-2556</t>
+  </si>
+  <si>
+    <t>478 Dundas St W, Oakville, ON L6H 6Y3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Upper+Glen+Abbey+Dental/data=!4m7!3m6!1s0x882b67f456dc268f:0xad1c8a42a3b555b8!8m2!3d43.4643337!4d-79.7424019!16s%2Fg%2F1tdjxndf!19sChIJjybcVvRnK4gRuFW1o0KKHK0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:23:52.931Z</t>
+  </si>
+  <si>
+    <t>Glenn Morawetz DDS</t>
+  </si>
+  <si>
+    <t>+1 905-338-2558</t>
+  </si>
+  <si>
+    <t>THE OAKVILLE PROFESSIONAL BUILDING, 627 Lyons Ln, Oakville, ON L6J 5Z7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Glenn+Morawetz+DDS/data=!4m7!3m6!1s0x882b5ce400f56e11:0x5237cb23e7af5d64!8m2!3d43.4540537!4d-79.6903191!16s%2Fg%2F1thw7c8n!19sChIJEW71AORcK4gRZF2v5yPLN1I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:23:54.899Z</t>
+  </si>
+  <si>
+    <t>Confident Smile Dental Hygiene Clinic</t>
+  </si>
+  <si>
+    <t>+1 905-257-4257</t>
+  </si>
+  <si>
+    <t>532 Postridge Dr, Oakville, ON L6H 7T2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Confident+Smile+Dental+Hygiene+Clinic/data=!4m7!3m6!1s0x882b42c7d07a245d:0xa063fc1be2b4f45b!8m2!3d43.4901396!4d-79.7153711!16s%2Fg%2F1th7yzx3!19sChIJXSR60MdCK4gRW_S04hv8Y6A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:24:59.926Z</t>
+  </si>
+  <si>
+    <t>Pin Harry Oliver</t>
+  </si>
+  <si>
+    <t>+1 905-633-1200</t>
+  </si>
+  <si>
+    <t>Prosthodontist</t>
+  </si>
+  <si>
+    <t>425 Locust St, Burlington, ON L7S 1T8, Canada</t>
+  </si>
+  <si>
+    <t>Burlington</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pin+Harry+Oliver/data=!4m7!3m6!1s0x882c9e3ac6a57b21:0x7e1540651d17220b!8m2!3d43.324584!4d-79.7977822!16s%2Fg%2F1hc2rtwrr!19sChIJIXulxjqeLIgRCyIXHWVAFX4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:04.143Z</t>
+  </si>
+  <si>
+    <t>South End Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 705-523-6876</t>
+  </si>
+  <si>
+    <t>2040 Algonquin Rd #17, Sudbury, ON P3E 4Z6, Canada</t>
+  </si>
+  <si>
+    <t>Sudbury</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+End+Dental+Centre/data=!4m7!3m6!1s0x41aa0644d14a2621:0xc0a19993e2a91ed9!8m2!3d46.4477005!4d-80.9951171!16s%2Fg%2F1tf289s1!19sChIJISZK0UQGqkER2R6p4pOZocA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:18.405Z</t>
+  </si>
+  <si>
+    <t>Janicijevic Boro Dr</t>
+  </si>
+  <si>
+    <t>+1 705-566-0975</t>
+  </si>
+  <si>
+    <t>1091 Lasalle Blvd, Sudbury, ON P3A 1X9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Janicijevic+Boro+Dr/data=!4m7!3m6!1s0x4d2faa7474cb1dd3:0x217751f8973108b3!8m2!3d46.52185!4d-80.9549171!16s%2Fg%2F1tj5qcks!19sChIJ0x3LdHSqL00Rswgxl_hRdyE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:20.300Z</t>
+  </si>
+  <si>
+    <t>Paris Family Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 705-523-5500</t>
+  </si>
+  <si>
+    <t>1865 Paris St, Greater Sudbury, ON P3E 3C5, Canada</t>
+  </si>
+  <si>
+    <t>Greater Sudbury</t>
+  </si>
+  <si>
+    <t>Monday7:30 AM–4 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Paris+Family+Dental+Centre/data=!4m7!3m6!1s0x41aa0659d5d616b1:0xf525543955c7fbdb!8m2!3d46.4547009!4d-81.0026625!16s%2Fg%2F1q663lpwn!19sChIJsRbW1VkGqkER2_vHVTlUJfU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:22.178Z</t>
+  </si>
+  <si>
+    <t>Family Dental Health</t>
+  </si>
+  <si>
+    <t>+1 705-673-4289</t>
+  </si>
+  <si>
+    <t>121 Durham St, Sudbury, ON P3E 1B7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dental+Health/data=!4m7!3m6!1s0x4d2faae7e39d5011:0x870a7f142f1b623c!8m2!3d46.490745!4d-80.9952264!16s%2Fg%2F11c2prgmfb!19sChIJEVCd4-eqL00RPGIbLxR_Coc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:24.161Z</t>
+  </si>
+  <si>
+    <t>Reich Mark Dr</t>
+  </si>
+  <si>
+    <t>+1 705-560-2727</t>
+  </si>
+  <si>
+    <t>1280 Lasalle Blvd #202, Greater Sudbury, ON P3A 1Y8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Reich+Mark+Dr/data=!4m7!3m6!1s0x4d2f009e29ccdb8f:0x22a0c7a99dabd799!8m2!3d46.5224876!4d-80.9486007!16s%2Fg%2F1v96lf8g!19sChIJj9vMKZ4AL00RmdernanHoCI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:25.956Z</t>
+  </si>
+  <si>
+    <t>Copper Cliff Dental Office</t>
+  </si>
+  <si>
+    <t>+1 705-682-0622</t>
+  </si>
+  <si>
+    <t>17 Serpentine St, Copper Cliff, ON P0M 1N0, Canada</t>
+  </si>
+  <si>
+    <t>Copper Cliff</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Copper+Cliff+Dental+Office/data=!4m7!3m6!1s0x4d2facace8bf0039:0xa55f945891b4106c!8m2!3d46.4775683!4d-81.066807!16s%2Fg%2F1w0h746t!19sChIJOQC_6KysL00RbBC0kViUX6U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:27.715Z</t>
+  </si>
+  <si>
+    <t>Dr Joseph Nebre</t>
+  </si>
+  <si>
+    <t>+1 705-525-1100</t>
+  </si>
+  <si>
+    <t>463 Falconbridge Rd, Greater Sudbury, ON P3A 5N4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Joseph+Nebre/data=!4m7!3m6!1s0x4d2f01c05fc80bb3:0xb306974316ea7421!8m2!3d46.5107434!4d-80.9332223!16s%2Fg%2F11j7yb6zvn!19sChIJswvIX8ABL00RIXTqFkOXBrM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:29.611Z</t>
+  </si>
+  <si>
+    <t>Trottier Charles H Dr</t>
+  </si>
+  <si>
+    <t>+1 705-671-1887</t>
+  </si>
+  <si>
+    <t>265 Elm St, Greater Sudbury, ON P3C 1V5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Trottier+Charles+H+Dr/data=!4m7!3m6!1s0x4d2faae02d763ce7:0x1c6fcd20117717ca!8m2!3d46.4928702!4d-81.0053786!16s%2Fg%2F1tfs0q0p!19sChIJ5zx2LeCqL00Ryhd3ESDNbxw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:33.582Z</t>
+  </si>
+  <si>
+    <t>Peter Villa DDS</t>
+  </si>
+  <si>
+    <t>+1 705-523-3355</t>
+  </si>
+  <si>
+    <t>2009 Long Lake Rd, Sudbury, ON P3E 6C3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Peter+Villa+DDS/data=!4m7!3m6!1s0x4d2e55163b5645bd:0x126056d7f4b96507!8m2!3d46.4515113!4d-81.0050125!16s%2Fg%2F1txnp2ph!19sChIJvUVWOxZVLk0RB2W59NdWYBI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:36.800Z</t>
+  </si>
+  <si>
+    <t>Dr Martin Martic</t>
+  </si>
+  <si>
+    <t>+1 705-560-7000</t>
+  </si>
+  <si>
+    <t>850 Barry Downe Rd, Greater Sudbury, ON P3A 3T7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Martin+Martic/data=!4m7!3m6!1s0x4d2fabf836ce7879:0xa3d54b60a933cde0!8m2!3d46.5153885!4d-80.9437349!16s%2Fg%2F11pz53x2pn!19sChIJeXjONvirL00R4M0zqWBL1aM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:38.895Z</t>
+  </si>
+  <si>
+    <t>Dr. Tom Tiedemann</t>
+  </si>
+  <si>
+    <t>+1 705-675-2900</t>
+  </si>
+  <si>
+    <t>900 Lasalle Blvd, Sudbury, ON P3A 5W8, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–7:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tom+Tiedemann/data=!4m7!3m6!1s0x4d2faa7274d24bc3:0xf1e0026c1be85acf!8m2!3d46.5233697!4d-80.9610897!16s%2Fg%2F11bbycqbmn!19sChIJw0vSdHKqL00Rz1roG2wC4PE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:40.661Z</t>
+  </si>
+  <si>
+    <t>Dr Henry Moser</t>
+  </si>
+  <si>
+    <t>+1 705-522-0220 ext. 2</t>
+  </si>
+  <si>
+    <t>1984 Regent St #102, Sudbury, ON P3E 5S1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Henry+Moser/data=!4m7!3m6!1s0x41aa005fe11cdcc1:0xe495763fccfc721e!8m2!3d46.4517358!4d-80.9998154!16s%2Fg%2F11b75hzswr!19sChIJwdwc4V8AqkERHnL8zD92leQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:45.127Z</t>
+  </si>
+  <si>
+    <t>Bruce Haddad DDS</t>
+  </si>
+  <si>
+    <t>+1 705-674-0191</t>
+  </si>
+  <si>
+    <t>1351 Martindale Rd B, Greater Sudbury, ON P3E 4J7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bruce+Haddad+DDS/data=!4m7!3m6!1s0x4d2e55292b446177:0x2cb41cb89fc853a4!8m2!3d46.4645545!4d-81.0095692!16s%2Fg%2F1tf8sr01!19sChIJd2FEKylVLk0RpFPIn7gctCw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:49.716Z</t>
+  </si>
+  <si>
+    <t>Arteck Dental Services</t>
+  </si>
+  <si>
+    <t>+1 705-671-2526</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>2152 Long Lake Rd Unit 1, Greater Sudbury, ON P3E 5H1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Arteck+Dental+Services/data=!4m7!3m6!1s0x4d2e5516db42517f:0x9ce69fd4ffaf97fc!8m2!3d46.4479538!4d-81.0042543!16s%2Fg%2F1tff77hh!19sChIJf1FC2xZVLk0R_Jev_9Sf5pw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:29:52.421Z</t>
+  </si>
+  <si>
+    <t>Kuchtaruk Andrew Dr</t>
+  </si>
+  <si>
+    <t>+1 705-523-4522</t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>1935 Paris St, Greater Sudbury, ON P3E 3C6, Canada</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kuchtaruk+Andrew+Dr/data=!4m7!3m6!1s0x4d2e553d92e52dbb:0x6b317ca3474c5121!8m2!3d46.4531631!4d-81.0031142!16s%2Fg%2F1w0j3v6q!19sChIJuy3lkj1VLk0RIVFMR6N8MWs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:30:05.036Z</t>
+  </si>
+  <si>
+    <t>Dr Andersen Joel</t>
+  </si>
+  <si>
+    <t>+1 705-522-8718</t>
+  </si>
+  <si>
+    <t>1935 Paris St, Greater Sudbury, ON T3E 3C6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Andersen+Joel/data=!4m7!3m6!1s0x41aa00d39f2401c9:0xe53b323b5327dbe1!8m2!3d46.45282!4d-81.0032832!16s%2Fg%2F1w0p57y9!19sChIJyQEkn9MAqkER4dsnUzsyO-U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:30:06.651Z</t>
+  </si>
+  <si>
+    <t>E Bortolotto DDS</t>
+  </si>
+  <si>
+    <t>+1 705-897-5883</t>
+  </si>
+  <si>
+    <t>2996 Old Hwy 69, Val Caron, ON P3N 1P3, Canada</t>
+  </si>
+  <si>
+    <t>Val Caron</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/E+Bortolotto+DDS/data=!4m7!3m6!1s0x4d2fa8b705040685:0xe5637d3c083c7e8f!8m2!3d46.6101723!4d-81.006877!16s%2Fg%2F1tjt1ksm!19sChIJhQYEBbeoL00Rj348CDx9Y-U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:30:41.703Z</t>
+  </si>
+  <si>
+    <t>Gerhart Kristie Dr</t>
+  </si>
+  <si>
+    <t>+1 705-969-4774</t>
+  </si>
+  <si>
+    <t>4434 Notre Dame Ave, Hanmer, ON P3P 1X5, Canada</t>
+  </si>
+  <si>
+    <t>Hanmer</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gerhart+Kristie+Dr/data=!4m7!3m6!1s0x4d2fa7b041c3c451:0x7f440d9fa08caa11!8m2!3d46.6494674!4d-80.9440689!16s%2Fg%2F1tj4gpcq!19sChIJUcTDQbCnL00REaqMoJ8NRH8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:31:04.547Z</t>
+  </si>
+  <si>
+    <t>Dental Office Coniston</t>
+  </si>
+  <si>
+    <t>+1 705-694-5342</t>
+  </si>
+  <si>
+    <t>61 1st Ave, Coniston, ON P0M 1M0, Canada</t>
+  </si>
+  <si>
+    <t>Coniston</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Office+Coniston/data=!4m7!3m6!1s0x4d2f0231981c6dab:0x464181ccc3dd7997!8m2!3d46.4921261!4d-80.8482776!16s%2Fg%2F11b5wkz4q0!19sChIJq20cmDECL00Rl3ndw8yBQUY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:31:06.474Z</t>
+  </si>
+  <si>
+    <t>Dr. Bob Khosraviani</t>
+  </si>
+  <si>
+    <t>+1 905-404-6660</t>
+  </si>
+  <si>
+    <t>98 Stevenson Rd S, Oshawa, ON L1J 5M1, Canada</t>
+  </si>
+  <si>
+    <t>Oshawa</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Bob+Khosraviani/data=!4m7!3m6!1s0x89d51d00bbd39161:0x53f492d18883928!8m2!3d43.8903723!4d-78.8825429!16s%2Fg%2F11c7498cw0!19sChIJYZHTuwAd1YkRKDmIGC1JPwU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:32:53.731Z</t>
+  </si>
+  <si>
+    <t>Dr. Sandra Zakarow &amp; Associates</t>
+  </si>
+  <si>
+    <t>+1 905-434-1991</t>
+  </si>
+  <si>
+    <t>172 King St E #201, Oshawa, ON L1H 1B7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sandra+Zakarow+%26+Associates/data=!4m7!3m6!1s0x89d51d8d2063fbd1:0xb43f4fbc96a07d77!8m2!3d43.899515!4d-78.8576163!16s%2Fg%2F11g3_9_ztk!19sChIJ0ftjII0d1YkRd32glrxPP7Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:32:56.860Z</t>
+  </si>
+  <si>
+    <t>DD Dental</t>
+  </si>
+  <si>
+    <t>+1 905-240-7002</t>
+  </si>
+  <si>
+    <t>467 Bond St E, Oshawa, ON L1G 1B9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/DD+Dental/data=!4m7!3m6!1s0x89d51ccf0434a153:0xfc004206cf33fd9!8m2!3d43.9030929!4d-78.8473209!16s%2Fg%2F11b6nvypp1!19sChIJU6E0BM8c1YkR2T_zbCAEwA8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:33:03.566Z</t>
+  </si>
+  <si>
+    <t>Luczak Dorota Dentistry Professional Co</t>
+  </si>
+  <si>
+    <t>+1 905-436-6199</t>
+  </si>
+  <si>
+    <t>122 Simcoe St N, Oshawa, ON L1G 4S5, Canada</t>
+  </si>
+  <si>
+    <t>Monday1–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Luczak+Dorota+Dentistry+Professional+Co/data=!4m7!3m6!1s0x89d51ce64283928b:0x47b4f4ec30037401!8m2!3d43.9007527!4d-78.8653068!16s%2Fg%2F1tl8lpx5!19sChIJi5KDQuYc1YkRAXQDMOz0tEc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:33:05.537Z</t>
+  </si>
+  <si>
+    <t>5 Points Dental Office</t>
+  </si>
+  <si>
+    <t>+1 905-571-4005</t>
+  </si>
+  <si>
+    <t>1177 Ritson Rd N, Oshawa, ON L1G 8B9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/5+Points+Dental+Office/data=!4m7!3m6!1s0x89d51b6160e6999f:0x22a11e5e2170b6e5!8m2!3d43.9309902!4d-78.8659579!16s%2Fg%2F1vknqck_!19sChIJn5nmYGEb1YkR5bZwIV4eoSI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:33:28.553Z</t>
+  </si>
+  <si>
+    <t>Steve Mascarin</t>
+  </si>
+  <si>
+    <t>+1 905-432-5000</t>
+  </si>
+  <si>
+    <t>510 Taunton Rd E, Oshawa, ON L1K 1A8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Steve+Mascarin/data=!4m7!3m6!1s0x89d5c42ce55b5935:0x9686c1da6f28c6f1!8m2!3d43.9372787!4d-78.8609651!16s%2Fg%2F11bw3d0wq9!19sChIJNVlb5SzE1YkR8cYob9rBhpY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:33:52.140Z</t>
+  </si>
+  <si>
+    <t>Denture Clinic</t>
+  </si>
+  <si>
+    <t>+1 905-434-8999</t>
+  </si>
+  <si>
+    <t>419 King St W, Oshawa, ON L1J 2K5, Canada</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denture+Clinic/data=!4m7!3m6!1s0x89d51d00b9d4fa07:0x55e191be00bb09c7!8m2!3d43.8898779!4d-78.8796635!16s%2Fg%2F1tfmd6r4!19sChIJB_rUuQAd1YkRxwm7AL6R4VU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:34:38.481Z</t>
+  </si>
+  <si>
+    <t>Icy Smile Bar</t>
+  </si>
+  <si>
+    <t>+1 647-510-3741</t>
+  </si>
+  <si>
+    <t>555 Simcoe St S, Oshawa, ON L1H 8K8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Icy+Smile+Bar/data=!4m7!3m6!1s0x89d51d070976ee27:0xd6fa590edf4d501!8m2!3d43.8838615!4d-78.8557284!16s%2Fg%2F11stb15mnt!19sChIJJ-52CQcd1YkRAdX07ZClbw0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:34:59.880Z</t>
+  </si>
+  <si>
+    <t>Dr. C. Nayot</t>
+  </si>
+  <si>
+    <t>+1 905-725-5088</t>
+  </si>
+  <si>
+    <t>292 King St W, Oshawa, ON L1J 0A1, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–5:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+C.+Nayot/data=!4m7!3m6!1s0x89d51cfd1239025d:0x4ac3b37ee7d920ad!8m2!3d43.8955478!4d-78.8745607!16s%2Fg%2F1v1tp1wh!19sChIJXQI5Ev0c1YkRrSDZ536zw0o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:35:07.503Z</t>
+  </si>
+  <si>
+    <t>Baystone Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 705-730-7575</t>
+  </si>
+  <si>
+    <t>454 Bayfield St, Barrie, ON L4M 5A2, Canada</t>
+  </si>
+  <si>
+    <t>Barrie</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Baystone+Dental+Centre/data=!4m7!3m6!1s0x882aa2eedfc54523:0x1a4ac7e40821f470!8m2!3d44.4105255!4d-79.7092653!16s%2Fg%2F11fnwg_fwy!19sChIJI0XF3-6iKogRcPQhCOTHSho?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:36:15.333Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental Care @ Barrie Dental Arts</t>
+  </si>
+  <si>
+    <t>+1 647-398-9799</t>
+  </si>
+  <si>
+    <t>85 Ferris Ln #201, Barrie, ON L4M 6B9, Canada</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>MondayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+Care+@+Barrie+Dental+Arts/data=!4m7!3m6!1s0x882b2f765ce1934b:0x86badae5787636!8m2!3d44.4054983!4d-79.6941003!16s%2Fg%2F11vt1yz33p!19sChIJS5PhXHYvK4gRNnZ45dq6hgA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:36:18.301Z</t>
+  </si>
+  <si>
+    <t>Vila Smiles Family Dentistry</t>
+  </si>
+  <si>
+    <t>+1 705-500-6243</t>
+  </si>
+  <si>
+    <t>85 Ferris Ln Unit 105, Barrie, ON L4M 6B9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vila+Smiles+Family+Dentistry/data=!4m7!3m6!1s0x882aa39027d6f9cb:0x1f574ab1f6603ac4!8m2!3d44.4054983!4d-79.6941003!16s%2Fg%2F11ykxy7kn2!19sChIJy_nWJ5CjKogRxDpg9rFKVx8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:36:22.662Z</t>
+  </si>
+  <si>
+    <t>Advanced Teeth Whitening</t>
+  </si>
+  <si>
+    <t>+1 705-734-7769</t>
+  </si>
+  <si>
+    <t>526 Bryne Dr, Barrie, ON L4N 9P6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Advanced+Teeth+Whitening/data=!4m7!3m6!1s0x882abda40a565b29:0x1a78ca0af7a68b75!8m2!3d44.3293495!4d-79.6895567!16s%2Fg%2F11xcwlkxj3!19sChIJKVtWCqS9KogRdYum9wrKeBo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:37:20.046Z</t>
+  </si>
+  <si>
+    <t>Deller Murray P Dr</t>
+  </si>
+  <si>
+    <t>+1 705-728-1261</t>
+  </si>
+  <si>
+    <t>85 Ferris Ln, Barrie, ON L4M 6B9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Deller+Murray+P+Dr/data=!4m7!3m6!1s0x882aa31fd2fbd9d3:0xd48ebb64d365699!8m2!3d44.4055055!4d-79.6942665!16s%2Fg%2F1tmpl3tr!19sChIJ09n70h-jKogRmVY2TbbrSA0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:37:49.202Z</t>
+  </si>
+  <si>
+    <t>Dr. Tisch David</t>
+  </si>
+  <si>
+    <t>+1 705-721-8851</t>
+  </si>
+  <si>
+    <t>34 Quarry Ridge Rd Ste 200, Barrie, ON L4M 7G1, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–4:30 PM; Tuesday8 AM–4:30 PM; Wednesday8 AM–4:30 PM; Thursday8 AM–4:30 PM; Friday8 AM–12 PM; Saturday12 AM–1 PM; SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tisch+David/data=!4m7!3m6!1s0x882aa31fd2fbd9d3:0xdb2c4721060ccca8!8m2!3d44.4156798!4d-79.6558302!16s%2Fg%2F1vgw97l8!19sChIJ09n70h-jKogRqMwMBiFHLNs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:38:08.912Z</t>
+  </si>
+  <si>
+    <t>Clinic of Whiteness</t>
+  </si>
+  <si>
+    <t>+1 705-970-3533</t>
+  </si>
+  <si>
+    <t>371 King St Unit 5, Barrie, ON L4N 6B5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinic+of+Whiteness/data=!4m7!3m6!1s0x882abd1390d9cc7b:0xe3b83443f9e6f22!8m2!3d44.3279969!4d-79.6984485!16s%2Fg%2F11zhxg_6dl!19sChIJe8zZkBO9KogRIm-eP0SDOw4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:38:56.830Z</t>
+  </si>
+  <si>
+    <t>Simcoe Muskoka Dental Hygiene</t>
+  </si>
+  <si>
+    <t>+1 705-321-1871</t>
+  </si>
+  <si>
+    <t>67 Red Oak Dr, Barrie, ON L4N 9M5, Canada</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Monday7 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Simcoe+Muskoka+Dental+Hygiene/data=!4m7!3m6!1s0x882abde9ff399da9:0xe9a3b0fd2655e4f2!8m2!3d44.328844!4d-79.7328137!16s%2Fg%2F11j2xjp1pn!19sChIJqZ05_-m9KogR8uRVJv2wo-k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:39:00.299Z</t>
+  </si>
+  <si>
+    <t>Infinity Dental Specialists</t>
+  </si>
+  <si>
+    <t>+1 905-378-2272</t>
+  </si>
+  <si>
+    <t>95 Lakeport Rd Unit C, St. Catharines, ON L2N 4P9, Canada</t>
+  </si>
+  <si>
+    <t>St. Catharines</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Infinity+Dental+Specialists/data=!4m7!3m6!1s0x89d3510bc92c0367:0xd06aee83b20174b8!8m2!3d43.1970023!4d-79.2613014!16s%2Fg%2F11ml25vrh6!19sChIJZwMsyQtR04kRuHQBsoPuatA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:39:24.061Z</t>
+  </si>
+  <si>
+    <t>Chan David S L Dr &amp; Dr Amit Narwal</t>
+  </si>
+  <si>
+    <t>+1 905-937-4710</t>
+  </si>
+  <si>
+    <t>282 Linwell Rd, St. Catharines, ON L2N 6N5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chan+David+S+L+Dr+%26+Dr+Amit+Narwal/data=!4m7!3m6!1s0x89d350da3714899d:0xed5164bbff9e05bc!8m2!3d43.1948637!4d-79.2374242!16s%2Fg%2F1v_z599l!19sChIJnYkUN9pQ04kRvAWe_7tkUe0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:39:26.147Z</t>
+  </si>
+  <si>
+    <t>Warkentin Kirby J Dr</t>
+  </si>
+  <si>
+    <t>+1 905-682-7595</t>
+  </si>
+  <si>
+    <t>4 Lake St, St. Catharines, ON L2R 5W6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Warkentin+Kirby+J+Dr/data=!4m7!3m6!1s0x89d351b3d3fe0b41:0x9dc8b20b733a554a!8m2!3d43.1572242!4d-79.2501261!16s%2Fg%2F1tgn5qrv!19sChIJQQv-07NR04kRSlU6cwuyyJ0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:39:27.782Z</t>
+  </si>
+  <si>
+    <t>Walter Rodrigues Family</t>
+  </si>
+  <si>
+    <t>+1 905-688-0510</t>
+  </si>
+  <si>
+    <t>203 Ontario St, St. Catharines, ON L2R 5L2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Walter+Rodrigues+Family/data=!4m7!3m6!1s0x89d351a5136a09bb:0x81a01a4eeb4b5f6b!8m2!3d43.1621693!4d-79.2581059!16s%2Fg%2F1tdzs3dm!19sChIJuwlqE6VR04kRa19L604aoIE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:39:45.518Z</t>
+  </si>
+  <si>
+    <t>Dentistry By Dr. Korody And Associates</t>
+  </si>
+  <si>
+    <t>+1 905-937-1515</t>
+  </si>
+  <si>
+    <t>17 Lock St #1, St. Catharines, ON L2N 5B6, Canada</t>
+  </si>
+  <si>
+    <t>Monday6 AM–7:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentistry+By+Dr.+Korody+And+Associates/data=!4m7!3m6!1s0x89d3515ecc2cc4f5:0xc9a461c5f5606e00!8m2!3d43.2022889!4d-79.26683!16s%2Fg%2F11bx8rk1xl!19sChIJ9cQszF5R04kRAG5g9cVhpMk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:39:56.984Z</t>
+  </si>
+  <si>
+    <t>Affordable Laser &amp; Cosmetic Clinic</t>
+  </si>
+  <si>
+    <t>+1 905-346-0500</t>
+  </si>
+  <si>
+    <t>180 Vine St S, St. Catharines, ON L2R 3Y5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Affordable+Laser+%26+Cosmetic+Clinic/data=!4m7!3m6!1s0x89d350f6c495ae0f:0x7e7a46a9f28213a9!8m2!3d43.1717857!4d-79.2289943!16s%2Fg%2F11b5wqr8ns!19sChIJD66VxPZQ04kRqROC8qlGen4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:39:58.648Z</t>
+  </si>
+  <si>
+    <t>My Orthodontic Laboratory</t>
+  </si>
+  <si>
+    <t>+1 905-685-1123</t>
+  </si>
+  <si>
+    <t>159 Niagara St, St. Catharines, ON L2R 4L8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/My+Orthodontic+Laboratory/data=!4m7!3m6!1s0x89d350f9d7cc3c1d:0xe68fbe1d116d98e5!8m2!3d43.1707701!4d-79.2341873!16s%2Fg%2F1tc_r_c0!19sChIJHTzM1_lQ04kR5ZhtER2-j-Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:40:14.045Z</t>
+  </si>
+  <si>
+    <t>Dr.Timperio Dental</t>
+  </si>
+  <si>
+    <t>+1 905-938-7636</t>
+  </si>
+  <si>
+    <t>142 Linwell Rd, St. Catharines, ON L2N 6N4, Canada</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.Timperio+Dental/data=!4m7!3m6!1s0x89d3512305d9a317:0x646f65713444cf05!8m2!3d43.1898877!4d-79.2531674!16s%2Fg%2F11z79b9khw!19sChIJF6PZBSNR04kRBc9ENHFlb2Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:40:16.106Z</t>
+  </si>
+  <si>
+    <t>Sinclair K E Dr &amp; Dr Amit Narwal</t>
+  </si>
+  <si>
+    <t>+1 905-685-4003</t>
+  </si>
+  <si>
+    <t>105 Queenston St, St. Catharines, ON L2R 2Z5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sinclair+K+E+Dr+%26+Dr+Amit+Narwal/data=!4m7!3m6!1s0x89d35059fca1229f:0xa02ab5d86fbd00cf!8m2!3d43.1637229!4d-79.2334671!16s%2Fg%2F1vm7cfr_!19sChIJnyKh_FlQ04kRzwC9b9i1KqA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:40:18.032Z</t>
+  </si>
+  <si>
+    <t>Niagara Dental Health Centre</t>
+  </si>
+  <si>
+    <t>+1 905-581-1786</t>
+  </si>
+  <si>
+    <t>185 Merritt St, St. Catharines, ON L2T 1J7, Canada</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Niagara+Dental+Health+Centre/data=!4m7!3m6!1s0x89d3501aca10b697:0x5711e01996e7b5e7!8m2!3d43.135321!4d-79.2090252!16s%2Fg%2F11btwrx6q1!19sChIJl7YQyhpQ04kR57XnlhngEVc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:40:31.628Z</t>
+  </si>
+  <si>
+    <t>Eric Kemp DD Denture Care</t>
+  </si>
+  <si>
+    <t>+1 289-969-9247</t>
+  </si>
+  <si>
+    <t>210 Martindale Rd, St. Catharines, ON L2R 6P9, Canada</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Monday10 AM–4 PM; Tuesday10 AM–4 PM; Wednesday10 AM–4 PM; Thursday10 AM–4 PM; Friday10 AM–4 PM; SaturdayClosed; SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Eric+Kemp+DD+Denture+Care/data=!4m7!3m6!1s0x89d349cb6fab70d5:0x55de889f708752d8!8m2!3d43.1729438!4d-79.2730653!16s%2Fg%2F1tcz996s!19sChIJ1XCrb8tJ04kR2FKHcJ-I3lU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T10:40:33.488Z</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +3373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3164,6 +5276,5131 @@
         <v>289</v>
       </c>
     </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>290</v>
+      </c>
+      <c r="B47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" t="s">
+        <v>292</v>
+      </c>
+      <c r="E47" t="s">
+        <v>277</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>293</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>294</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>295</v>
+      </c>
+      <c r="M47" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B48" t="s">
+        <v>298</v>
+      </c>
+      <c r="C48" t="s">
+        <v>299</v>
+      </c>
+      <c r="D48" t="s">
+        <v>300</v>
+      </c>
+      <c r="E48" t="s">
+        <v>277</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" t="s">
+        <v>301</v>
+      </c>
+      <c r="J48" t="s">
+        <v>302</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>303</v>
+      </c>
+      <c r="M48" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>305</v>
+      </c>
+      <c r="B49" t="s">
+        <v>306</v>
+      </c>
+      <c r="C49" t="s">
+        <v>71</v>
+      </c>
+      <c r="D49" t="s">
+        <v>307</v>
+      </c>
+      <c r="E49" t="s">
+        <v>277</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>38</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>308</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>309</v>
+      </c>
+      <c r="M49" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>311</v>
+      </c>
+      <c r="B50" t="s">
+        <v>312</v>
+      </c>
+      <c r="C50" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" t="s">
+        <v>313</v>
+      </c>
+      <c r="E50" t="s">
+        <v>277</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>38</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>46</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>314</v>
+      </c>
+      <c r="M50" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>316</v>
+      </c>
+      <c r="B51" t="s">
+        <v>317</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>318</v>
+      </c>
+      <c r="E51" t="s">
+        <v>319</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>38</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>320</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>321</v>
+      </c>
+      <c r="M51" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>323</v>
+      </c>
+      <c r="B52" t="s">
+        <v>324</v>
+      </c>
+      <c r="C52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" t="s">
+        <v>325</v>
+      </c>
+      <c r="E52" t="s">
+        <v>319</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>326</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>327</v>
+      </c>
+      <c r="M52" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>329</v>
+      </c>
+      <c r="B53" t="s">
+        <v>330</v>
+      </c>
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" t="s">
+        <v>331</v>
+      </c>
+      <c r="E53" t="s">
+        <v>319</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>332</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>333</v>
+      </c>
+      <c r="M53" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>335</v>
+      </c>
+      <c r="B54" t="s">
+        <v>336</v>
+      </c>
+      <c r="C54" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" t="s">
+        <v>337</v>
+      </c>
+      <c r="E54" t="s">
+        <v>319</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>338</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>339</v>
+      </c>
+      <c r="M54" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>341</v>
+      </c>
+      <c r="B55" t="s">
+        <v>342</v>
+      </c>
+      <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" t="s">
+        <v>343</v>
+      </c>
+      <c r="E55" t="s">
+        <v>319</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>157</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>344</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>345</v>
+      </c>
+      <c r="M55" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>347</v>
+      </c>
+      <c r="B56" t="s">
+        <v>348</v>
+      </c>
+      <c r="C56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" t="s">
+        <v>349</v>
+      </c>
+      <c r="E56" t="s">
+        <v>319</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>46</v>
+      </c>
+      <c r="I56" t="s">
+        <v>98</v>
+      </c>
+      <c r="J56" t="s">
+        <v>46</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>350</v>
+      </c>
+      <c r="M56" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>352</v>
+      </c>
+      <c r="B57" t="s">
+        <v>353</v>
+      </c>
+      <c r="C57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" t="s">
+        <v>354</v>
+      </c>
+      <c r="E57" t="s">
+        <v>355</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>139</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>356</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>357</v>
+      </c>
+      <c r="M57" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>359</v>
+      </c>
+      <c r="B58" t="s">
+        <v>360</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" t="s">
+        <v>361</v>
+      </c>
+      <c r="E58" t="s">
+        <v>355</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>52</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>362</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>363</v>
+      </c>
+      <c r="M58" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>365</v>
+      </c>
+      <c r="B59" t="s">
+        <v>366</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>367</v>
+      </c>
+      <c r="E59" t="s">
+        <v>355</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>52</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>368</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>369</v>
+      </c>
+      <c r="M59" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>371</v>
+      </c>
+      <c r="B60" t="s">
+        <v>372</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" t="s">
+        <v>373</v>
+      </c>
+      <c r="E60" t="s">
+        <v>355</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>374</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>375</v>
+      </c>
+      <c r="M60" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>377</v>
+      </c>
+      <c r="B61" t="s">
+        <v>378</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" t="s">
+        <v>379</v>
+      </c>
+      <c r="E61" t="s">
+        <v>355</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>46</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>380</v>
+      </c>
+      <c r="M61" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>382</v>
+      </c>
+      <c r="B62" t="s">
+        <v>383</v>
+      </c>
+      <c r="C62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" t="s">
+        <v>384</v>
+      </c>
+      <c r="E62" t="s">
+        <v>385</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>338</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>386</v>
+      </c>
+      <c r="M62" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>388</v>
+      </c>
+      <c r="B63" t="s">
+        <v>389</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s">
+        <v>390</v>
+      </c>
+      <c r="E63" t="s">
+        <v>385</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>391</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>392</v>
+      </c>
+      <c r="M63" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>394</v>
+      </c>
+      <c r="B64" t="s">
+        <v>395</v>
+      </c>
+      <c r="C64" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" t="s">
+        <v>396</v>
+      </c>
+      <c r="E64" t="s">
+        <v>385</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>38</v>
+      </c>
+      <c r="I64" t="s">
+        <v>397</v>
+      </c>
+      <c r="J64" t="s">
+        <v>398</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>399</v>
+      </c>
+      <c r="M64" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>401</v>
+      </c>
+      <c r="B65" t="s">
+        <v>402</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>403</v>
+      </c>
+      <c r="E65" t="s">
+        <v>355</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" t="s">
+        <v>98</v>
+      </c>
+      <c r="J65" t="s">
+        <v>46</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>404</v>
+      </c>
+      <c r="M65" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>406</v>
+      </c>
+      <c r="B66" t="s">
+        <v>407</v>
+      </c>
+      <c r="C66" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" t="s">
+        <v>408</v>
+      </c>
+      <c r="E66" t="s">
+        <v>355</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>209</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>409</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>410</v>
+      </c>
+      <c r="M66" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>412</v>
+      </c>
+      <c r="B67" t="s">
+        <v>413</v>
+      </c>
+      <c r="C67" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" t="s">
+        <v>414</v>
+      </c>
+      <c r="E67" t="s">
+        <v>355</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>38</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>368</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>415</v>
+      </c>
+      <c r="M67" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>417</v>
+      </c>
+      <c r="B68" t="s">
+        <v>418</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
+        <v>419</v>
+      </c>
+      <c r="E68" t="s">
+        <v>355</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>139</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>46</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>420</v>
+      </c>
+      <c r="M68" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>422</v>
+      </c>
+      <c r="B69" t="s">
+        <v>423</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>424</v>
+      </c>
+      <c r="E69" t="s">
+        <v>385</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>92</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>391</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>425</v>
+      </c>
+      <c r="M69" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>427</v>
+      </c>
+      <c r="B70" t="s">
+        <v>428</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>429</v>
+      </c>
+      <c r="E70" t="s">
+        <v>355</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>46</v>
+      </c>
+      <c r="I70" t="s">
+        <v>98</v>
+      </c>
+      <c r="J70" t="s">
+        <v>430</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>431</v>
+      </c>
+      <c r="M70" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>433</v>
+      </c>
+      <c r="B71" t="s">
+        <v>434</v>
+      </c>
+      <c r="C71" t="s">
+        <v>258</v>
+      </c>
+      <c r="D71" t="s">
+        <v>435</v>
+      </c>
+      <c r="E71" t="s">
+        <v>436</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>139</v>
+      </c>
+      <c r="I71" t="s">
+        <v>437</v>
+      </c>
+      <c r="J71" t="s">
+        <v>438</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>439</v>
+      </c>
+      <c r="M71" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>441</v>
+      </c>
+      <c r="B72" t="s">
+        <v>442</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>443</v>
+      </c>
+      <c r="E72" t="s">
+        <v>355</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>46</v>
+      </c>
+      <c r="I72" t="s">
+        <v>98</v>
+      </c>
+      <c r="J72" t="s">
+        <v>294</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>444</v>
+      </c>
+      <c r="M72" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>446</v>
+      </c>
+      <c r="B73" t="s">
+        <v>447</v>
+      </c>
+      <c r="C73" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" t="s">
+        <v>448</v>
+      </c>
+      <c r="E73" t="s">
+        <v>449</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>450</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>338</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>451</v>
+      </c>
+      <c r="M73" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>453</v>
+      </c>
+      <c r="B74" t="s">
+        <v>454</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" t="s">
+        <v>455</v>
+      </c>
+      <c r="E74" t="s">
+        <v>456</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>52</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>326</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>457</v>
+      </c>
+      <c r="M74" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>459</v>
+      </c>
+      <c r="B75" t="s">
+        <v>460</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s">
+        <v>461</v>
+      </c>
+      <c r="E75" t="s">
+        <v>449</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>38</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>462</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>463</v>
+      </c>
+      <c r="M75" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>465</v>
+      </c>
+      <c r="B76" t="s">
+        <v>466</v>
+      </c>
+      <c r="C76" t="s">
+        <v>121</v>
+      </c>
+      <c r="D76" t="s">
+        <v>467</v>
+      </c>
+      <c r="E76" t="s">
+        <v>58</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>38</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>468</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>469</v>
+      </c>
+      <c r="M76" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>471</v>
+      </c>
+      <c r="B77" t="s">
+        <v>472</v>
+      </c>
+      <c r="C77" t="s">
+        <v>121</v>
+      </c>
+      <c r="D77" t="s">
+        <v>473</v>
+      </c>
+      <c r="E77" t="s">
+        <v>449</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>46</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>474</v>
+      </c>
+      <c r="M77" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>476</v>
+      </c>
+      <c r="B78" t="s">
+        <v>477</v>
+      </c>
+      <c r="C78" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" t="s">
+        <v>478</v>
+      </c>
+      <c r="E78" t="s">
+        <v>449</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>38</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>398</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>479</v>
+      </c>
+      <c r="M78" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>481</v>
+      </c>
+      <c r="B79" t="s">
+        <v>482</v>
+      </c>
+      <c r="C79" t="s">
+        <v>71</v>
+      </c>
+      <c r="D79" t="s">
+        <v>483</v>
+      </c>
+      <c r="E79" t="s">
+        <v>484</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>38</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>485</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>486</v>
+      </c>
+      <c r="M79" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>488</v>
+      </c>
+      <c r="B80" t="s">
+        <v>489</v>
+      </c>
+      <c r="C80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" t="s">
+        <v>490</v>
+      </c>
+      <c r="E80" t="s">
+        <v>484</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>46</v>
+      </c>
+      <c r="I80" t="s">
+        <v>98</v>
+      </c>
+      <c r="J80" t="s">
+        <v>46</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>491</v>
+      </c>
+      <c r="M80" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>493</v>
+      </c>
+      <c r="B81" t="s">
+        <v>494</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" t="s">
+        <v>495</v>
+      </c>
+      <c r="E81" t="s">
+        <v>58</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>38</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>368</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>496</v>
+      </c>
+      <c r="M81" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>498</v>
+      </c>
+      <c r="B82" t="s">
+        <v>499</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" t="s">
+        <v>500</v>
+      </c>
+      <c r="E82" t="s">
+        <v>456</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>38</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s">
+        <v>501</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>502</v>
+      </c>
+      <c r="M82" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>504</v>
+      </c>
+      <c r="B83" t="s">
+        <v>505</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" t="s">
+        <v>506</v>
+      </c>
+      <c r="E83" t="s">
+        <v>507</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>59</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>368</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>508</v>
+      </c>
+      <c r="M83" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>510</v>
+      </c>
+      <c r="B84" t="s">
+        <v>511</v>
+      </c>
+      <c r="C84" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" t="s">
+        <v>512</v>
+      </c>
+      <c r="E84" t="s">
+        <v>507</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>157</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>513</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>514</v>
+      </c>
+      <c r="M84" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>516</v>
+      </c>
+      <c r="B85" t="s">
+        <v>517</v>
+      </c>
+      <c r="C85" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85" t="s">
+        <v>518</v>
+      </c>
+      <c r="E85" t="s">
+        <v>507</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>519</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>462</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>520</v>
+      </c>
+      <c r="M85" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>522</v>
+      </c>
+      <c r="B86" t="s">
+        <v>523</v>
+      </c>
+      <c r="C86" t="s">
+        <v>28</v>
+      </c>
+      <c r="D86" t="s">
+        <v>524</v>
+      </c>
+      <c r="E86" t="s">
+        <v>507</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>46</v>
+      </c>
+      <c r="I86" t="s">
+        <v>98</v>
+      </c>
+      <c r="J86" t="s">
+        <v>46</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>525</v>
+      </c>
+      <c r="M86" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>527</v>
+      </c>
+      <c r="B87" t="s">
+        <v>528</v>
+      </c>
+      <c r="C87" t="s">
+        <v>71</v>
+      </c>
+      <c r="D87" t="s">
+        <v>529</v>
+      </c>
+      <c r="E87" t="s">
+        <v>507</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>38</v>
+      </c>
+      <c r="I87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s">
+        <v>530</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>531</v>
+      </c>
+      <c r="M87" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>533</v>
+      </c>
+      <c r="B88" t="s">
+        <v>534</v>
+      </c>
+      <c r="C88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" t="s">
+        <v>535</v>
+      </c>
+      <c r="E88" t="s">
+        <v>536</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>462</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>537</v>
+      </c>
+      <c r="M88" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>539</v>
+      </c>
+      <c r="B89" t="s">
+        <v>540</v>
+      </c>
+      <c r="C89" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" t="s">
+        <v>541</v>
+      </c>
+      <c r="E89" t="s">
+        <v>536</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>59</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s">
+        <v>391</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>542</v>
+      </c>
+      <c r="M89" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>544</v>
+      </c>
+      <c r="B90" t="s">
+        <v>545</v>
+      </c>
+      <c r="C90" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" t="s">
+        <v>546</v>
+      </c>
+      <c r="E90" t="s">
+        <v>536</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>547</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>344</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>548</v>
+      </c>
+      <c r="M90" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>550</v>
+      </c>
+      <c r="B91" t="s">
+        <v>551</v>
+      </c>
+      <c r="C91" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" t="s">
+        <v>552</v>
+      </c>
+      <c r="E91" t="s">
+        <v>536</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>73</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>462</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>553</v>
+      </c>
+      <c r="M91" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>555</v>
+      </c>
+      <c r="B92" t="s">
+        <v>556</v>
+      </c>
+      <c r="C92" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" t="s">
+        <v>557</v>
+      </c>
+      <c r="E92" t="s">
+        <v>536</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>38</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>46</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" t="s">
+        <v>558</v>
+      </c>
+      <c r="M92" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>560</v>
+      </c>
+      <c r="B93" t="s">
+        <v>561</v>
+      </c>
+      <c r="C93" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" t="s">
+        <v>562</v>
+      </c>
+      <c r="E93" t="s">
+        <v>536</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>139</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>46</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>563</v>
+      </c>
+      <c r="M93" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>565</v>
+      </c>
+      <c r="B94" t="s">
+        <v>566</v>
+      </c>
+      <c r="C94" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" t="s">
+        <v>567</v>
+      </c>
+      <c r="E94" t="s">
+        <v>536</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>38</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>46</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>568</v>
+      </c>
+      <c r="M94" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>570</v>
+      </c>
+      <c r="B95" t="s">
+        <v>571</v>
+      </c>
+      <c r="C95" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" t="s">
+        <v>572</v>
+      </c>
+      <c r="E95" t="s">
+        <v>536</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>139</v>
+      </c>
+      <c r="I95" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s">
+        <v>344</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" t="s">
+        <v>573</v>
+      </c>
+      <c r="M95" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>575</v>
+      </c>
+      <c r="B96" t="s">
+        <v>576</v>
+      </c>
+      <c r="C96" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" t="s">
+        <v>577</v>
+      </c>
+      <c r="E96" t="s">
+        <v>536</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>38</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s">
+        <v>46</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" t="s">
+        <v>578</v>
+      </c>
+      <c r="M96" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>580</v>
+      </c>
+      <c r="B97" t="s">
+        <v>581</v>
+      </c>
+      <c r="C97" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" t="s">
+        <v>582</v>
+      </c>
+      <c r="E97" t="s">
+        <v>536</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>38</v>
+      </c>
+      <c r="I97" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s">
+        <v>46</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" t="s">
+        <v>583</v>
+      </c>
+      <c r="M97" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>585</v>
+      </c>
+      <c r="B98" t="s">
+        <v>586</v>
+      </c>
+      <c r="C98" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" t="s">
+        <v>587</v>
+      </c>
+      <c r="E98" t="s">
+        <v>536</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>38</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s">
+        <v>326</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" t="s">
+        <v>588</v>
+      </c>
+      <c r="M98" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>590</v>
+      </c>
+      <c r="B99" t="s">
+        <v>591</v>
+      </c>
+      <c r="C99" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" t="s">
+        <v>592</v>
+      </c>
+      <c r="E99" t="s">
+        <v>536</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" t="s">
+        <v>38</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>344</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" t="s">
+        <v>593</v>
+      </c>
+      <c r="M99" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>595</v>
+      </c>
+      <c r="B100" t="s">
+        <v>596</v>
+      </c>
+      <c r="C100" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" t="s">
+        <v>597</v>
+      </c>
+      <c r="E100" t="s">
+        <v>436</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>46</v>
+      </c>
+      <c r="I100" t="s">
+        <v>98</v>
+      </c>
+      <c r="J100" t="s">
+        <v>46</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" t="s">
+        <v>598</v>
+      </c>
+      <c r="M100" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>600</v>
+      </c>
+      <c r="B101" t="s">
+        <v>601</v>
+      </c>
+      <c r="C101" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" t="s">
+        <v>602</v>
+      </c>
+      <c r="E101" t="s">
+        <v>436</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>139</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s">
+        <v>603</v>
+      </c>
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" t="s">
+        <v>604</v>
+      </c>
+      <c r="M101" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>606</v>
+      </c>
+      <c r="B102" t="s">
+        <v>607</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" t="s">
+        <v>608</v>
+      </c>
+      <c r="E102" t="s">
+        <v>436</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>157</v>
+      </c>
+      <c r="I102" t="s">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s">
+        <v>46</v>
+      </c>
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" t="s">
+        <v>609</v>
+      </c>
+      <c r="M102" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>611</v>
+      </c>
+      <c r="B103" t="s">
+        <v>612</v>
+      </c>
+      <c r="C103" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" t="s">
+        <v>613</v>
+      </c>
+      <c r="E103" t="s">
+        <v>436</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>30</v>
+      </c>
+      <c r="I103" t="s">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s">
+        <v>391</v>
+      </c>
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" t="s">
+        <v>614</v>
+      </c>
+      <c r="M103" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>616</v>
+      </c>
+      <c r="B104" t="s">
+        <v>617</v>
+      </c>
+      <c r="C104" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" t="s">
+        <v>618</v>
+      </c>
+      <c r="E104" t="s">
+        <v>436</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" t="s">
+        <v>38</v>
+      </c>
+      <c r="I104" t="s">
+        <v>21</v>
+      </c>
+      <c r="J104" t="s">
+        <v>485</v>
+      </c>
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" t="s">
+        <v>619</v>
+      </c>
+      <c r="M104" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>621</v>
+      </c>
+      <c r="B105" t="s">
+        <v>622</v>
+      </c>
+      <c r="C105" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105" t="s">
+        <v>623</v>
+      </c>
+      <c r="E105" t="s">
+        <v>436</v>
+      </c>
+      <c r="F105" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" t="s">
+        <v>46</v>
+      </c>
+      <c r="I105" t="s">
+        <v>98</v>
+      </c>
+      <c r="J105" t="s">
+        <v>46</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" t="s">
+        <v>624</v>
+      </c>
+      <c r="M105" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>626</v>
+      </c>
+      <c r="B106" t="s">
+        <v>627</v>
+      </c>
+      <c r="C106" t="s">
+        <v>121</v>
+      </c>
+      <c r="D106" t="s">
+        <v>628</v>
+      </c>
+      <c r="E106" t="s">
+        <v>436</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>38</v>
+      </c>
+      <c r="I106" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s">
+        <v>501</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" t="s">
+        <v>629</v>
+      </c>
+      <c r="M106" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>631</v>
+      </c>
+      <c r="B107" t="s">
+        <v>632</v>
+      </c>
+      <c r="C107" t="s">
+        <v>121</v>
+      </c>
+      <c r="D107" t="s">
+        <v>633</v>
+      </c>
+      <c r="E107" t="s">
+        <v>436</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>30</v>
+      </c>
+      <c r="I107" t="s">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s">
+        <v>294</v>
+      </c>
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107" t="s">
+        <v>634</v>
+      </c>
+      <c r="M107" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>636</v>
+      </c>
+      <c r="B108" t="s">
+        <v>637</v>
+      </c>
+      <c r="C108" t="s">
+        <v>28</v>
+      </c>
+      <c r="D108" t="s">
+        <v>638</v>
+      </c>
+      <c r="E108" t="s">
+        <v>436</v>
+      </c>
+      <c r="F108" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>59</v>
+      </c>
+      <c r="I108" t="s">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s">
+        <v>485</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" t="s">
+        <v>639</v>
+      </c>
+      <c r="M108" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>641</v>
+      </c>
+      <c r="B109" t="s">
+        <v>642</v>
+      </c>
+      <c r="C109" t="s">
+        <v>643</v>
+      </c>
+      <c r="D109" t="s">
+        <v>644</v>
+      </c>
+      <c r="E109" t="s">
+        <v>436</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" t="s">
+        <v>21</v>
+      </c>
+      <c r="J109" t="s">
+        <v>645</v>
+      </c>
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109" t="s">
+        <v>646</v>
+      </c>
+      <c r="M109" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>648</v>
+      </c>
+      <c r="B110" t="s">
+        <v>649</v>
+      </c>
+      <c r="C110" t="s">
+        <v>71</v>
+      </c>
+      <c r="D110" t="s">
+        <v>650</v>
+      </c>
+      <c r="E110" t="s">
+        <v>436</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" t="s">
+        <v>38</v>
+      </c>
+      <c r="I110" t="s">
+        <v>21</v>
+      </c>
+      <c r="J110" t="s">
+        <v>374</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" t="s">
+        <v>651</v>
+      </c>
+      <c r="M110" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>653</v>
+      </c>
+      <c r="B111" t="s">
+        <v>654</v>
+      </c>
+      <c r="C111" t="s">
+        <v>71</v>
+      </c>
+      <c r="D111" t="s">
+        <v>655</v>
+      </c>
+      <c r="E111" t="s">
+        <v>436</v>
+      </c>
+      <c r="F111" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" t="s">
+        <v>38</v>
+      </c>
+      <c r="I111" t="s">
+        <v>21</v>
+      </c>
+      <c r="J111" t="s">
+        <v>46</v>
+      </c>
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111" t="s">
+        <v>656</v>
+      </c>
+      <c r="M111" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>658</v>
+      </c>
+      <c r="B112" t="s">
+        <v>659</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" t="s">
+        <v>660</v>
+      </c>
+      <c r="E112" t="s">
+        <v>436</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>73</v>
+      </c>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s">
+        <v>485</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" t="s">
+        <v>661</v>
+      </c>
+      <c r="M112" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>663</v>
+      </c>
+      <c r="B113" t="s">
+        <v>664</v>
+      </c>
+      <c r="C113" t="s">
+        <v>71</v>
+      </c>
+      <c r="D113" t="s">
+        <v>665</v>
+      </c>
+      <c r="E113" t="s">
+        <v>436</v>
+      </c>
+      <c r="F113" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" t="s">
+        <v>38</v>
+      </c>
+      <c r="I113" t="s">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s">
+        <v>356</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113" t="s">
+        <v>666</v>
+      </c>
+      <c r="M113" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>668</v>
+      </c>
+      <c r="B114" t="s">
+        <v>669</v>
+      </c>
+      <c r="C114" t="s">
+        <v>28</v>
+      </c>
+      <c r="D114" t="s">
+        <v>670</v>
+      </c>
+      <c r="E114" t="s">
+        <v>58</v>
+      </c>
+      <c r="F114" t="s">
+        <v>18</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>73</v>
+      </c>
+      <c r="I114" t="s">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s">
+        <v>46</v>
+      </c>
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114" t="s">
+        <v>671</v>
+      </c>
+      <c r="M114" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>673</v>
+      </c>
+      <c r="B115" t="s">
+        <v>674</v>
+      </c>
+      <c r="C115" t="s">
+        <v>28</v>
+      </c>
+      <c r="D115" t="s">
+        <v>675</v>
+      </c>
+      <c r="E115" t="s">
+        <v>436</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
+        <v>676</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s">
+        <v>677</v>
+      </c>
+      <c r="K115" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" t="s">
+        <v>678</v>
+      </c>
+      <c r="M115" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>680</v>
+      </c>
+      <c r="B116" t="s">
+        <v>681</v>
+      </c>
+      <c r="C116" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" t="s">
+        <v>682</v>
+      </c>
+      <c r="E116" t="s">
+        <v>683</v>
+      </c>
+      <c r="F116" t="s">
+        <v>18</v>
+      </c>
+      <c r="G116" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" t="s">
+        <v>59</v>
+      </c>
+      <c r="I116" t="s">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s">
+        <v>684</v>
+      </c>
+      <c r="K116" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" t="s">
+        <v>685</v>
+      </c>
+      <c r="M116" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>687</v>
+      </c>
+      <c r="B117" t="s">
+        <v>688</v>
+      </c>
+      <c r="C117" t="s">
+        <v>28</v>
+      </c>
+      <c r="D117" t="s">
+        <v>689</v>
+      </c>
+      <c r="E117" t="s">
+        <v>683</v>
+      </c>
+      <c r="F117" t="s">
+        <v>18</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" t="s">
+        <v>20</v>
+      </c>
+      <c r="I117" t="s">
+        <v>690</v>
+      </c>
+      <c r="J117" t="s">
+        <v>374</v>
+      </c>
+      <c r="K117" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" t="s">
+        <v>691</v>
+      </c>
+      <c r="M117" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>693</v>
+      </c>
+      <c r="B118" t="s">
+        <v>694</v>
+      </c>
+      <c r="C118" t="s">
+        <v>28</v>
+      </c>
+      <c r="D118" t="s">
+        <v>695</v>
+      </c>
+      <c r="E118" t="s">
+        <v>683</v>
+      </c>
+      <c r="F118" t="s">
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
+        <v>38</v>
+      </c>
+      <c r="I118" t="s">
+        <v>21</v>
+      </c>
+      <c r="J118" t="s">
+        <v>684</v>
+      </c>
+      <c r="K118" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" t="s">
+        <v>696</v>
+      </c>
+      <c r="M118" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>698</v>
+      </c>
+      <c r="B119" t="s">
+        <v>699</v>
+      </c>
+      <c r="C119" t="s">
+        <v>28</v>
+      </c>
+      <c r="D119" t="s">
+        <v>700</v>
+      </c>
+      <c r="E119" t="s">
+        <v>683</v>
+      </c>
+      <c r="F119" t="s">
+        <v>18</v>
+      </c>
+      <c r="G119" t="s">
+        <v>19</v>
+      </c>
+      <c r="H119" t="s">
+        <v>46</v>
+      </c>
+      <c r="I119" t="s">
+        <v>98</v>
+      </c>
+      <c r="J119" t="s">
+        <v>46</v>
+      </c>
+      <c r="K119" t="s">
+        <v>23</v>
+      </c>
+      <c r="L119" t="s">
+        <v>701</v>
+      </c>
+      <c r="M119" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>703</v>
+      </c>
+      <c r="B120" t="s">
+        <v>704</v>
+      </c>
+      <c r="C120" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" t="s">
+        <v>705</v>
+      </c>
+      <c r="E120" t="s">
+        <v>683</v>
+      </c>
+      <c r="F120" t="s">
+        <v>18</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" t="s">
+        <v>46</v>
+      </c>
+      <c r="I120" t="s">
+        <v>98</v>
+      </c>
+      <c r="J120" t="s">
+        <v>46</v>
+      </c>
+      <c r="K120" t="s">
+        <v>23</v>
+      </c>
+      <c r="L120" t="s">
+        <v>706</v>
+      </c>
+      <c r="M120" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>708</v>
+      </c>
+      <c r="B121" t="s">
+        <v>709</v>
+      </c>
+      <c r="C121" t="s">
+        <v>28</v>
+      </c>
+      <c r="D121" t="s">
+        <v>710</v>
+      </c>
+      <c r="E121" t="s">
+        <v>683</v>
+      </c>
+      <c r="F121" t="s">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" t="s">
+        <v>20</v>
+      </c>
+      <c r="I121" t="s">
+        <v>21</v>
+      </c>
+      <c r="J121" t="s">
+        <v>338</v>
+      </c>
+      <c r="K121" t="s">
+        <v>23</v>
+      </c>
+      <c r="L121" t="s">
+        <v>711</v>
+      </c>
+      <c r="M121" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>713</v>
+      </c>
+      <c r="B122" t="s">
+        <v>714</v>
+      </c>
+      <c r="C122" t="s">
+        <v>28</v>
+      </c>
+      <c r="D122" t="s">
+        <v>715</v>
+      </c>
+      <c r="E122" t="s">
+        <v>683</v>
+      </c>
+      <c r="F122" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" t="s">
+        <v>209</v>
+      </c>
+      <c r="I122" t="s">
+        <v>21</v>
+      </c>
+      <c r="J122" t="s">
+        <v>46</v>
+      </c>
+      <c r="K122" t="s">
+        <v>23</v>
+      </c>
+      <c r="L122" t="s">
+        <v>716</v>
+      </c>
+      <c r="M122" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>718</v>
+      </c>
+      <c r="B123" t="s">
+        <v>719</v>
+      </c>
+      <c r="C123" t="s">
+        <v>71</v>
+      </c>
+      <c r="D123" t="s">
+        <v>720</v>
+      </c>
+      <c r="E123" t="s">
+        <v>683</v>
+      </c>
+      <c r="F123" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" t="s">
+        <v>38</v>
+      </c>
+      <c r="I123" t="s">
+        <v>21</v>
+      </c>
+      <c r="J123" t="s">
+        <v>338</v>
+      </c>
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123" t="s">
+        <v>721</v>
+      </c>
+      <c r="M123" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>723</v>
+      </c>
+      <c r="B124" t="s">
+        <v>724</v>
+      </c>
+      <c r="C124" t="s">
+        <v>725</v>
+      </c>
+      <c r="D124" t="s">
+        <v>726</v>
+      </c>
+      <c r="E124" t="s">
+        <v>727</v>
+      </c>
+      <c r="F124" t="s">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>19</v>
+      </c>
+      <c r="H124" t="s">
+        <v>38</v>
+      </c>
+      <c r="I124" t="s">
+        <v>728</v>
+      </c>
+      <c r="J124" t="s">
+        <v>46</v>
+      </c>
+      <c r="K124" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124" t="s">
+        <v>729</v>
+      </c>
+      <c r="M124" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>731</v>
+      </c>
+      <c r="B125" t="s">
+        <v>732</v>
+      </c>
+      <c r="C125" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125" t="s">
+        <v>733</v>
+      </c>
+      <c r="E125" t="s">
+        <v>734</v>
+      </c>
+      <c r="F125" t="s">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" t="s">
+        <v>38</v>
+      </c>
+      <c r="I125" t="s">
+        <v>21</v>
+      </c>
+      <c r="J125" t="s">
+        <v>485</v>
+      </c>
+      <c r="K125" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125" t="s">
+        <v>735</v>
+      </c>
+      <c r="M125" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>737</v>
+      </c>
+      <c r="B126" t="s">
+        <v>738</v>
+      </c>
+      <c r="C126" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" t="s">
+        <v>739</v>
+      </c>
+      <c r="E126" t="s">
+        <v>734</v>
+      </c>
+      <c r="F126" t="s">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>19</v>
+      </c>
+      <c r="H126" t="s">
+        <v>38</v>
+      </c>
+      <c r="I126" t="s">
+        <v>21</v>
+      </c>
+      <c r="J126" t="s">
+        <v>344</v>
+      </c>
+      <c r="K126" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126" t="s">
+        <v>740</v>
+      </c>
+      <c r="M126" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>742</v>
+      </c>
+      <c r="B127" t="s">
+        <v>743</v>
+      </c>
+      <c r="C127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D127" t="s">
+        <v>744</v>
+      </c>
+      <c r="E127" t="s">
+        <v>745</v>
+      </c>
+      <c r="F127" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
+      </c>
+      <c r="H127" t="s">
+        <v>92</v>
+      </c>
+      <c r="I127" t="s">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s">
+        <v>746</v>
+      </c>
+      <c r="K127" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127" t="s">
+        <v>747</v>
+      </c>
+      <c r="M127" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>749</v>
+      </c>
+      <c r="B128" t="s">
+        <v>750</v>
+      </c>
+      <c r="C128" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" t="s">
+        <v>751</v>
+      </c>
+      <c r="E128" t="s">
+        <v>734</v>
+      </c>
+      <c r="F128" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
+      </c>
+      <c r="H128" t="s">
+        <v>38</v>
+      </c>
+      <c r="I128" t="s">
+        <v>21</v>
+      </c>
+      <c r="J128" t="s">
+        <v>501</v>
+      </c>
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128" t="s">
+        <v>752</v>
+      </c>
+      <c r="M128" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>754</v>
+      </c>
+      <c r="B129" t="s">
+        <v>755</v>
+      </c>
+      <c r="C129" t="s">
+        <v>28</v>
+      </c>
+      <c r="D129" t="s">
+        <v>756</v>
+      </c>
+      <c r="E129" t="s">
+        <v>745</v>
+      </c>
+      <c r="F129" t="s">
+        <v>18</v>
+      </c>
+      <c r="G129" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" t="s">
+        <v>59</v>
+      </c>
+      <c r="I129" t="s">
+        <v>21</v>
+      </c>
+      <c r="J129" t="s">
+        <v>501</v>
+      </c>
+      <c r="K129" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129" t="s">
+        <v>757</v>
+      </c>
+      <c r="M129" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>759</v>
+      </c>
+      <c r="B130" t="s">
+        <v>760</v>
+      </c>
+      <c r="C130" t="s">
+        <v>28</v>
+      </c>
+      <c r="D130" t="s">
+        <v>761</v>
+      </c>
+      <c r="E130" t="s">
+        <v>762</v>
+      </c>
+      <c r="F130" t="s">
+        <v>18</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" t="s">
+        <v>30</v>
+      </c>
+      <c r="I130" t="s">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s">
+        <v>344</v>
+      </c>
+      <c r="K130" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130" t="s">
+        <v>763</v>
+      </c>
+      <c r="M130" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>765</v>
+      </c>
+      <c r="B131" t="s">
+        <v>766</v>
+      </c>
+      <c r="C131" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131" t="s">
+        <v>767</v>
+      </c>
+      <c r="E131" t="s">
+        <v>745</v>
+      </c>
+      <c r="F131" t="s">
+        <v>18</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
+      </c>
+      <c r="H131" t="s">
+        <v>38</v>
+      </c>
+      <c r="I131" t="s">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s">
+        <v>46</v>
+      </c>
+      <c r="K131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131" t="s">
+        <v>768</v>
+      </c>
+      <c r="M131" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>770</v>
+      </c>
+      <c r="B132" t="s">
+        <v>771</v>
+      </c>
+      <c r="C132" t="s">
+        <v>28</v>
+      </c>
+      <c r="D132" t="s">
+        <v>772</v>
+      </c>
+      <c r="E132" t="s">
+        <v>745</v>
+      </c>
+      <c r="F132" t="s">
+        <v>18</v>
+      </c>
+      <c r="G132" t="s">
+        <v>19</v>
+      </c>
+      <c r="H132" t="s">
+        <v>73</v>
+      </c>
+      <c r="I132" t="s">
+        <v>21</v>
+      </c>
+      <c r="J132" t="s">
+        <v>46</v>
+      </c>
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132" t="s">
+        <v>773</v>
+      </c>
+      <c r="M132" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>775</v>
+      </c>
+      <c r="B133" t="s">
+        <v>776</v>
+      </c>
+      <c r="C133" t="s">
+        <v>28</v>
+      </c>
+      <c r="D133" t="s">
+        <v>777</v>
+      </c>
+      <c r="E133" t="s">
+        <v>734</v>
+      </c>
+      <c r="F133" t="s">
+        <v>18</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
+      </c>
+      <c r="H133" t="s">
+        <v>38</v>
+      </c>
+      <c r="I133" t="s">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s">
+        <v>501</v>
+      </c>
+      <c r="K133" t="s">
+        <v>23</v>
+      </c>
+      <c r="L133" t="s">
+        <v>778</v>
+      </c>
+      <c r="M133" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>780</v>
+      </c>
+      <c r="B134" t="s">
+        <v>781</v>
+      </c>
+      <c r="C134" t="s">
+        <v>28</v>
+      </c>
+      <c r="D134" t="s">
+        <v>782</v>
+      </c>
+      <c r="E134" t="s">
+        <v>745</v>
+      </c>
+      <c r="F134" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" t="s">
+        <v>46</v>
+      </c>
+      <c r="I134" t="s">
+        <v>98</v>
+      </c>
+      <c r="J134" t="s">
+        <v>46</v>
+      </c>
+      <c r="K134" t="s">
+        <v>23</v>
+      </c>
+      <c r="L134" t="s">
+        <v>783</v>
+      </c>
+      <c r="M134" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>785</v>
+      </c>
+      <c r="B135" t="s">
+        <v>786</v>
+      </c>
+      <c r="C135" t="s">
+        <v>28</v>
+      </c>
+      <c r="D135" t="s">
+        <v>787</v>
+      </c>
+      <c r="E135" t="s">
+        <v>734</v>
+      </c>
+      <c r="F135" t="s">
+        <v>18</v>
+      </c>
+      <c r="G135" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" t="s">
+        <v>92</v>
+      </c>
+      <c r="I135" t="s">
+        <v>21</v>
+      </c>
+      <c r="J135" t="s">
+        <v>788</v>
+      </c>
+      <c r="K135" t="s">
+        <v>23</v>
+      </c>
+      <c r="L135" t="s">
+        <v>789</v>
+      </c>
+      <c r="M135" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>791</v>
+      </c>
+      <c r="B136" t="s">
+        <v>792</v>
+      </c>
+      <c r="C136" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" t="s">
+        <v>793</v>
+      </c>
+      <c r="E136" t="s">
+        <v>734</v>
+      </c>
+      <c r="F136" t="s">
+        <v>18</v>
+      </c>
+      <c r="G136" t="s">
+        <v>19</v>
+      </c>
+      <c r="H136" t="s">
+        <v>46</v>
+      </c>
+      <c r="I136" t="s">
+        <v>98</v>
+      </c>
+      <c r="J136" t="s">
+        <v>684</v>
+      </c>
+      <c r="K136" t="s">
+        <v>23</v>
+      </c>
+      <c r="L136" t="s">
+        <v>794</v>
+      </c>
+      <c r="M136" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>796</v>
+      </c>
+      <c r="B137" t="s">
+        <v>797</v>
+      </c>
+      <c r="C137" t="s">
+        <v>28</v>
+      </c>
+      <c r="D137" t="s">
+        <v>798</v>
+      </c>
+      <c r="E137" t="s">
+        <v>745</v>
+      </c>
+      <c r="F137" t="s">
+        <v>18</v>
+      </c>
+      <c r="G137" t="s">
+        <v>19</v>
+      </c>
+      <c r="H137" t="s">
+        <v>46</v>
+      </c>
+      <c r="I137" t="s">
+        <v>98</v>
+      </c>
+      <c r="J137" t="s">
+        <v>46</v>
+      </c>
+      <c r="K137" t="s">
+        <v>23</v>
+      </c>
+      <c r="L137" t="s">
+        <v>799</v>
+      </c>
+      <c r="M137" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>801</v>
+      </c>
+      <c r="B138" t="s">
+        <v>802</v>
+      </c>
+      <c r="C138" t="s">
+        <v>803</v>
+      </c>
+      <c r="D138" t="s">
+        <v>804</v>
+      </c>
+      <c r="E138" t="s">
+        <v>745</v>
+      </c>
+      <c r="F138" t="s">
+        <v>18</v>
+      </c>
+      <c r="G138" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" t="s">
+        <v>46</v>
+      </c>
+      <c r="I138" t="s">
+        <v>98</v>
+      </c>
+      <c r="J138" t="s">
+        <v>46</v>
+      </c>
+      <c r="K138" t="s">
+        <v>23</v>
+      </c>
+      <c r="L138" t="s">
+        <v>805</v>
+      </c>
+      <c r="M138" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>807</v>
+      </c>
+      <c r="B139" t="s">
+        <v>808</v>
+      </c>
+      <c r="C139" t="s">
+        <v>809</v>
+      </c>
+      <c r="D139" t="s">
+        <v>810</v>
+      </c>
+      <c r="E139" t="s">
+        <v>745</v>
+      </c>
+      <c r="F139" t="s">
+        <v>18</v>
+      </c>
+      <c r="G139" t="s">
+        <v>19</v>
+      </c>
+      <c r="H139" t="s">
+        <v>811</v>
+      </c>
+      <c r="I139" t="s">
+        <v>21</v>
+      </c>
+      <c r="J139" t="s">
+        <v>46</v>
+      </c>
+      <c r="K139" t="s">
+        <v>23</v>
+      </c>
+      <c r="L139" t="s">
+        <v>812</v>
+      </c>
+      <c r="M139" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>814</v>
+      </c>
+      <c r="B140" t="s">
+        <v>815</v>
+      </c>
+      <c r="C140" t="s">
+        <v>809</v>
+      </c>
+      <c r="D140" t="s">
+        <v>816</v>
+      </c>
+      <c r="E140" t="s">
+        <v>745</v>
+      </c>
+      <c r="F140" t="s">
+        <v>18</v>
+      </c>
+      <c r="G140" t="s">
+        <v>19</v>
+      </c>
+      <c r="H140" t="s">
+        <v>46</v>
+      </c>
+      <c r="I140" t="s">
+        <v>98</v>
+      </c>
+      <c r="J140" t="s">
+        <v>46</v>
+      </c>
+      <c r="K140" t="s">
+        <v>23</v>
+      </c>
+      <c r="L140" t="s">
+        <v>817</v>
+      </c>
+      <c r="M140" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>819</v>
+      </c>
+      <c r="B141" t="s">
+        <v>820</v>
+      </c>
+      <c r="C141" t="s">
+        <v>28</v>
+      </c>
+      <c r="D141" t="s">
+        <v>821</v>
+      </c>
+      <c r="E141" t="s">
+        <v>822</v>
+      </c>
+      <c r="F141" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" t="s">
+        <v>19</v>
+      </c>
+      <c r="H141" t="s">
+        <v>823</v>
+      </c>
+      <c r="I141" t="s">
+        <v>21</v>
+      </c>
+      <c r="J141" t="s">
+        <v>374</v>
+      </c>
+      <c r="K141" t="s">
+        <v>23</v>
+      </c>
+      <c r="L141" t="s">
+        <v>824</v>
+      </c>
+      <c r="M141" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>826</v>
+      </c>
+      <c r="B142" t="s">
+        <v>827</v>
+      </c>
+      <c r="C142" t="s">
+        <v>28</v>
+      </c>
+      <c r="D142" t="s">
+        <v>828</v>
+      </c>
+      <c r="E142" t="s">
+        <v>829</v>
+      </c>
+      <c r="F142" t="s">
+        <v>18</v>
+      </c>
+      <c r="G142" t="s">
+        <v>19</v>
+      </c>
+      <c r="H142" t="s">
+        <v>20</v>
+      </c>
+      <c r="I142" t="s">
+        <v>21</v>
+      </c>
+      <c r="J142" t="s">
+        <v>344</v>
+      </c>
+      <c r="K142" t="s">
+        <v>23</v>
+      </c>
+      <c r="L142" t="s">
+        <v>830</v>
+      </c>
+      <c r="M142" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>832</v>
+      </c>
+      <c r="B143" t="s">
+        <v>833</v>
+      </c>
+      <c r="C143" t="s">
+        <v>28</v>
+      </c>
+      <c r="D143" t="s">
+        <v>834</v>
+      </c>
+      <c r="E143" t="s">
+        <v>835</v>
+      </c>
+      <c r="F143" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" t="s">
+        <v>19</v>
+      </c>
+      <c r="H143" t="s">
+        <v>38</v>
+      </c>
+      <c r="I143" t="s">
+        <v>21</v>
+      </c>
+      <c r="J143" t="s">
+        <v>46</v>
+      </c>
+      <c r="K143" t="s">
+        <v>23</v>
+      </c>
+      <c r="L143" t="s">
+        <v>836</v>
+      </c>
+      <c r="M143" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>838</v>
+      </c>
+      <c r="B144" t="s">
+        <v>839</v>
+      </c>
+      <c r="C144" t="s">
+        <v>28</v>
+      </c>
+      <c r="D144" t="s">
+        <v>840</v>
+      </c>
+      <c r="E144" t="s">
+        <v>841</v>
+      </c>
+      <c r="F144" t="s">
+        <v>18</v>
+      </c>
+      <c r="G144" t="s">
+        <v>19</v>
+      </c>
+      <c r="H144" t="s">
+        <v>59</v>
+      </c>
+      <c r="I144" t="s">
+        <v>21</v>
+      </c>
+      <c r="J144" t="s">
+        <v>294</v>
+      </c>
+      <c r="K144" t="s">
+        <v>23</v>
+      </c>
+      <c r="L144" t="s">
+        <v>842</v>
+      </c>
+      <c r="M144" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>844</v>
+      </c>
+      <c r="B145" t="s">
+        <v>845</v>
+      </c>
+      <c r="C145" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" t="s">
+        <v>846</v>
+      </c>
+      <c r="E145" t="s">
+        <v>841</v>
+      </c>
+      <c r="F145" t="s">
+        <v>18</v>
+      </c>
+      <c r="G145" t="s">
+        <v>19</v>
+      </c>
+      <c r="H145" t="s">
+        <v>139</v>
+      </c>
+      <c r="I145" t="s">
+        <v>21</v>
+      </c>
+      <c r="J145" t="s">
+        <v>344</v>
+      </c>
+      <c r="K145" t="s">
+        <v>23</v>
+      </c>
+      <c r="L145" t="s">
+        <v>847</v>
+      </c>
+      <c r="M145" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>849</v>
+      </c>
+      <c r="B146" t="s">
+        <v>850</v>
+      </c>
+      <c r="C146" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146" t="s">
+        <v>851</v>
+      </c>
+      <c r="E146" t="s">
+        <v>841</v>
+      </c>
+      <c r="F146" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146" t="s">
+        <v>139</v>
+      </c>
+      <c r="I146" t="s">
+        <v>21</v>
+      </c>
+      <c r="J146" t="s">
+        <v>46</v>
+      </c>
+      <c r="K146" t="s">
+        <v>23</v>
+      </c>
+      <c r="L146" t="s">
+        <v>852</v>
+      </c>
+      <c r="M146" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>854</v>
+      </c>
+      <c r="B147" t="s">
+        <v>855</v>
+      </c>
+      <c r="C147" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" t="s">
+        <v>856</v>
+      </c>
+      <c r="E147" t="s">
+        <v>841</v>
+      </c>
+      <c r="F147" t="s">
+        <v>18</v>
+      </c>
+      <c r="G147" t="s">
+        <v>19</v>
+      </c>
+      <c r="H147" t="s">
+        <v>38</v>
+      </c>
+      <c r="I147" t="s">
+        <v>21</v>
+      </c>
+      <c r="J147" t="s">
+        <v>857</v>
+      </c>
+      <c r="K147" t="s">
+        <v>23</v>
+      </c>
+      <c r="L147" t="s">
+        <v>858</v>
+      </c>
+      <c r="M147" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>860</v>
+      </c>
+      <c r="B148" t="s">
+        <v>861</v>
+      </c>
+      <c r="C148" t="s">
+        <v>28</v>
+      </c>
+      <c r="D148" t="s">
+        <v>862</v>
+      </c>
+      <c r="E148" t="s">
+        <v>841</v>
+      </c>
+      <c r="F148" t="s">
+        <v>18</v>
+      </c>
+      <c r="G148" t="s">
+        <v>19</v>
+      </c>
+      <c r="H148" t="s">
+        <v>20</v>
+      </c>
+      <c r="I148" t="s">
+        <v>21</v>
+      </c>
+      <c r="J148" t="s">
+        <v>46</v>
+      </c>
+      <c r="K148" t="s">
+        <v>23</v>
+      </c>
+      <c r="L148" t="s">
+        <v>863</v>
+      </c>
+      <c r="M148" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>865</v>
+      </c>
+      <c r="B149" t="s">
+        <v>866</v>
+      </c>
+      <c r="C149" t="s">
+        <v>28</v>
+      </c>
+      <c r="D149" t="s">
+        <v>867</v>
+      </c>
+      <c r="E149" t="s">
+        <v>841</v>
+      </c>
+      <c r="F149" t="s">
+        <v>18</v>
+      </c>
+      <c r="G149" t="s">
+        <v>19</v>
+      </c>
+      <c r="H149" t="s">
+        <v>38</v>
+      </c>
+      <c r="I149" t="s">
+        <v>21</v>
+      </c>
+      <c r="J149" t="s">
+        <v>684</v>
+      </c>
+      <c r="K149" t="s">
+        <v>23</v>
+      </c>
+      <c r="L149" t="s">
+        <v>868</v>
+      </c>
+      <c r="M149" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>870</v>
+      </c>
+      <c r="B150" t="s">
+        <v>871</v>
+      </c>
+      <c r="C150" t="s">
+        <v>299</v>
+      </c>
+      <c r="D150" t="s">
+        <v>872</v>
+      </c>
+      <c r="E150" t="s">
+        <v>841</v>
+      </c>
+      <c r="F150" t="s">
+        <v>18</v>
+      </c>
+      <c r="G150" t="s">
+        <v>19</v>
+      </c>
+      <c r="H150" t="s">
+        <v>38</v>
+      </c>
+      <c r="I150" t="s">
+        <v>873</v>
+      </c>
+      <c r="J150" t="s">
+        <v>46</v>
+      </c>
+      <c r="K150" t="s">
+        <v>23</v>
+      </c>
+      <c r="L150" t="s">
+        <v>874</v>
+      </c>
+      <c r="M150" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>876</v>
+      </c>
+      <c r="B151" t="s">
+        <v>877</v>
+      </c>
+      <c r="C151" t="s">
+        <v>79</v>
+      </c>
+      <c r="D151" t="s">
+        <v>878</v>
+      </c>
+      <c r="E151" t="s">
+        <v>841</v>
+      </c>
+      <c r="F151" t="s">
+        <v>18</v>
+      </c>
+      <c r="G151" t="s">
+        <v>19</v>
+      </c>
+      <c r="H151" t="s">
+        <v>73</v>
+      </c>
+      <c r="I151" t="s">
+        <v>21</v>
+      </c>
+      <c r="J151" t="s">
+        <v>338</v>
+      </c>
+      <c r="K151" t="s">
+        <v>23</v>
+      </c>
+      <c r="L151" t="s">
+        <v>879</v>
+      </c>
+      <c r="M151" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>881</v>
+      </c>
+      <c r="B152" t="s">
+        <v>882</v>
+      </c>
+      <c r="C152" t="s">
+        <v>28</v>
+      </c>
+      <c r="D152" t="s">
+        <v>883</v>
+      </c>
+      <c r="E152" t="s">
+        <v>841</v>
+      </c>
+      <c r="F152" t="s">
+        <v>18</v>
+      </c>
+      <c r="G152" t="s">
+        <v>19</v>
+      </c>
+      <c r="H152" t="s">
+        <v>46</v>
+      </c>
+      <c r="I152" t="s">
+        <v>98</v>
+      </c>
+      <c r="J152" t="s">
+        <v>884</v>
+      </c>
+      <c r="K152" t="s">
+        <v>23</v>
+      </c>
+      <c r="L152" t="s">
+        <v>885</v>
+      </c>
+      <c r="M152" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>887</v>
+      </c>
+      <c r="B153" t="s">
+        <v>888</v>
+      </c>
+      <c r="C153" t="s">
+        <v>28</v>
+      </c>
+      <c r="D153" t="s">
+        <v>889</v>
+      </c>
+      <c r="E153" t="s">
+        <v>890</v>
+      </c>
+      <c r="F153" t="s">
+        <v>18</v>
+      </c>
+      <c r="G153" t="s">
+        <v>19</v>
+      </c>
+      <c r="H153" t="s">
+        <v>92</v>
+      </c>
+      <c r="I153" t="s">
+        <v>21</v>
+      </c>
+      <c r="J153" t="s">
+        <v>46</v>
+      </c>
+      <c r="K153" t="s">
+        <v>23</v>
+      </c>
+      <c r="L153" t="s">
+        <v>891</v>
+      </c>
+      <c r="M153" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>893</v>
+      </c>
+      <c r="B154" t="s">
+        <v>894</v>
+      </c>
+      <c r="C154" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" t="s">
+        <v>895</v>
+      </c>
+      <c r="E154" t="s">
+        <v>890</v>
+      </c>
+      <c r="F154" t="s">
+        <v>18</v>
+      </c>
+      <c r="G154" t="s">
+        <v>19</v>
+      </c>
+      <c r="H154" t="s">
+        <v>896</v>
+      </c>
+      <c r="I154" t="s">
+        <v>21</v>
+      </c>
+      <c r="J154" t="s">
+        <v>897</v>
+      </c>
+      <c r="K154" t="s">
+        <v>23</v>
+      </c>
+      <c r="L154" t="s">
+        <v>898</v>
+      </c>
+      <c r="M154" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>900</v>
+      </c>
+      <c r="B155" t="s">
+        <v>901</v>
+      </c>
+      <c r="C155" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" t="s">
+        <v>902</v>
+      </c>
+      <c r="E155" t="s">
+        <v>890</v>
+      </c>
+      <c r="F155" t="s">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>19</v>
+      </c>
+      <c r="H155" t="s">
+        <v>38</v>
+      </c>
+      <c r="I155" t="s">
+        <v>21</v>
+      </c>
+      <c r="J155" t="s">
+        <v>344</v>
+      </c>
+      <c r="K155" t="s">
+        <v>23</v>
+      </c>
+      <c r="L155" t="s">
+        <v>903</v>
+      </c>
+      <c r="M155" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>905</v>
+      </c>
+      <c r="B156" t="s">
+        <v>906</v>
+      </c>
+      <c r="C156" t="s">
+        <v>79</v>
+      </c>
+      <c r="D156" t="s">
+        <v>907</v>
+      </c>
+      <c r="E156" t="s">
+        <v>890</v>
+      </c>
+      <c r="F156" t="s">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" t="s">
+        <v>38</v>
+      </c>
+      <c r="I156" t="s">
+        <v>21</v>
+      </c>
+      <c r="J156" t="s">
+        <v>46</v>
+      </c>
+      <c r="K156" t="s">
+        <v>23</v>
+      </c>
+      <c r="L156" t="s">
+        <v>908</v>
+      </c>
+      <c r="M156" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>910</v>
+      </c>
+      <c r="B157" t="s">
+        <v>911</v>
+      </c>
+      <c r="C157" t="s">
+        <v>28</v>
+      </c>
+      <c r="D157" t="s">
+        <v>912</v>
+      </c>
+      <c r="E157" t="s">
+        <v>890</v>
+      </c>
+      <c r="F157" t="s">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>19</v>
+      </c>
+      <c r="H157" t="s">
+        <v>38</v>
+      </c>
+      <c r="I157" t="s">
+        <v>21</v>
+      </c>
+      <c r="J157" t="s">
+        <v>344</v>
+      </c>
+      <c r="K157" t="s">
+        <v>23</v>
+      </c>
+      <c r="L157" t="s">
+        <v>913</v>
+      </c>
+      <c r="M157" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>915</v>
+      </c>
+      <c r="B158" t="s">
+        <v>916</v>
+      </c>
+      <c r="C158" t="s">
+        <v>258</v>
+      </c>
+      <c r="D158" t="s">
+        <v>917</v>
+      </c>
+      <c r="E158" t="s">
+        <v>890</v>
+      </c>
+      <c r="F158" t="s">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" t="s">
+        <v>38</v>
+      </c>
+      <c r="I158" t="s">
+        <v>260</v>
+      </c>
+      <c r="J158" t="s">
+        <v>918</v>
+      </c>
+      <c r="K158" t="s">
+        <v>23</v>
+      </c>
+      <c r="L158" t="s">
+        <v>919</v>
+      </c>
+      <c r="M158" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>921</v>
+      </c>
+      <c r="B159" t="s">
+        <v>922</v>
+      </c>
+      <c r="C159" t="s">
+        <v>79</v>
+      </c>
+      <c r="D159" t="s">
+        <v>923</v>
+      </c>
+      <c r="E159" t="s">
+        <v>890</v>
+      </c>
+      <c r="F159" t="s">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>19</v>
+      </c>
+      <c r="H159" t="s">
+        <v>38</v>
+      </c>
+      <c r="I159" t="s">
+        <v>21</v>
+      </c>
+      <c r="J159" t="s">
+        <v>684</v>
+      </c>
+      <c r="K159" t="s">
+        <v>23</v>
+      </c>
+      <c r="L159" t="s">
+        <v>924</v>
+      </c>
+      <c r="M159" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>926</v>
+      </c>
+      <c r="B160" t="s">
+        <v>927</v>
+      </c>
+      <c r="C160" t="s">
+        <v>71</v>
+      </c>
+      <c r="D160" t="s">
+        <v>928</v>
+      </c>
+      <c r="E160" t="s">
+        <v>890</v>
+      </c>
+      <c r="F160" t="s">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>19</v>
+      </c>
+      <c r="H160" t="s">
+        <v>929</v>
+      </c>
+      <c r="I160" t="s">
+        <v>21</v>
+      </c>
+      <c r="J160" t="s">
+        <v>930</v>
+      </c>
+      <c r="K160" t="s">
+        <v>23</v>
+      </c>
+      <c r="L160" t="s">
+        <v>931</v>
+      </c>
+      <c r="M160" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>933</v>
+      </c>
+      <c r="B161" t="s">
+        <v>934</v>
+      </c>
+      <c r="C161" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161" t="s">
+        <v>935</v>
+      </c>
+      <c r="E161" t="s">
+        <v>936</v>
+      </c>
+      <c r="F161" t="s">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>19</v>
+      </c>
+      <c r="H161" t="s">
+        <v>38</v>
+      </c>
+      <c r="I161" t="s">
+        <v>21</v>
+      </c>
+      <c r="J161" t="s">
+        <v>294</v>
+      </c>
+      <c r="K161" t="s">
+        <v>23</v>
+      </c>
+      <c r="L161" t="s">
+        <v>937</v>
+      </c>
+      <c r="M161" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>939</v>
+      </c>
+      <c r="B162" t="s">
+        <v>940</v>
+      </c>
+      <c r="C162" t="s">
+        <v>28</v>
+      </c>
+      <c r="D162" t="s">
+        <v>941</v>
+      </c>
+      <c r="E162" t="s">
+        <v>936</v>
+      </c>
+      <c r="F162" t="s">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" t="s">
+        <v>38</v>
+      </c>
+      <c r="I162" t="s">
+        <v>21</v>
+      </c>
+      <c r="J162" t="s">
+        <v>684</v>
+      </c>
+      <c r="K162" t="s">
+        <v>23</v>
+      </c>
+      <c r="L162" t="s">
+        <v>942</v>
+      </c>
+      <c r="M162" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>944</v>
+      </c>
+      <c r="B163" t="s">
+        <v>945</v>
+      </c>
+      <c r="C163" t="s">
+        <v>28</v>
+      </c>
+      <c r="D163" t="s">
+        <v>946</v>
+      </c>
+      <c r="E163" t="s">
+        <v>936</v>
+      </c>
+      <c r="F163" t="s">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>19</v>
+      </c>
+      <c r="H163" t="s">
+        <v>30</v>
+      </c>
+      <c r="I163" t="s">
+        <v>21</v>
+      </c>
+      <c r="J163" t="s">
+        <v>485</v>
+      </c>
+      <c r="K163" t="s">
+        <v>23</v>
+      </c>
+      <c r="L163" t="s">
+        <v>947</v>
+      </c>
+      <c r="M163" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>949</v>
+      </c>
+      <c r="B164" t="s">
+        <v>950</v>
+      </c>
+      <c r="C164" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" t="s">
+        <v>951</v>
+      </c>
+      <c r="E164" t="s">
+        <v>936</v>
+      </c>
+      <c r="F164" t="s">
+        <v>18</v>
+      </c>
+      <c r="G164" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164" t="s">
+        <v>46</v>
+      </c>
+      <c r="I164" t="s">
+        <v>98</v>
+      </c>
+      <c r="J164" t="s">
+        <v>46</v>
+      </c>
+      <c r="K164" t="s">
+        <v>23</v>
+      </c>
+      <c r="L164" t="s">
+        <v>952</v>
+      </c>
+      <c r="M164" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>954</v>
+      </c>
+      <c r="B165" t="s">
+        <v>955</v>
+      </c>
+      <c r="C165" t="s">
+        <v>195</v>
+      </c>
+      <c r="D165" t="s">
+        <v>956</v>
+      </c>
+      <c r="E165" t="s">
+        <v>936</v>
+      </c>
+      <c r="F165" t="s">
+        <v>18</v>
+      </c>
+      <c r="G165" t="s">
+        <v>19</v>
+      </c>
+      <c r="H165" t="s">
+        <v>38</v>
+      </c>
+      <c r="I165" t="s">
+        <v>21</v>
+      </c>
+      <c r="J165" t="s">
+        <v>957</v>
+      </c>
+      <c r="K165" t="s">
+        <v>23</v>
+      </c>
+      <c r="L165" t="s">
+        <v>958</v>
+      </c>
+      <c r="M165" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>960</v>
+      </c>
+      <c r="B166" t="s">
+        <v>961</v>
+      </c>
+      <c r="C166" t="s">
+        <v>195</v>
+      </c>
+      <c r="D166" t="s">
+        <v>962</v>
+      </c>
+      <c r="E166" t="s">
+        <v>936</v>
+      </c>
+      <c r="F166" t="s">
+        <v>18</v>
+      </c>
+      <c r="G166" t="s">
+        <v>19</v>
+      </c>
+      <c r="H166" t="s">
+        <v>46</v>
+      </c>
+      <c r="I166" t="s">
+        <v>98</v>
+      </c>
+      <c r="J166" t="s">
+        <v>46</v>
+      </c>
+      <c r="K166" t="s">
+        <v>23</v>
+      </c>
+      <c r="L166" t="s">
+        <v>963</v>
+      </c>
+      <c r="M166" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>965</v>
+      </c>
+      <c r="B167" t="s">
+        <v>966</v>
+      </c>
+      <c r="C167" t="s">
+        <v>803</v>
+      </c>
+      <c r="D167" t="s">
+        <v>967</v>
+      </c>
+      <c r="E167" t="s">
+        <v>936</v>
+      </c>
+      <c r="F167" t="s">
+        <v>18</v>
+      </c>
+      <c r="G167" t="s">
+        <v>19</v>
+      </c>
+      <c r="H167" t="s">
+        <v>38</v>
+      </c>
+      <c r="I167" t="s">
+        <v>21</v>
+      </c>
+      <c r="J167" t="s">
+        <v>46</v>
+      </c>
+      <c r="K167" t="s">
+        <v>23</v>
+      </c>
+      <c r="L167" t="s">
+        <v>968</v>
+      </c>
+      <c r="M167" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>970</v>
+      </c>
+      <c r="B168" t="s">
+        <v>971</v>
+      </c>
+      <c r="C168" t="s">
+        <v>28</v>
+      </c>
+      <c r="D168" t="s">
+        <v>972</v>
+      </c>
+      <c r="E168" t="s">
+        <v>936</v>
+      </c>
+      <c r="F168" t="s">
+        <v>18</v>
+      </c>
+      <c r="G168" t="s">
+        <v>19</v>
+      </c>
+      <c r="H168" t="s">
+        <v>38</v>
+      </c>
+      <c r="I168" t="s">
+        <v>21</v>
+      </c>
+      <c r="J168" t="s">
+        <v>973</v>
+      </c>
+      <c r="K168" t="s">
+        <v>23</v>
+      </c>
+      <c r="L168" t="s">
+        <v>974</v>
+      </c>
+      <c r="M168" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>976</v>
+      </c>
+      <c r="B169" t="s">
+        <v>977</v>
+      </c>
+      <c r="C169" t="s">
+        <v>28</v>
+      </c>
+      <c r="D169" t="s">
+        <v>978</v>
+      </c>
+      <c r="E169" t="s">
+        <v>936</v>
+      </c>
+      <c r="F169" t="s">
+        <v>18</v>
+      </c>
+      <c r="G169" t="s">
+        <v>19</v>
+      </c>
+      <c r="H169" t="s">
+        <v>92</v>
+      </c>
+      <c r="I169" t="s">
+        <v>21</v>
+      </c>
+      <c r="J169" t="s">
+        <v>684</v>
+      </c>
+      <c r="K169" t="s">
+        <v>23</v>
+      </c>
+      <c r="L169" t="s">
+        <v>979</v>
+      </c>
+      <c r="M169" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>981</v>
+      </c>
+      <c r="B170" t="s">
+        <v>982</v>
+      </c>
+      <c r="C170" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" t="s">
+        <v>983</v>
+      </c>
+      <c r="E170" t="s">
+        <v>936</v>
+      </c>
+      <c r="F170" t="s">
+        <v>18</v>
+      </c>
+      <c r="G170" t="s">
+        <v>19</v>
+      </c>
+      <c r="H170" t="s">
+        <v>984</v>
+      </c>
+      <c r="I170" t="s">
+        <v>21</v>
+      </c>
+      <c r="J170" t="s">
+        <v>344</v>
+      </c>
+      <c r="K170" t="s">
+        <v>23</v>
+      </c>
+      <c r="L170" t="s">
+        <v>985</v>
+      </c>
+      <c r="M170" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>987</v>
+      </c>
+      <c r="B171" t="s">
+        <v>988</v>
+      </c>
+      <c r="C171" t="s">
+        <v>299</v>
+      </c>
+      <c r="D171" t="s">
+        <v>989</v>
+      </c>
+      <c r="E171" t="s">
+        <v>936</v>
+      </c>
+      <c r="F171" t="s">
+        <v>18</v>
+      </c>
+      <c r="G171" t="s">
+        <v>19</v>
+      </c>
+      <c r="H171" t="s">
+        <v>38</v>
+      </c>
+      <c r="I171" t="s">
+        <v>990</v>
+      </c>
+      <c r="J171" t="s">
+        <v>991</v>
+      </c>
+      <c r="K171" t="s">
+        <v>23</v>
+      </c>
+      <c r="L171" t="s">
+        <v>992</v>
+      </c>
+      <c r="M171" t="s">
+        <v>993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/Canada/ON.xlsx
+++ b/Sajjad data/by_country_and_state/Canada/ON.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3367" uniqueCount="1469">
   <si>
     <t>Business Name</t>
   </si>
@@ -2993,6 +2993,1431 @@
   </si>
   <si>
     <t>2026-10-26T10:40:33.488Z</t>
+  </si>
+  <si>
+    <t>Blair Carolyn Dr</t>
+  </si>
+  <si>
+    <t>+1 519-624-6809</t>
+  </si>
+  <si>
+    <t>87 Grand Ave S, Cambridge, ON N1S 2L7, Canada</t>
+  </si>
+  <si>
+    <t>Cambridge</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Blair+Carolyn+Dr/data=!4m7!3m6!1s0x882c77b3b49f3d61:0xa483d95b94ab56c7!8m2!3d43.3543529!4d-80.3172669!16s%2Fg%2F1hc13gghh!19sChIJYT2ftLN3LIgRx1arlFvZg6Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:21:58.292Z</t>
+  </si>
+  <si>
+    <t>Chow Moon W Dr</t>
+  </si>
+  <si>
+    <t>+1 519-651-1250</t>
+  </si>
+  <si>
+    <t>100 Jamieson Pkwy #12, Cambridge, ON N3C 4B3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chow+Moon+W+Dr/data=!4m7!3m6!1s0x882b88f8018130e9:0x9aad59fdb17c489e!8m2!3d43.4172425!4d-80.3088356!16s%2Fg%2F1vmr1__m!19sChIJ6TCBAfiIK4gRnkh8sf1ZrZo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:22:20.018Z</t>
+  </si>
+  <si>
+    <t>Dr Jeffrey G Matyas</t>
+  </si>
+  <si>
+    <t>+1 519-621-0370</t>
+  </si>
+  <si>
+    <t>6 George St N, Cambridge, ON N1S 2M7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Jeffrey+G+Matyas/data=!4m7!3m6!1s0x882c77b4f92f527b:0x94f7967e819ebc44!8m2!3d43.358483!4d-80.3188929!16s%2Fg%2F1wnbynfp!19sChIJe1Iv-bR3LIgRRLyegX6W95Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:23:24.674Z</t>
+  </si>
+  <si>
+    <t>Hartwig Angelica Dr</t>
+  </si>
+  <si>
+    <t>+1 519-620-1555</t>
+  </si>
+  <si>
+    <t>685 Myers Rd, Cambridge, ON N1R 5S2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hartwig+Angelica+Dr/data=!4m7!3m6!1s0x882c778762e70c19:0xff8742285c87db01!8m2!3d43.3446529!4d-80.2778816!16s%2Fg%2F1tk6wk2h!19sChIJGQznYod3LIgRAduHXChCh_8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:23:26.600Z</t>
+  </si>
+  <si>
+    <t>Days Road Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 613-389-0039</t>
+  </si>
+  <si>
+    <t>499 Days Rd, Kingston, ON K7M 3R6, Canada</t>
+  </si>
+  <si>
+    <t>Kingston</t>
+  </si>
+  <si>
+    <t>Monday7:30 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Days+Road+Dental+Clinic/data=!4m7!3m6!1s0x4cd2acfa8d059031:0xcfb916d5d7217ba1!8m2!3d44.2358982!4d-76.5713085!16s%2Fg%2F1tdd09cf!19sChIJMZAFjfqs0kwRoXsh19UWuc8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:24:21.612Z</t>
+  </si>
+  <si>
+    <t>William Ho DDS</t>
+  </si>
+  <si>
+    <t>+1 613-634-8188</t>
+  </si>
+  <si>
+    <t>728 Arlington Park Pl, Kingston, ON K7M 8H9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/William+Ho+DDS/data=!4m7!3m6!1s0x4cd2ac539fb38c39:0x2700b4cfb4eab206!8m2!3d44.2496221!4d-76.5727252!16s%2Fg%2F11b5wl3ts5!19sChIJOYyzn1Os0kwRBrLqtM-0ACc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:24:23.635Z</t>
+  </si>
+  <si>
+    <t>Dr. Sitarski's Dental Office</t>
+  </si>
+  <si>
+    <t>+1 613-544-3217</t>
+  </si>
+  <si>
+    <t>dental clinic</t>
+  </si>
+  <si>
+    <t>375 Select Dr, Kingston, ON K7M 8R1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sitarski%27s+Dental+Office/data=!4m7!3m6!1s0x4cd2abcbf6bd729d:0x303709d111ee58b8!8m2!3d44.2560986!4d-76.5552213!16s%2Fg%2F11vzcbgnvv!19sChIJnXK99sur0kwRuFjuEdEJNzA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:24:25.576Z</t>
+  </si>
+  <si>
+    <t>Suenaga Shawn Dr</t>
+  </si>
+  <si>
+    <t>+1 613-549-4537</t>
+  </si>
+  <si>
+    <t>105 Sutherland Dr, Kingston, ON K7K 5V6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Suenaga+Shawn+Dr/data=!4m7!3m6!1s0x4cd2abd7f4ffffff:0x23470cc127723859!8m2!3d44.2690731!4d-76.4798688!16s%2Fg%2F1td4txnr!19sChIJ____9Ner0kwRWThyJ8EMRyM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:24:27.629Z</t>
+  </si>
+  <si>
+    <t>Doctor Roy Chan</t>
+  </si>
+  <si>
+    <t>+1 613-766-7645</t>
+  </si>
+  <si>
+    <t>813 Blackburn Mews, Kingston, ON K7P 2N6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Doctor+Roy+Chan/data=!4m7!3m6!1s0x4cd2ac5251b0efb1:0x72e07f6ae5189cdc!8m2!3d44.2516439!4d-76.5714408!16s%2Fg%2F11bbrmcybl!19sChIJse-wUVKs0kwR3JwY5Wp_4HI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:24:29.598Z</t>
+  </si>
+  <si>
+    <t>MacDonald Paul Dr</t>
+  </si>
+  <si>
+    <t>+1 613-384-0090</t>
+  </si>
+  <si>
+    <t>Pediatric dentist</t>
+  </si>
+  <si>
+    <t>817 Bayridge Dr #202, Kingston, ON K7P 1T5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MacDonald+Paul+Dr/data=!4m7!3m6!1s0x4cd2ada50f6345dd:0x135d40934b244e57!8m2!3d44.2522762!4d-76.5893578!16s%2Fg%2F1vlqpv79!19sChIJ3UVjD6Wt0kwRV04kS5NAXRM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:25:40.050Z</t>
+  </si>
+  <si>
+    <t>Reed Brian Dr</t>
+  </si>
+  <si>
+    <t>+1 613-544-2881</t>
+  </si>
+  <si>
+    <t>STANLEY _BRUCE BUILDING, 275 Queen St, Kingston, ON K7K 3T1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Reed+Brian+Dr/data=!4m7!3m6!1s0x4cd2abaa069875a1:0x9a64798083e7f8b1!8m2!3d44.2339251!4d-76.490907!16s%2Fg%2F1wyc3zcv!19sChIJoXWYBqqr0kwRsfjng4B5ZJo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:25:49.511Z</t>
+  </si>
+  <si>
+    <t>Hammond Christopher Dr</t>
+  </si>
+  <si>
+    <t>+1 613-384-5756</t>
+  </si>
+  <si>
+    <t>621 Norris Ct, Kingston, ON K7P 2R9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hammond+Christopher+Dr/data=!4m7!3m6!1s0x4cd2ac351834064f:0xac3cce5a698d7002!8m2!3d44.2628402!4d-76.56707!16s%2Fg%2F1tcy8j5f!19sChIJTwY0GDWs0kwRAnCNaVrOPKw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:26:32.139Z</t>
+  </si>
+  <si>
+    <t>Atlantis Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 519-265-7202</t>
+  </si>
+  <si>
+    <t>55 Wyndham St N, Guelph, ON N1H 7T8, Canada</t>
+  </si>
+  <si>
+    <t>Guelph</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Atlantis+Dental+Centre/data=!4m7!3m6!1s0x882b9ac2001bb053:0xac602436807d44d6!8m2!3d43.5462246!4d-80.2474825!16s%2Fg%2F1wb8vb4l!19sChIJU7AbAMKaK4gR1kR9gDYkYKw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:28:22.198Z</t>
+  </si>
+  <si>
+    <t>Woolwich Dental Group</t>
+  </si>
+  <si>
+    <t>+1 519-824-8830</t>
+  </si>
+  <si>
+    <t>271 Woolwich St, Guelph, ON N1H 3V8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Woolwich+Dental+Group/data=!4m7!3m6!1s0x882b9a94e46aca83:0xeeea768894702d7e!8m2!3d43.5497014!4d-80.2559904!16s%2Fg%2F1tdg_yd3!19sChIJg8pq5JSaK4gRfi1wlIh26u4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:28:24.082Z</t>
+  </si>
+  <si>
+    <t>SmileLine Dentistry</t>
+  </si>
+  <si>
+    <t>+1 519-265-2659</t>
+  </si>
+  <si>
+    <t>300 Willow Rd Ste 101, Guelph, ON N1H 6R6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SmileLine+Dentistry/data=!4m7!3m6!1s0x882b910ae29d4aff:0x3aee6f789e3db404!8m2!3d43.5397473!4d-80.2786051!16s%2Fg%2F11h5njfdhy!19sChIJ_0qd4gqRK4gRBLQ9nnhv7jo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:28:25.954Z</t>
+  </si>
+  <si>
+    <t>Sun Ying Dr</t>
+  </si>
+  <si>
+    <t>+1 519-824-8250</t>
+  </si>
+  <si>
+    <t>7 Riverview Dr, Guelph, ON N1E 3R6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sun+Ying+Dr/data=!4m7!3m6!1s0x882b9a8f61edc969:0x6fd5713b270105a9!8m2!3d43.5605165!4d-80.2655153!16s%2Fg%2F1tff87d4!19sChIJacntYY-aK4gRqQUBJztx1W8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:28:57.512Z</t>
+  </si>
+  <si>
+    <t>Minett C P Dr</t>
+  </si>
+  <si>
+    <t>+1 519-836-7681</t>
+  </si>
+  <si>
+    <t>51 Yarmouth St, Guelph, ON N1H 7R4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Minett+C+P+Dr/data=!4m7!3m6!1s0x882b9aea9a68ab9f:0xac3c3f59639e5edf!8m2!3d43.5471923!4d-80.252359!16s%2Fg%2F1tf87qry!19sChIJn6tomuqaK4gR316eY1k_PKw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:29:43.634Z</t>
+  </si>
+  <si>
+    <t>Raco Albert P Dr</t>
+  </si>
+  <si>
+    <t>+1 519-763-5766</t>
+  </si>
+  <si>
+    <t>1027 Gordon St, Guelph, ON N1G 4X1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Raco+Albert+P+Dr/data=!4m7!3m6!1s0x882b84ca771333b3:0x3c441b626f3dfade!8m2!3d43.5204281!4d-80.2114604!16s%2Fg%2F1tdx9bbm!19sChIJszMTd8qEK4gR3vo9b2IbRDw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:30:15.433Z</t>
+  </si>
+  <si>
+    <t>Danielli Robert Dr</t>
+  </si>
+  <si>
+    <t>+1 519-766-0190</t>
+  </si>
+  <si>
+    <t>319 Speedvale Ave E, Guelph, ON N1E 1N4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Danielli+Robert+Dr/data=!4m7!3m6!1s0x882b9a8a1479dcd5:0xf2c60aff1234170d!8m2!3d43.5651498!4d-80.2583966!16s%2Fg%2F1tdl25zd!19sChIJ1dx5FIqaK4gRDRc0Ev8KxvI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:30:17.340Z</t>
+  </si>
+  <si>
+    <t>Sovereign Dental</t>
+  </si>
+  <si>
+    <t>+1 807-344-4746</t>
+  </si>
+  <si>
+    <t>911 Fort William Rd #3, Thunder Bay, ON P7B 3A6, Canada</t>
+  </si>
+  <si>
+    <t>Thunder Bay</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sovereign+Dental/data=!4m7!3m6!1s0x4d5921f98e299115:0x7c2e5a51007e7674!8m2!3d48.4042517!4d-89.2396491!16s%2Fg%2F11g6vfqx5z!19sChIJFZEpjvkhWU0RdHZ-AFFaLnw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:20.552Z</t>
+  </si>
+  <si>
+    <t>Dr. Alisa Santiago</t>
+  </si>
+  <si>
+    <t>+1 807-622-2026</t>
+  </si>
+  <si>
+    <t>136 Edward St S, Thunder Bay, ON P7E 2G6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alisa+Santiago/data=!4m7!3m6!1s0x4d591febd710aaf9:0xd33352f842acd490!8m2!3d48.3826522!4d-89.2782368!16s%2Fg%2F11mtfq939c!19sChIJ-aoQ1-sfWU0RkNSsQvhSM9M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:22.378Z</t>
+  </si>
+  <si>
+    <t>Waterfront Family Dental</t>
+  </si>
+  <si>
+    <t>+1 807-345-3665</t>
+  </si>
+  <si>
+    <t>167 Cumberland St N, Thunder Bay, ON P7A 4M6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Waterfront+Family+Dental/data=!4m7!3m6!1s0x4d5923084e33dfbb:0x50a1b548d2279834!8m2!3d48.4400223!4d-89.2140298!16s%2Fg%2F11q40yyjrz!19sChIJu98zTggjWU0RNJgn0ki1oVA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:24.140Z</t>
+  </si>
+  <si>
+    <t>Sovereign Dental Kids</t>
+  </si>
+  <si>
+    <t>+1 807-628-1028</t>
+  </si>
+  <si>
+    <t>1101 Arthur St W #3, Thunder Bay, ON P7E 5S2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sovereign+Dental+Kids/data=!4m7!3m6!1s0x4d591fd0418c9fe7:0x3b75205a0fe7a7f1!8m2!3d48.3823137!4d-89.3082085!16s%2Fg%2F11w4c3nwkv!19sChIJ55-MQdAfWU0R8afnD1ogdTs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:26.056Z</t>
+  </si>
+  <si>
+    <t>Young D Health Facility Ltd</t>
+  </si>
+  <si>
+    <t>+1 807-345-5252</t>
+  </si>
+  <si>
+    <t>Fitness center</t>
+  </si>
+  <si>
+    <t>536 River St, Thunder Bay, ON P7A 3S2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Young+D+Health+Facility+Ltd/data=!4m7!3m6!1s0x4d5923da7b8c07c1:0x3ee325e89fc22ea4!8m2!3d48.4469509!4d-89.228873!16s%2Fg%2F1tg2d3v3!19sChIJwQeMe9ojWU0RpC7Cn-gl4z4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:27.933Z</t>
+  </si>
+  <si>
+    <t>Superior Dental Hygiene Clinic</t>
+  </si>
+  <si>
+    <t>+1 807-629-2333</t>
+  </si>
+  <si>
+    <t>194 Court St N, Thunder Bay, ON P7A 4V6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Superior+Dental+Hygiene+Clinic/data=!4m7!3m6!1s0x4d592371e7eb6339:0x589f90a320f36abc!8m2!3d48.4419471!4d-89.216476!16s%2Fg%2F11j7jnx7bm!19sChIJOWPr53EjWU0RvGrzIKOQn1g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:29.707Z</t>
+  </si>
+  <si>
+    <t>Dr Molly Gareh Thunder Bay Orthodontics</t>
+  </si>
+  <si>
+    <t>+1 807-623-6301</t>
+  </si>
+  <si>
+    <t>1318 Victoria Ave E, Thunder Bay, ON P7C 1C2, Canada</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–4 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Molly+Gareh+Thunder+Bay+Orthodontics/data=!4m7!3m6!1s0x4d591f42ff6e6791:0xe7f37dba06cf478b!8m2!3d48.3839694!4d-89.2563827!16s%2Fg%2F1th5j2lb!19sChIJkWdu_0IfWU0Ri0fPBrp98-c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:31.421Z</t>
+  </si>
+  <si>
+    <t>Florindo Lori Dr</t>
+  </si>
+  <si>
+    <t>+1 807-345-7511</t>
+  </si>
+  <si>
+    <t>1064 Oliver Rd, Thunder Bay, ON P7B 7A4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Florindo+Lori+Dr/data=!4m7!3m6!1s0x4d5921b6ba3b074f:0xe98dd7ed262003f4!8m2!3d48.4213607!4d-89.2733139!16s%2Fg%2F1wn339d3!19sChIJTwc7urYhWU0R9AMgJu3Xjek?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:33.434Z</t>
+  </si>
+  <si>
+    <t>Bayview Denture Clinic</t>
+  </si>
+  <si>
+    <t>+1 807-286-0057</t>
+  </si>
+  <si>
+    <t>607 Memorial Ave, Thunder Bay, ON P7B 3Z3, Canada</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Monday9 AM–12 PM1–5 PM; Tuesday9 AM–12 PM1–5 PM; Wednesday9 AM–12 PM1–5 PM; Thursday9 AM–12 PM1–5 PM; FridayClosed; SaturdayClosed; SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bayview+Denture+Clinic/data=!4m7!3m6!1s0x4d5921aee79d6365:0xc1908f83765ebed8!8m2!3d48.4179544!4d-89.2401522!16s%2Fg%2F11b5w9h7b9!19sChIJZWOd564hWU0R2L5edoOPkME?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:35.713Z</t>
+  </si>
+  <si>
+    <t>Sworczuk Denture Clinic</t>
+  </si>
+  <si>
+    <t>+1 807-577-5177</t>
+  </si>
+  <si>
+    <t>508 Edward St N, Thunder Bay, ON P7C 4P9, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–4 PM; Tuesday9 AM–4 PM; Wednesday9 AM–4 PM; Thursday9 AM–4 PM; FridayClosed; SaturdayClosed; SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sworczuk+Denture+Clinic/data=!4m7!3m6!1s0x4d591f7e519b7279:0x99768f2ba8ae1d7!8m2!3d48.3945494!4d-89.2768966!16s%2Fg%2F1th5c6h3!19sChIJeXKbUX4fWU0R1-GKuvJolwk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:37.856Z</t>
+  </si>
+  <si>
+    <t>Sharon Lau Family Dentist Orthodontics Thunder Bay</t>
+  </si>
+  <si>
+    <t>+1 807-626-8001</t>
+  </si>
+  <si>
+    <t>995A Memorial Ave, Thunder Bay, ON P7B 4A1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sharon+Lau+Family+Dentist+Orthodontics+Thunder+Bay/data=!4m7!3m6!1s0x4d5921fafaefdce5:0x106c24e34e7f4f!8m2!3d48.4075749!4d-89.24511!16s%2Fg%2F1v46z_76!19sChIJ5dzv-vohWU0RT39O4yRsEAA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:39.694Z</t>
+  </si>
+  <si>
+    <t>Pawlicki Edward M Denture Clinic</t>
+  </si>
+  <si>
+    <t>+1 807-623-4374</t>
+  </si>
+  <si>
+    <t>1311 Victoria Ave E, Thunder Bay, ON P7C 1C3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pawlicki+Edward+M+Denture+Clinic/data=!4m7!3m6!1s0x4d591f43011db625:0x9b943b2ba623f94d!8m2!3d48.3842953!4d-89.2558529!16s%2Fg%2F1v2f04d1!19sChIJJbYdAUMfWU0RTfkjpis7lJs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:41.685Z</t>
+  </si>
+  <si>
+    <t>Dudley Clive DD Denturist</t>
+  </si>
+  <si>
+    <t>+1 807-622-3348</t>
+  </si>
+  <si>
+    <t>211 McKellar St S, Thunder Bay, ON P7E 1H6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dudley+Clive+DD+Denturist/data=!4m7!3m6!1s0x4d591f45c4f33823:0xb0fc7d6773b68429!8m2!3d48.382009!4d-89.249963!16s%2Fg%2F1xfsncxk!19sChIJIzjzxEUfWU0RKYS2c2d9_LA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:47.046Z</t>
+  </si>
+  <si>
+    <t>Peltoniemi R Dr</t>
+  </si>
+  <si>
+    <t>+1 807-345-2568</t>
+  </si>
+  <si>
+    <t>584 Red River Rd Ste 100, Thunder Bay, ON P7B 1H3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Peltoniemi+R+Dr/data=!4m7!3m6!1s0x4d59217e5b2074db:0xffae84f7f42bf9f!8m2!3d48.4395582!4d-89.237895!16s%2Fg%2F1tgk08bt!19sChIJ23QgW34hWU0Rn79Cf0_o-g8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:48.866Z</t>
+  </si>
+  <si>
+    <t>Dr. Peter O. Jacobson Dentist</t>
+  </si>
+  <si>
+    <t>+1 807-622-0486</t>
+  </si>
+  <si>
+    <t>400 Balmoral St, Thunder Bay, ON P7C 5G8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Peter+O.+Jacobson+Dentist/data=!4m7!3m6!1s0x4d591f5d8fa8484d:0x4c2c5fc0b278d646!8m2!3d48.3900176!4d-89.2576842!16s%2Fg%2F1tdfhb3m!19sChIJTUioj10fWU0RRtZ4ssBfLEw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:31:50.837Z</t>
+  </si>
+  <si>
+    <t>Dental Hygiene Smiles</t>
+  </si>
+  <si>
+    <t>+1 807-577-6453</t>
+  </si>
+  <si>
+    <t>307 Euclid Ave Ste 4, Thunder Bay, ON P7E 6G6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Hygiene+Smiles/data=!4m7!3m6!1s0x4d591f45234530c7:0x43c3b7d6165e107!8m2!3d48.3804329!4d-89.291393!16s%2Fg%2F11b6yqnxb0!19sChIJxzBFI0UfWU0RB-FlYX07PAQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:10.156Z</t>
+  </si>
+  <si>
+    <t>Thunder Bay Oral Surgery</t>
+  </si>
+  <si>
+    <t>+1 807-345-6637</t>
+  </si>
+  <si>
+    <t>Oral and maxillofacial surgeon</t>
+  </si>
+  <si>
+    <t>326 Red River Rd, Thunder Bay, ON P7B 1B1, Canada</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Monday8:15 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Thunder+Bay+Oral+Surgery/data=!4m7!3m6!1s0x4d5923e3ae18b513:0x7409ba2be06d78cb!8m2!3d48.4377529!4d-89.2246295!16s%2Fg%2F11lw8042jj!19sChIJE7UYruMjWU0Ry3ht4Cu6CXQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:12.370Z</t>
+  </si>
+  <si>
+    <t>Nystrom Bryan Dr</t>
+  </si>
+  <si>
+    <t>+1 807-344-7741</t>
+  </si>
+  <si>
+    <t>59 Court St N, Thunder Bay, ON P7A 4T6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nystrom+Bryan+Dr/data=!4m7!3m6!1s0x4d5923cb606ab7b7:0x3744d7e88867a67a!8m2!3d48.4374272!4d-89.2199739!16s%2Fg%2F1w4f7r6l!19sChIJt7dqYMsjWU0ReqZniOjXRDc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:14.216Z</t>
+  </si>
+  <si>
+    <t>M. Nystrom Denture Clinic</t>
+  </si>
+  <si>
+    <t>+1 807-473-4336</t>
+  </si>
+  <si>
+    <t>101 N Syndicate Ave, Thunder Bay, ON P7C 3V4, Canada</t>
+  </si>
+  <si>
+    <t>Monday9:30 AM–4:30 PM; Tuesday9:30 AM–4:30 PM; Wednesday9:30 AM–2:30 PM; Thursday9:30 AM–2:30 PM; Friday9:30 AM–2:30 PM; SaturdayClosed; SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/M.+Nystrom+Denture+Clinic/data=!4m7!3m6!1s0x4d591f85dc8158a5:0x8c0350c4e30f8194!8m2!3d48.3845996!4d-89.2480876!16s%2Fg%2F11yq1p72k7!19sChIJpViB3IUfWU0RlIEP48RQA4w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:16.021Z</t>
+  </si>
+  <si>
+    <t>Chow Elaine Dr - Wright Edward Dr</t>
+  </si>
+  <si>
+    <t>+1 807-623-2662</t>
+  </si>
+  <si>
+    <t>1265 Arthur St E, Thunder Bay, ON P7E 5H7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chow+Elaine+Dr+-+Wright+Edward+Dr/data=!4m7!3m6!1s0x4d591f4151eb54d1:0xaa871cbcba6f0de9!8m2!3d48.3811409!4d-89.254783!16s%2Fg%2F113f09n3k!19sChIJ0VTrUUEfWU0R6Q1vurwch6o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:17.997Z</t>
+  </si>
+  <si>
+    <t>Dr Laura Mercer</t>
+  </si>
+  <si>
+    <t>+1 807-623-2900</t>
+  </si>
+  <si>
+    <t>116 May St N, Thunder Bay, ON P7C 3P1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Laura+Mercer/data=!4m7!3m6!1s0x4d591f5bc090e62d:0xc158b64d3b57798e!8m2!3d48.3848!4d-89.24519!16s%2Fg%2F11rfq6d0c9!19sChIJLeaQwFsfWU0RjnlXO022WME?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:19.890Z</t>
+  </si>
+  <si>
+    <t>Fedori Donna Dr</t>
+  </si>
+  <si>
+    <t>+1 807-623-6369</t>
+  </si>
+  <si>
+    <t>124 Frederica St E, Thunder Bay, ON P7E 3V5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fedori+Donna+Dr/data=!4m7!3m6!1s0x4d591f06444996b9:0x9e585c04cae6265a!8m2!3d48.3648945!4d-89.2771071!16s%2Fg%2F1v6wnzds!19sChIJuZZJRAYfWU0RWibmygRcWJ4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:24.283Z</t>
+  </si>
+  <si>
+    <t>Jack McGuire Centre</t>
+  </si>
+  <si>
+    <t>+1 807-473-4858</t>
+  </si>
+  <si>
+    <t>2000 Otway St, Thunder Bay, ON P7K 1H5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jack+McGuire+Centre/data=!4m7!3m6!1s0x4d58e051d17b91bb:0x972c62340d549429!8m2!3d48.3641347!4d-89.3558545!16s%2Fg%2F1td4jrq7!19sChIJu5F70VHgWE0RKZRUDTRiLJc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:45.390Z</t>
+  </si>
+  <si>
+    <t>All Smiles Dental Hygiene</t>
+  </si>
+  <si>
+    <t>+1 807-346-5005</t>
+  </si>
+  <si>
+    <t>843 Red River Rd, Thunder Bay, ON P7B 1K3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/All+Smiles+Dental+Hygiene/data=!4m7!3m6!1s0x4d5921703d0fbcc9:0xf9a7be82145ff925!8m2!3d48.4455666!4d-89.2484446!16s%2Fg%2F11b5wdgbqt!19sChIJybwPPXAhWU0RJflfFIK-p_k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:47.365Z</t>
+  </si>
+  <si>
+    <t>Dr. Ronald Palinka</t>
+  </si>
+  <si>
+    <t>+1 807-345-1144</t>
+  </si>
+  <si>
+    <t>44 Algoma St S, Thunder Bay, ON P7B 3A9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ronald+Palinka/data=!4m7!3m6!1s0x4d59222d578baaa7:0xcba5adf6a3d0045b!8m2!3d48.4356224!4d-89.2257774!16s%2Fg%2F1thmkmw_!19sChIJp6qLVy0iWU0RWwTQo_atpcs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:49.007Z</t>
+  </si>
+  <si>
+    <t>Harbourview Health Facility</t>
+  </si>
+  <si>
+    <t>+1 807-623-1949</t>
+  </si>
+  <si>
+    <t>1535 Victoria Ave E, Thunder Bay, ON P7C 1C6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Harbourview+Health+Facility/data=!4m7!3m6!1s0x4d591f4283e72adf:0x3233692fd7bebb10!8m2!3d48.3843991!4d-89.2586015!16s%2Fg%2F11b5wjyq79!19sChIJ3yrng0IfWU0RELu-1y9pMzI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:32:54.735Z</t>
+  </si>
+  <si>
+    <t>University Dental &amp; Hygiene Clinic</t>
+  </si>
+  <si>
+    <t>+1 226-338-4016</t>
+  </si>
+  <si>
+    <t>Unit #7, 258 King St N, Waterloo, ON N2J 2Y9, Canada</t>
+  </si>
+  <si>
+    <t>Waterloo</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/University+Dental+%26+Hygiene+Clinic/data=!4m7!3m6!1s0x882bf3f451d62b95:0xbc7cbde90fe9621a!8m2!3d43.4771214!4d-80.5248316!16s%2Fg%2F11c56rjqyq!19sChIJlSvWUfTzK4gRGmLpD-m9fLw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:34:23.845Z</t>
+  </si>
+  <si>
+    <t>Bridge West Dental Office</t>
+  </si>
+  <si>
+    <t>+1 519-880-9480</t>
+  </si>
+  <si>
+    <t>373 Bridge St W Unit 9B, Waterloo, ON N2K 3M6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bridge+West+Dental+Office/data=!4m7!3m6!1s0x882bf3a0ceabbf77:0xc9b11cdbcb8691d0!8m2!3d43.4953651!4d-80.5009918!16s%2Fg%2F1tcysgj6!19sChIJd7-rzqDzK4gR0JGGy9scsck?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:34:32.167Z</t>
+  </si>
+  <si>
+    <t>Dr. Azadeh Rastikerdar-Prosthodontics and Dental implants</t>
+  </si>
+  <si>
+    <t>+1 519-800-4969</t>
+  </si>
+  <si>
+    <t>235 The Boardwalk, Waterloo, ON N2J 3Z4, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–4 PM; Tuesday8 AM–4 PM; Wednesday8 AM–4 PM; Thursday8 AM–4 PM; Friday8 AM–4 PM; SaturdayClosed; SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Azadeh+Rastikerdar-Prosthodontics+and+Dental+implants/data=!4m7!3m6!1s0x882bf77b06d1421f:0x69a3c8713c966aba!8m2!3d43.4358545!4d-80.5614658!16s%2Fg%2F11tt84g4nc!19sChIJH0LRBnv3K4gRumqWPHHIo2k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:35:54.722Z</t>
+  </si>
+  <si>
+    <t>AlphaMed Rx HealthMed Pharmacy &amp; Walk-in Clinic</t>
+  </si>
+  <si>
+    <t>+1 519-746-9999</t>
+  </si>
+  <si>
+    <t>Pharmacy</t>
+  </si>
+  <si>
+    <t>460 Albert St, Waterloo, ON N2L 3V4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/AlphaMed+Rx+HealthMed+Pharmacy+%26+Walk-in+Clinic/data=!4m7!3m6!1s0x882bf3c9eece2231:0xcc467979c5290f61!8m2!3d43.4857436!4d-80.5402634!16s%2Fg%2F11hyl5rkcc!19sChIJMSLO7snzK4gRYQ8pxXl5Rsw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:36:49.125Z</t>
+  </si>
+  <si>
+    <t>Brantford Dental Hygiene and Denture Clinic with Cliff Muzylowsky Denturist</t>
+  </si>
+  <si>
+    <t>+1 519-304-8484</t>
+  </si>
+  <si>
+    <t>84 Charing Cross St Unit 7, Brantford, ON N3R 2H6, Canada</t>
+  </si>
+  <si>
+    <t>Brantford</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brantford+Dental+Hygiene+and+Denture+Clinic+with+Cliff+Muzylowsky+Denturist/data=!4m7!3m6!1s0x882c6545a6bb475f:0x24f533760ded4133!8m2!3d43.1598209!4d-80.267211!16s%2Fg%2F11gxhmfv8w!19sChIJX0e7pkVlLIgRM0HtDXYz9SQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:16.465Z</t>
+  </si>
+  <si>
+    <t>Sokoloski Peter Dr</t>
+  </si>
+  <si>
+    <t>+1 519-753-1500</t>
+  </si>
+  <si>
+    <t>206 Brant Ave, Brantford, ON N3T 3H9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sokoloski+Peter+Dr/data=!4m7!3m6!1s0x882c6605a4a886dd:0xaec8a881ecb8ec1d!8m2!3d43.1461392!4d-80.2759651!16s%2Fg%2F1tl8lbrk!19sChIJ3YaopAVmLIgRHey47IGoyK4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:18.377Z</t>
+  </si>
+  <si>
+    <t>Endre Nemeth, D.D.S.</t>
+  </si>
+  <si>
+    <t>+1 519-758-8989</t>
+  </si>
+  <si>
+    <t>525 Park Rd N, Brantford, ON N3R 7K8, Canada</t>
+  </si>
+  <si>
+    <t>Monday9:30 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Endre+Nemeth,+D.D.S./data=!4m7!3m6!1s0x882c65a0ae01ec15:0x5b73fed0905784b6!8m2!3d43.1823265!4d-80.2495297!16s%2Fg%2F1tfcjd9c!19sChIJFewBrqBlLIgRtoRXkND-c1s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:20.283Z</t>
+  </si>
+  <si>
+    <t>Colborne Place Dental Office</t>
+  </si>
+  <si>
+    <t>+1 519-751-2533</t>
+  </si>
+  <si>
+    <t>603 Colborne St, Brantford, ON N3S 7S8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Colborne+Place+Dental+Office/data=!4m7!3m6!1s0x882c6679961e269f:0x5c5207209f8752f7!8m2!3d43.1388524!4d-80.2410481!16s%2Fg%2F11b5wp9w4d!19sChIJnyYelnlmLIgR91KHnyAHUlw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:22.347Z</t>
+  </si>
+  <si>
+    <t>Chan George Dr</t>
+  </si>
+  <si>
+    <t>+1 519-759-8840</t>
+  </si>
+  <si>
+    <t>353 St Paul Ave, Brantford, ON N3R 4N3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chan+George+Dr/data=!4m7!3m6!1s0x882c65f83f336243:0xd03360305171e499!8m2!3d43.1551907!4d-80.2747632!16s%2Fg%2F1tg4m086!19sChIJQ2IzP_hlLIgRmeRxUTBgM9A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:24.250Z</t>
+  </si>
+  <si>
+    <t>Dr. V. Duchnay and Associate</t>
+  </si>
+  <si>
+    <t>+1 519-756-0270</t>
+  </si>
+  <si>
+    <t>143 Charing Cross St, Brantford, ON N3R 3Z9, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+V.+Duchnay+and+Associate/data=!4m7!3m6!1s0x882c65eef5c819e9:0x6e617c6c5eef2ad8!8m2!3d43.1586707!4d-80.2626151!16s%2Fg%2F1tflyjh7!19sChIJ6RnI9e5lLIgR2CrvXmx8YW4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:26.165Z</t>
+  </si>
+  <si>
+    <t>Kurtz Heidi Dr</t>
+  </si>
+  <si>
+    <t>+1 519-759-1551</t>
+  </si>
+  <si>
+    <t>421 St Paul Ave, Brantford, ON N3R 4N8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kurtz+Heidi+Dr/data=!4m7!3m6!1s0x882c6603fe999217:0x9ad9e70185705fc1!8m2!3d43.1589233!4d-80.2719494!16s%2Fg%2F1tl1p2c8!19sChIJF5KZ_gNmLIgRwV9whQHn2Zo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:27.870Z</t>
+  </si>
+  <si>
+    <t>122 Charing Cross Family Dentistry</t>
+  </si>
+  <si>
+    <t>+1 519-756-5333</t>
+  </si>
+  <si>
+    <t>122 Charing Cross St, Brantford, ON N3R 2J1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/122+Charing+Cross+Family+Dentistry/data=!4m7!3m6!1s0x882c65ee150c4a27:0x488d9591170571e!8m2!3d43.1588744!4d-80.2642741!16s%2Fg%2F1tf7h9c2!19sChIJJ0oMFe5lLIgRHldwEVnZiAQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:38:46.578Z</t>
+  </si>
+  <si>
+    <t>Syrowy O M Dr</t>
+  </si>
+  <si>
+    <t>+1 519-753-8541</t>
+  </si>
+  <si>
+    <t>221 Brant Ave, Brantford, ON N3T 3J3, Canada</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Syrowy+O+M+Dr/data=!4m7!3m6!1s0x882c65fffc18a7bd:0x6ce956370bd37cb4!8m2!3d43.1470865!4d-80.2761731!16s%2Fg%2F1thvhk_r!19sChIJvacY_P9lLIgRtHzTCzdW6Ww?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:39:00.379Z</t>
+  </si>
+  <si>
+    <t>Iarocci Dr J</t>
+  </si>
+  <si>
+    <t>+1 519-752-9661</t>
+  </si>
+  <si>
+    <t>383 St Paul Ave, Brantford, ON N3R 4N5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Iarocci+Dr+J/data=!4m7!3m6!1s0x882c65f777daed8b:0xd45e702b6ad2f6be!8m2!3d43.1567959!4d-80.2738279!16s%2Fg%2F1tfr11r6!19sChIJi-3ad_dlLIgRvvbSaitwXtQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:39:18.358Z</t>
+  </si>
+  <si>
+    <t>B.A. Selinger</t>
+  </si>
+  <si>
+    <t>+1 519-753-8031</t>
+  </si>
+  <si>
+    <t>2 Dundee St, Brantford, ON N3R 4M1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/B.A.+Selinger/data=!4m7!3m6!1s0x882c65b2d6fc3b85:0xff250bc1e3252403!8m2!3d43.1568!4d-80.2730731!16s%2Fg%2F11t49qgc76!19sChIJhTv81rJlLIgRAyQl48ELJf8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:39:20.299Z</t>
+  </si>
+  <si>
+    <t>Ghobrial Sam Dr</t>
+  </si>
+  <si>
+    <t>+1 519-759-1121</t>
+  </si>
+  <si>
+    <t>300 King George Rd, Brantford, ON N3R 5L8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ghobrial+Sam+Dr/data=!4m7!3m6!1s0x882c6f7f13428929:0xfee3c0d5446e8908!8m2!3d43.1830008!4d-80.2803975!16s%2Fg%2F1vjdqq3t!19sChIJKYlCE39vLIgRCIluRNXA4_4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:39:22.444Z</t>
+  </si>
+  <si>
+    <t>PUCCI spaw, Cosmetic K9 Teeth Cleaning &amp; Reiki</t>
+  </si>
+  <si>
+    <t>+1 519-802-1207</t>
+  </si>
+  <si>
+    <t>Pet groomer</t>
+  </si>
+  <si>
+    <t>75 Dalhousie St Unit 101, Brantford, ON N3S 0E2, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/PUCCI+spaw,+Cosmetic+K9+Teeth+Cleaning+%26+Reiki/data=!4m7!3m6!1s0x882c6548b87190b5:0xf70b740e93d63c91!8m2!3d43.1391871!4d-80.2654572!16s%2Fg%2F11fpl7knhj!19sChIJtZBxuEhlLIgRkTzWkw50C_c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:39:24.185Z</t>
+  </si>
+  <si>
+    <t>Dentistry on Nelson</t>
+  </si>
+  <si>
+    <t>+1 519-759-6364</t>
+  </si>
+  <si>
+    <t>51 Nelson St, Brantford, ON N3T 2M7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentistry+on+Nelson/data=!4m7!3m6!1s0x882c6700469b0725:0x1bd1dcb79c6dd5bf!8m2!3d43.1419291!4d-80.2641474!16s%2Fg%2F11w9nm_bky!19sChIJJQebRgBnLIgRv9VtnLfc0Rs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:39:26.158Z</t>
+  </si>
+  <si>
+    <t>TempOral Services</t>
+  </si>
+  <si>
+    <t>+1 226-450-2500</t>
+  </si>
+  <si>
+    <t>18 Edinburgh Ct, Brantford, ON N3R 6A6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/TempOral+Services/data=!4m7!3m6!1s0x882c65a02db95553:0x6c0994330ed613eb!8m2!3d43.1811294!4d-80.2538655!16s%2Fg%2F11hczzfh1m!19sChIJU1W5LaBlLIgR6xPWDjOUCWw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:39:54.116Z</t>
+  </si>
+  <si>
+    <t>Maple Ridge Dental Office</t>
+  </si>
+  <si>
+    <t>+1 905-831-3603</t>
+  </si>
+  <si>
+    <t>2074 Liverpool Rd, Pickering, ON L1X 1E2, Canada</t>
+  </si>
+  <si>
+    <t>Pickering</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Maple+Ridge+Dental+Office/data=!4m7!3m6!1s0x405736ee3a959e1d:0x42dd6b1bf42b5c4f!8m2!3d43.8472889!4d-79.096247!16s%2Fg%2F1vy7hknf!19sChIJHZ6VOu42V0ART1wr9Btr3UI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:40:41.601Z</t>
+  </si>
+  <si>
+    <t>Dr Stephen Carmona Glendale Dental Office</t>
+  </si>
+  <si>
+    <t>+1 905-420-9211</t>
+  </si>
+  <si>
+    <t>1900 Dixie Rd, Pickering, ON L1V 6M4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Stephen+Carmona+Glendale+Dental+Office/data=!4m7!3m6!1s0x89d4df2a38d49be1:0x6c68dc63371a64ab!8m2!3d43.8419391!4d-79.1049605!16s%2Fg%2F11c564cyfw!19sChIJ4ZvUOCrf1IkRq2QaN2PcaGw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:40:59.130Z</t>
+  </si>
+  <si>
+    <t>Westney Heights</t>
+  </si>
+  <si>
+    <t>+1 905-426-8181</t>
+  </si>
+  <si>
+    <t>110 Ritchie Ave Ste 8, Ajax, ON L1S 7G5, Canada</t>
+  </si>
+  <si>
+    <t>Ajax</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Westney+Heights/data=!4m7!3m6!1s0x89d4dfeaf2ab03e9:0xdf756b575daa0062!8m2!3d43.8548174!4d-79.0406613!16s%2Fg%2F1tgnn1pr!19sChIJ6QOr8urf1IkRYgCqXVdrdd8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:41:17.143Z</t>
+  </si>
+  <si>
+    <t>Pickering Market Dental Office</t>
+  </si>
+  <si>
+    <t>+1 905-420-8990</t>
+  </si>
+  <si>
+    <t>820 Kingston Rd Unit 6, Pickering, ON L1V 1A8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pickering+Market+Dental+Office/data=!4m7!3m6!1s0x89d4dedc6080ac95:0xf4e23b3c49baf14f!8m2!3d43.8228646!4d-79.1114336!16s%2Fg%2F11b5wlmkj8!19sChIJlayAYNze1IkRT_G6STw74vQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:41:49.846Z</t>
+  </si>
+  <si>
+    <t>Dr. Jonathan D. Lazaro Dentistry Professional Corporations</t>
+  </si>
+  <si>
+    <t>+1 905-428-2122</t>
+  </si>
+  <si>
+    <t>536 Kingston Rd W, Ajax, ON L1T 3A3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jonathan+D.+Lazaro+Dentistry+Professional+Corporations/data=!4m7!3m6!1s0x89d4df97edcb79fb:0x8e65796e31c1754c!8m2!3d43.8554135!4d-79.0522988!16s%2Fg%2F1tk9rrmc!19sChIJ-3nL7Zff1IkRTHXBMW55ZY4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:42:10.876Z</t>
+  </si>
+  <si>
+    <t>Clover ridge dental</t>
+  </si>
+  <si>
+    <t>+1 905-427-3600</t>
+  </si>
+  <si>
+    <t>955 Westney Rd S, Ajax, ON L1S 3K7, Canada</t>
+  </si>
+  <si>
+    <t>Monday1:30–9 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clover+ridge+dental/data=!4m7!3m6!1s0x89d4e08086296b77:0xafc73deca1955466!8m2!3d43.8314196!4d-79.0160782!16s%2Fg%2F1tknlfcx!19sChIJd2sphoDg1IkRZlSVoew9x68?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:42:26.030Z</t>
+  </si>
+  <si>
+    <t>Dr Chin Sue-Lynn</t>
+  </si>
+  <si>
+    <t>+1 905-831-2707</t>
+  </si>
+  <si>
+    <t>1099 Kingston Rd, Pickering, ON L1V 1B5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Chin+Sue-Lynn/data=!4m7!3m6!1s0x89d4dec59cd45513:0x8af7f2e243f88ea8!8m2!3d43.8276706!4d-79.0968335!16s%2Fg%2F11b6_nzfjf!19sChIJE1XUnMXe1IkRqI74Q-Ly94o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:42:44.253Z</t>
+  </si>
+  <si>
+    <t>Dr. Medhat Guirguis</t>
+  </si>
+  <si>
+    <t>+1 905-837-0001</t>
+  </si>
+  <si>
+    <t>650 Kingston Rd, Pickering, ON L1V 1A6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Medhat+Guirguis/data=!4m7!3m6!1s0x89d4d94f16fd2043:0x9a33195ef5ab2c27!8m2!3d43.8178775!4d-79.1189989!16s%2Fg%2F11b66jxgf2!19sChIJQyD9Fk_Z1IkRJyyr9V4ZM5o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:42:47.703Z</t>
+  </si>
+  <si>
+    <t>Dr. Paul Countryman</t>
+  </si>
+  <si>
+    <t>+1 905-831-7555</t>
+  </si>
+  <si>
+    <t>1794 Liverpool Rd, Pickering, ON L1V 1V9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Paul+Countryman/data=!4m7!3m6!1s0x89d4dedc2badcbcf:0x9d65557ed0fa343c!8m2!3d43.8344056!4d-79.0907253!16s%2Fg%2F11b6d6mlf2!19sChIJz8utK9ze1IkRPDT60H5VZZ0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:42:49.546Z</t>
+  </si>
+  <si>
+    <t>Dr.William Nevill Dentistry Prof. Corp</t>
+  </si>
+  <si>
+    <t>+1 905-683-6920</t>
+  </si>
+  <si>
+    <t>250 Bayly St W, Ajax, ON L1S 3V4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.William+Nevill+Dentistry+Prof.+Corp/data=!4m7!3m6!1s0x89d4dfd063c3fa2f:0x6b851b15ba83cb2a!8m2!3d43.8435928!4d-79.0280663!16s%2Fg%2F11b5wlb1b2!19sChIJL_rDY9Df1IkRKsuDuhUbhWs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:42:51.575Z</t>
+  </si>
+  <si>
+    <t>Howard I Holmes DDS</t>
+  </si>
+  <si>
+    <t>+1 905-837-1500</t>
+  </si>
+  <si>
+    <t>944 Merritton Rd, Pickering, ON L1V 1B1, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Howard+I+Holmes+DDS/data=!4m7!3m6!1s0x89d4decbc0ea3ea9:0xf5b63538bba6236e!8m2!3d43.825152!4d-79.1054697!16s%2Fg%2F11b5wrrsz8!19sChIJqT7qwMve1IkRbiOmuzg1tvU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:42:53.298Z</t>
+  </si>
+  <si>
+    <t>Stamford Green Dental</t>
+  </si>
+  <si>
+    <t>+1 905-356-1623</t>
+  </si>
+  <si>
+    <t>3626 Portage Rd, Niagara Falls, ON L2J 2K7, Canada</t>
+  </si>
+  <si>
+    <t>Niagara Falls</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stamford+Green+Dental/data=!4m7!3m6!1s0x89d35cae748ac2c7:0x16ed9a89de6b0b76!8m2!3d43.120496!4d-79.099013!16s%2Fg%2F11b6__493g!19sChIJx8KKdK5c04kRdgtr3oma7RY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:44:41.393Z</t>
+  </si>
+  <si>
+    <t>Kim Brian Dr</t>
+  </si>
+  <si>
+    <t>+1 905-357-4777</t>
+  </si>
+  <si>
+    <t>3770 Montrose Rd, Niagara Falls, ON L2H 3K3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kim+Brian+Dr/data=!4m7!3m6!1s0x89d344b33d3f2167:0xae158e6ab31a7d78!8m2!3d43.1174179!4d-79.121795!16s%2Fg%2F1wc326wg!19sChIJZyE_PbNE04kReH0as2qOFa4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:44:43.105Z</t>
+  </si>
+  <si>
+    <t>The Smile Centre/Dr Ron McClure</t>
+  </si>
+  <si>
+    <t>+1 905-356-2444</t>
+  </si>
+  <si>
+    <t>4030 Montrose Rd, Niagara Falls, ON L2H 3E1, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+Smile+Centre%2FDr+Ron+McClure/data=!4m7!3m6!1s0x89d344b162a9419b:0xaec8e16aaa77831b!8m2!3d43.1142054!4d-79.1231507!16s%2Fg%2F1tkjm5cf!19sChIJm0GpYrFE04kRG4N3qmrhyK4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:44:54.099Z</t>
+  </si>
+  <si>
+    <t>Niagara Aesthetic Dental Lab Inc</t>
+  </si>
+  <si>
+    <t>+1 289-296-3884</t>
+  </si>
+  <si>
+    <t>5610 Fraser St, Niagara Falls, ON L2E 3C9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Niagara+Aesthetic+Dental+Lab+Inc/data=!4m7!3m6!1s0x89d34377e0e6c415:0x52404d1a3c39acec!8m2!3d43.1120477!4d-79.0888256!16s%2Fg%2F1hc2dp4gx!19sChIJFcTm4HdD04kR7Kw5PBpNQFI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:45:16.551Z</t>
+  </si>
+  <si>
+    <t>Down 2 Earth Mobile Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 705-312-7327</t>
+  </si>
+  <si>
+    <t>Peterborough, ON K9H 3R3, Canada</t>
+  </si>
+  <si>
+    <t>Peterborough</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Down+2+Earth+Mobile+Dental+Clinic/data=!4m7!3m6!1s0x89d58d6b41d427d7:0xb86fc843880352c5!8m2!3d44.3047061!4d-78.3199606!16s%2Fg%2F11kbzf241w!19sChIJ1yfUQWuN1YkRxVIDiEPIb7g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:47:59.620Z</t>
+  </si>
+  <si>
+    <t>Chris McArthur, DDS</t>
+  </si>
+  <si>
+    <t>+1 705-743-6140</t>
+  </si>
+  <si>
+    <t>201 Aylmer St N, Peterborough, ON K9J 3K3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chris+McArthur,+DDS/data=!4m7!3m6!1s0x89d58cef3f9006a5:0xbef5911902702da8!8m2!3d44.2995378!4d-78.3231257!16s%2Fg%2F1tdn52fj!19sChIJpQaQP--M1YkRqC1wAhmR9b4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:48:02.663Z</t>
+  </si>
+  <si>
+    <t>Dean Dental Lab</t>
+  </si>
+  <si>
+    <t>+1 705-876-9471</t>
+  </si>
+  <si>
+    <t>880 Armour Rd, Peterborough, ON K9H 2A6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dean+Dental+Lab/data=!4m7!3m6!1s0x89d58ca7302b9f2f:0x59583f2389eb43d5!8m2!3d44.3232742!4d-78.3092529!16s%2Fg%2F1v9t_x8n!19sChIJL58rMKeM1YkR1UPriSM_WFk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:48:15.270Z</t>
+  </si>
+  <si>
+    <t>Wang Austin Dr</t>
+  </si>
+  <si>
+    <t>+1 705-743-5862</t>
+  </si>
+  <si>
+    <t>335 Reid St, Peterborough, ON K9H 4G3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wang+Austin+Dr/data=!4m7!3m6!1s0x89d58cf2020dbb3d:0x2a814a796ea2b2e8!8m2!3d44.3035622!4d-78.3280613!16s%2Fg%2F1ts307vk!19sChIJPbsNAvKM1YkR6LKibnlKgSo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:48:16.953Z</t>
+  </si>
+  <si>
+    <t>Peterborough Dental Laboratory</t>
+  </si>
+  <si>
+    <t>+1 705-743-3191</t>
+  </si>
+  <si>
+    <t>112 Hunter St E, Peterborough, ON K9H 1G6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Peterborough+Dental+Laboratory/data=!4m7!3m6!1s0x89d58cb8a3ae1fd7:0x452ddc3f0a653814!8m2!3d44.3068638!4d-78.3089412!16s%2Fg%2F1tdvl4xm!19sChIJ1x-uo7iM1YkRFDhlCj_cLUU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:48:18.684Z</t>
+  </si>
+  <si>
+    <t>Sordi Cameron Dr</t>
+  </si>
+  <si>
+    <t>+1 705-743-4881</t>
+  </si>
+  <si>
+    <t>191 Sherbrooke St, Peterborough, ON K9J 2N2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sordi+Cameron+Dr/data=!4m7!3m6!1s0x89d58ce92c07451f:0x692955fce6a7d7a!8m2!3d44.300486!4d-78.3213809!16s%2Fg%2F1vrqbmjv!19sChIJH0UHLOmM1YkRen1qzl-VkgY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:48:20.670Z</t>
+  </si>
+  <si>
+    <t>Planet Kids Paediatrics</t>
+  </si>
+  <si>
+    <t>+1 705-775-0195</t>
+  </si>
+  <si>
+    <t>Pediatrician</t>
+  </si>
+  <si>
+    <t>272 Charlotte St Ste 304, Peterborough, ON K9J 2V4, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–4 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Planet+Kids+Paediatrics/data=!4m7!3m6!1s0x89d58d92c319afe9:0xc9a1b30d746b9e4e!8m2!3d44.3034784!4d-78.3251612!16s%2Fg%2F11h_cxtdx9!19sChIJ6a8Zw5KN1YkRTp5rdA2zock?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:48:51.599Z</t>
+  </si>
+  <si>
+    <t>Anderson Kenneth R Dr</t>
+  </si>
+  <si>
+    <t>+1 705-745-3049</t>
+  </si>
+  <si>
+    <t>301 Bellevue St, Peterborough, ON K9H 5E8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Anderson+Kenneth+R+Dr/data=!4m7!3m6!1s0x89d58c85a20079fb:0x982f8ee00fb03ec5!8m2!3d44.3188853!4d-78.3300999!16s%2Fg%2F1tgb8bhx!19sChIJ-3kAooWM1YkRxT6wD-COL5g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:49:17.889Z</t>
+  </si>
+  <si>
+    <t>Stunning Smiles</t>
+  </si>
+  <si>
+    <t>+1 705-808-4481</t>
+  </si>
+  <si>
+    <t>1222 Pulpit Rd, Peterborough, ON K9K 1H5, Canada</t>
+  </si>
+  <si>
+    <t>Monday5:30–9:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stunning+Smiles/data=!4m7!3m6!1s0x89d58d055b317c49:0x333b0be516c13d8e!8m2!3d44.2977575!4d-78.3584561!16s%2Fg%2F11v63v2yqh!19sChIJSXwxWwWN1YkRjj3BFuULOzM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:49:34.833Z</t>
   </si>
 </sst>
 </file>
@@ -3373,7 +4798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M259"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -10401,6 +11826,3614 @@
         <v>993</v>
       </c>
     </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>994</v>
+      </c>
+      <c r="B172" t="s">
+        <v>995</v>
+      </c>
+      <c r="C172" t="s">
+        <v>28</v>
+      </c>
+      <c r="D172" t="s">
+        <v>996</v>
+      </c>
+      <c r="E172" t="s">
+        <v>997</v>
+      </c>
+      <c r="F172" t="s">
+        <v>18</v>
+      </c>
+      <c r="G172" t="s">
+        <v>19</v>
+      </c>
+      <c r="H172" t="s">
+        <v>38</v>
+      </c>
+      <c r="I172" t="s">
+        <v>21</v>
+      </c>
+      <c r="J172" t="s">
+        <v>485</v>
+      </c>
+      <c r="K172" t="s">
+        <v>23</v>
+      </c>
+      <c r="L172" t="s">
+        <v>998</v>
+      </c>
+      <c r="M172" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C173" t="s">
+        <v>28</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E173" t="s">
+        <v>997</v>
+      </c>
+      <c r="F173" t="s">
+        <v>18</v>
+      </c>
+      <c r="G173" t="s">
+        <v>19</v>
+      </c>
+      <c r="H173" t="s">
+        <v>92</v>
+      </c>
+      <c r="I173" t="s">
+        <v>21</v>
+      </c>
+      <c r="J173" t="s">
+        <v>530</v>
+      </c>
+      <c r="K173" t="s">
+        <v>23</v>
+      </c>
+      <c r="L173" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M173" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C174" t="s">
+        <v>28</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E174" t="s">
+        <v>997</v>
+      </c>
+      <c r="F174" t="s">
+        <v>18</v>
+      </c>
+      <c r="G174" t="s">
+        <v>19</v>
+      </c>
+      <c r="H174" t="s">
+        <v>38</v>
+      </c>
+      <c r="I174" t="s">
+        <v>21</v>
+      </c>
+      <c r="J174" t="s">
+        <v>344</v>
+      </c>
+      <c r="K174" t="s">
+        <v>23</v>
+      </c>
+      <c r="L174" t="s">
+        <v>1008</v>
+      </c>
+      <c r="M174" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C175" t="s">
+        <v>28</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E175" t="s">
+        <v>997</v>
+      </c>
+      <c r="F175" t="s">
+        <v>18</v>
+      </c>
+      <c r="G175" t="s">
+        <v>19</v>
+      </c>
+      <c r="H175" t="s">
+        <v>30</v>
+      </c>
+      <c r="I175" t="s">
+        <v>21</v>
+      </c>
+      <c r="J175" t="s">
+        <v>46</v>
+      </c>
+      <c r="K175" t="s">
+        <v>23</v>
+      </c>
+      <c r="L175" t="s">
+        <v>1013</v>
+      </c>
+      <c r="M175" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C176" t="s">
+        <v>28</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F176" t="s">
+        <v>18</v>
+      </c>
+      <c r="G176" t="s">
+        <v>19</v>
+      </c>
+      <c r="H176" t="s">
+        <v>157</v>
+      </c>
+      <c r="I176" t="s">
+        <v>21</v>
+      </c>
+      <c r="J176" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K176" t="s">
+        <v>23</v>
+      </c>
+      <c r="L176" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M176" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C177" t="s">
+        <v>28</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E177" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F177" t="s">
+        <v>18</v>
+      </c>
+      <c r="G177" t="s">
+        <v>19</v>
+      </c>
+      <c r="H177" t="s">
+        <v>92</v>
+      </c>
+      <c r="I177" t="s">
+        <v>21</v>
+      </c>
+      <c r="J177" t="s">
+        <v>513</v>
+      </c>
+      <c r="K177" t="s">
+        <v>23</v>
+      </c>
+      <c r="L177" t="s">
+        <v>1025</v>
+      </c>
+      <c r="M177" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E178" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F178" t="s">
+        <v>18</v>
+      </c>
+      <c r="G178" t="s">
+        <v>19</v>
+      </c>
+      <c r="H178" t="s">
+        <v>157</v>
+      </c>
+      <c r="I178" t="s">
+        <v>21</v>
+      </c>
+      <c r="J178" t="s">
+        <v>501</v>
+      </c>
+      <c r="K178" t="s">
+        <v>23</v>
+      </c>
+      <c r="L178" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M178" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C179" t="s">
+        <v>28</v>
+      </c>
+      <c r="D179" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E179" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F179" t="s">
+        <v>18</v>
+      </c>
+      <c r="G179" t="s">
+        <v>19</v>
+      </c>
+      <c r="H179" t="s">
+        <v>38</v>
+      </c>
+      <c r="I179" t="s">
+        <v>21</v>
+      </c>
+      <c r="J179" t="s">
+        <v>46</v>
+      </c>
+      <c r="K179" t="s">
+        <v>23</v>
+      </c>
+      <c r="L179" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M179" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C180" t="s">
+        <v>28</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E180" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F180" t="s">
+        <v>18</v>
+      </c>
+      <c r="G180" t="s">
+        <v>19</v>
+      </c>
+      <c r="H180" t="s">
+        <v>20</v>
+      </c>
+      <c r="I180" t="s">
+        <v>21</v>
+      </c>
+      <c r="J180" t="s">
+        <v>338</v>
+      </c>
+      <c r="K180" t="s">
+        <v>23</v>
+      </c>
+      <c r="L180" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M180" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E181" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F181" t="s">
+        <v>18</v>
+      </c>
+      <c r="G181" t="s">
+        <v>19</v>
+      </c>
+      <c r="H181" t="s">
+        <v>823</v>
+      </c>
+      <c r="I181" t="s">
+        <v>21</v>
+      </c>
+      <c r="J181" t="s">
+        <v>46</v>
+      </c>
+      <c r="K181" t="s">
+        <v>23</v>
+      </c>
+      <c r="L181" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M181" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C182" t="s">
+        <v>28</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F182" t="s">
+        <v>18</v>
+      </c>
+      <c r="G182" t="s">
+        <v>19</v>
+      </c>
+      <c r="H182" t="s">
+        <v>38</v>
+      </c>
+      <c r="I182" t="s">
+        <v>21</v>
+      </c>
+      <c r="J182" t="s">
+        <v>46</v>
+      </c>
+      <c r="K182" t="s">
+        <v>23</v>
+      </c>
+      <c r="L182" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M182" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C183" t="s">
+        <v>28</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E183" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F183" t="s">
+        <v>18</v>
+      </c>
+      <c r="G183" t="s">
+        <v>19</v>
+      </c>
+      <c r="H183" t="s">
+        <v>38</v>
+      </c>
+      <c r="I183" t="s">
+        <v>21</v>
+      </c>
+      <c r="J183" t="s">
+        <v>46</v>
+      </c>
+      <c r="K183" t="s">
+        <v>23</v>
+      </c>
+      <c r="L183" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M183" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C184" t="s">
+        <v>15</v>
+      </c>
+      <c r="D184" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F184" t="s">
+        <v>18</v>
+      </c>
+      <c r="G184" t="s">
+        <v>19</v>
+      </c>
+      <c r="H184" t="s">
+        <v>811</v>
+      </c>
+      <c r="I184" t="s">
+        <v>21</v>
+      </c>
+      <c r="J184" t="s">
+        <v>485</v>
+      </c>
+      <c r="K184" t="s">
+        <v>23</v>
+      </c>
+      <c r="L184" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M184" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C185" t="s">
+        <v>28</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F185" t="s">
+        <v>18</v>
+      </c>
+      <c r="G185" t="s">
+        <v>19</v>
+      </c>
+      <c r="H185" t="s">
+        <v>547</v>
+      </c>
+      <c r="I185" t="s">
+        <v>21</v>
+      </c>
+      <c r="J185" t="s">
+        <v>344</v>
+      </c>
+      <c r="K185" t="s">
+        <v>23</v>
+      </c>
+      <c r="L185" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M185" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C186" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F186" t="s">
+        <v>18</v>
+      </c>
+      <c r="G186" t="s">
+        <v>19</v>
+      </c>
+      <c r="H186" t="s">
+        <v>38</v>
+      </c>
+      <c r="I186" t="s">
+        <v>21</v>
+      </c>
+      <c r="J186" t="s">
+        <v>391</v>
+      </c>
+      <c r="K186" t="s">
+        <v>23</v>
+      </c>
+      <c r="L186" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M186" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C187" t="s">
+        <v>28</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F187" t="s">
+        <v>18</v>
+      </c>
+      <c r="G187" t="s">
+        <v>19</v>
+      </c>
+      <c r="H187" t="s">
+        <v>73</v>
+      </c>
+      <c r="I187" t="s">
+        <v>21</v>
+      </c>
+      <c r="J187" t="s">
+        <v>46</v>
+      </c>
+      <c r="K187" t="s">
+        <v>23</v>
+      </c>
+      <c r="L187" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M187" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C188" t="s">
+        <v>28</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F188" t="s">
+        <v>18</v>
+      </c>
+      <c r="G188" t="s">
+        <v>19</v>
+      </c>
+      <c r="H188" t="s">
+        <v>547</v>
+      </c>
+      <c r="I188" t="s">
+        <v>21</v>
+      </c>
+      <c r="J188" t="s">
+        <v>501</v>
+      </c>
+      <c r="K188" t="s">
+        <v>23</v>
+      </c>
+      <c r="L188" t="s">
+        <v>1083</v>
+      </c>
+      <c r="M188" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C189" t="s">
+        <v>28</v>
+      </c>
+      <c r="D189" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F189" t="s">
+        <v>18</v>
+      </c>
+      <c r="G189" t="s">
+        <v>19</v>
+      </c>
+      <c r="H189" t="s">
+        <v>59</v>
+      </c>
+      <c r="I189" t="s">
+        <v>21</v>
+      </c>
+      <c r="J189" t="s">
+        <v>973</v>
+      </c>
+      <c r="K189" t="s">
+        <v>23</v>
+      </c>
+      <c r="L189" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M189" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C190" t="s">
+        <v>28</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F190" t="s">
+        <v>18</v>
+      </c>
+      <c r="G190" t="s">
+        <v>19</v>
+      </c>
+      <c r="H190" t="s">
+        <v>38</v>
+      </c>
+      <c r="I190" t="s">
+        <v>21</v>
+      </c>
+      <c r="J190" t="s">
+        <v>344</v>
+      </c>
+      <c r="K190" t="s">
+        <v>23</v>
+      </c>
+      <c r="L190" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M190" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C191" t="s">
+        <v>28</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F191" t="s">
+        <v>18</v>
+      </c>
+      <c r="G191" t="s">
+        <v>19</v>
+      </c>
+      <c r="H191" t="s">
+        <v>59</v>
+      </c>
+      <c r="I191" t="s">
+        <v>21</v>
+      </c>
+      <c r="J191" t="s">
+        <v>485</v>
+      </c>
+      <c r="K191" t="s">
+        <v>23</v>
+      </c>
+      <c r="L191" t="s">
+        <v>1099</v>
+      </c>
+      <c r="M191" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C192" t="s">
+        <v>28</v>
+      </c>
+      <c r="D192" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F192" t="s">
+        <v>18</v>
+      </c>
+      <c r="G192" t="s">
+        <v>19</v>
+      </c>
+      <c r="H192" t="s">
+        <v>38</v>
+      </c>
+      <c r="I192" t="s">
+        <v>21</v>
+      </c>
+      <c r="J192" t="s">
+        <v>294</v>
+      </c>
+      <c r="K192" t="s">
+        <v>23</v>
+      </c>
+      <c r="L192" t="s">
+        <v>1104</v>
+      </c>
+      <c r="M192" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C193" t="s">
+        <v>15</v>
+      </c>
+      <c r="D193" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F193" t="s">
+        <v>18</v>
+      </c>
+      <c r="G193" t="s">
+        <v>19</v>
+      </c>
+      <c r="H193" t="s">
+        <v>38</v>
+      </c>
+      <c r="I193" t="s">
+        <v>21</v>
+      </c>
+      <c r="J193" t="s">
+        <v>338</v>
+      </c>
+      <c r="K193" t="s">
+        <v>23</v>
+      </c>
+      <c r="L193" t="s">
+        <v>1109</v>
+      </c>
+      <c r="M193" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E194" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F194" t="s">
+        <v>18</v>
+      </c>
+      <c r="G194" t="s">
+        <v>19</v>
+      </c>
+      <c r="H194" t="s">
+        <v>38</v>
+      </c>
+      <c r="I194" t="s">
+        <v>21</v>
+      </c>
+      <c r="J194" t="s">
+        <v>485</v>
+      </c>
+      <c r="K194" t="s">
+        <v>23</v>
+      </c>
+      <c r="L194" t="s">
+        <v>1114</v>
+      </c>
+      <c r="M194" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E195" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F195" t="s">
+        <v>18</v>
+      </c>
+      <c r="G195" t="s">
+        <v>19</v>
+      </c>
+      <c r="H195" t="s">
+        <v>139</v>
+      </c>
+      <c r="I195" t="s">
+        <v>21</v>
+      </c>
+      <c r="J195" t="s">
+        <v>46</v>
+      </c>
+      <c r="K195" t="s">
+        <v>23</v>
+      </c>
+      <c r="L195" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M195" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C196" t="s">
+        <v>15</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F196" t="s">
+        <v>18</v>
+      </c>
+      <c r="G196" t="s">
+        <v>19</v>
+      </c>
+      <c r="H196" t="s">
+        <v>38</v>
+      </c>
+      <c r="I196" t="s">
+        <v>21</v>
+      </c>
+      <c r="J196" t="s">
+        <v>294</v>
+      </c>
+      <c r="K196" t="s">
+        <v>23</v>
+      </c>
+      <c r="L196" t="s">
+        <v>1125</v>
+      </c>
+      <c r="M196" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C197" t="s">
+        <v>121</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E197" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F197" t="s">
+        <v>18</v>
+      </c>
+      <c r="G197" t="s">
+        <v>19</v>
+      </c>
+      <c r="H197" t="s">
+        <v>38</v>
+      </c>
+      <c r="I197" t="s">
+        <v>21</v>
+      </c>
+      <c r="J197" t="s">
+        <v>1130</v>
+      </c>
+      <c r="K197" t="s">
+        <v>23</v>
+      </c>
+      <c r="L197" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M197" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C198" t="s">
+        <v>28</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E198" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F198" t="s">
+        <v>18</v>
+      </c>
+      <c r="G198" t="s">
+        <v>19</v>
+      </c>
+      <c r="H198" t="s">
+        <v>896</v>
+      </c>
+      <c r="I198" t="s">
+        <v>21</v>
+      </c>
+      <c r="J198" t="s">
+        <v>344</v>
+      </c>
+      <c r="K198" t="s">
+        <v>23</v>
+      </c>
+      <c r="L198" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M198" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C199" t="s">
+        <v>299</v>
+      </c>
+      <c r="D199" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E199" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F199" t="s">
+        <v>18</v>
+      </c>
+      <c r="G199" t="s">
+        <v>19</v>
+      </c>
+      <c r="H199" t="s">
+        <v>30</v>
+      </c>
+      <c r="I199" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J199" t="s">
+        <v>1142</v>
+      </c>
+      <c r="K199" t="s">
+        <v>23</v>
+      </c>
+      <c r="L199" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M199" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C200" t="s">
+        <v>299</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F200" t="s">
+        <v>18</v>
+      </c>
+      <c r="G200" t="s">
+        <v>19</v>
+      </c>
+      <c r="H200" t="s">
+        <v>547</v>
+      </c>
+      <c r="I200" t="s">
+        <v>728</v>
+      </c>
+      <c r="J200" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K200" t="s">
+        <v>23</v>
+      </c>
+      <c r="L200" t="s">
+        <v>1149</v>
+      </c>
+      <c r="M200" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C201" t="s">
+        <v>28</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E201" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F201" t="s">
+        <v>18</v>
+      </c>
+      <c r="G201" t="s">
+        <v>19</v>
+      </c>
+      <c r="H201" t="s">
+        <v>46</v>
+      </c>
+      <c r="I201" t="s">
+        <v>98</v>
+      </c>
+      <c r="J201" t="s">
+        <v>485</v>
+      </c>
+      <c r="K201" t="s">
+        <v>23</v>
+      </c>
+      <c r="L201" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M201" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C202" t="s">
+        <v>28</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E202" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F202" t="s">
+        <v>18</v>
+      </c>
+      <c r="G202" t="s">
+        <v>19</v>
+      </c>
+      <c r="H202" t="s">
+        <v>38</v>
+      </c>
+      <c r="I202" t="s">
+        <v>21</v>
+      </c>
+      <c r="J202" t="s">
+        <v>46</v>
+      </c>
+      <c r="K202" t="s">
+        <v>23</v>
+      </c>
+      <c r="L202" t="s">
+        <v>1159</v>
+      </c>
+      <c r="M202" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C203" t="s">
+        <v>299</v>
+      </c>
+      <c r="D203" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E203" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F203" t="s">
+        <v>18</v>
+      </c>
+      <c r="G203" t="s">
+        <v>19</v>
+      </c>
+      <c r="H203" t="s">
+        <v>823</v>
+      </c>
+      <c r="I203" t="s">
+        <v>690</v>
+      </c>
+      <c r="J203" t="s">
+        <v>46</v>
+      </c>
+      <c r="K203" t="s">
+        <v>23</v>
+      </c>
+      <c r="L203" t="s">
+        <v>1164</v>
+      </c>
+      <c r="M203" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C204" t="s">
+        <v>28</v>
+      </c>
+      <c r="D204" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E204" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F204" t="s">
+        <v>18</v>
+      </c>
+      <c r="G204" t="s">
+        <v>19</v>
+      </c>
+      <c r="H204" t="s">
+        <v>38</v>
+      </c>
+      <c r="I204" t="s">
+        <v>21</v>
+      </c>
+      <c r="J204" t="s">
+        <v>338</v>
+      </c>
+      <c r="K204" t="s">
+        <v>23</v>
+      </c>
+      <c r="L204" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M204" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C205" t="s">
+        <v>28</v>
+      </c>
+      <c r="D205" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E205" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F205" t="s">
+        <v>18</v>
+      </c>
+      <c r="G205" t="s">
+        <v>19</v>
+      </c>
+      <c r="H205" t="s">
+        <v>896</v>
+      </c>
+      <c r="I205" t="s">
+        <v>21</v>
+      </c>
+      <c r="J205" t="s">
+        <v>46</v>
+      </c>
+      <c r="K205" t="s">
+        <v>23</v>
+      </c>
+      <c r="L205" t="s">
+        <v>1174</v>
+      </c>
+      <c r="M205" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C206" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E206" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F206" t="s">
+        <v>18</v>
+      </c>
+      <c r="G206" t="s">
+        <v>19</v>
+      </c>
+      <c r="H206" t="s">
+        <v>38</v>
+      </c>
+      <c r="I206" t="s">
+        <v>21</v>
+      </c>
+      <c r="J206" t="s">
+        <v>485</v>
+      </c>
+      <c r="K206" t="s">
+        <v>23</v>
+      </c>
+      <c r="L206" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M206" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D207" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E207" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F207" t="s">
+        <v>18</v>
+      </c>
+      <c r="G207" t="s">
+        <v>19</v>
+      </c>
+      <c r="H207" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I207" t="s">
+        <v>21</v>
+      </c>
+      <c r="J207" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K207" t="s">
+        <v>23</v>
+      </c>
+      <c r="L207" t="s">
+        <v>1187</v>
+      </c>
+      <c r="M207" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C208" t="s">
+        <v>28</v>
+      </c>
+      <c r="D208" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E208" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F208" t="s">
+        <v>18</v>
+      </c>
+      <c r="G208" t="s">
+        <v>19</v>
+      </c>
+      <c r="H208" t="s">
+        <v>38</v>
+      </c>
+      <c r="I208" t="s">
+        <v>21</v>
+      </c>
+      <c r="J208" t="s">
+        <v>46</v>
+      </c>
+      <c r="K208" t="s">
+        <v>23</v>
+      </c>
+      <c r="L208" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M208" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C209" t="s">
+        <v>299</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E209" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F209" t="s">
+        <v>18</v>
+      </c>
+      <c r="G209" t="s">
+        <v>19</v>
+      </c>
+      <c r="H209" t="s">
+        <v>46</v>
+      </c>
+      <c r="I209" t="s">
+        <v>260</v>
+      </c>
+      <c r="J209" t="s">
+        <v>1197</v>
+      </c>
+      <c r="K209" t="s">
+        <v>23</v>
+      </c>
+      <c r="L209" t="s">
+        <v>1198</v>
+      </c>
+      <c r="M209" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C210" t="s">
+        <v>28</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E210" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F210" t="s">
+        <v>18</v>
+      </c>
+      <c r="G210" t="s">
+        <v>19</v>
+      </c>
+      <c r="H210" t="s">
+        <v>38</v>
+      </c>
+      <c r="I210" t="s">
+        <v>21</v>
+      </c>
+      <c r="J210" t="s">
+        <v>46</v>
+      </c>
+      <c r="K210" t="s">
+        <v>23</v>
+      </c>
+      <c r="L210" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M210" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C211" t="s">
+        <v>28</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E211" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F211" t="s">
+        <v>18</v>
+      </c>
+      <c r="G211" t="s">
+        <v>19</v>
+      </c>
+      <c r="H211" t="s">
+        <v>38</v>
+      </c>
+      <c r="I211" t="s">
+        <v>21</v>
+      </c>
+      <c r="J211" t="s">
+        <v>46</v>
+      </c>
+      <c r="K211" t="s">
+        <v>23</v>
+      </c>
+      <c r="L211" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M211" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C212" t="s">
+        <v>28</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E212" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F212" t="s">
+        <v>18</v>
+      </c>
+      <c r="G212" t="s">
+        <v>19</v>
+      </c>
+      <c r="H212" t="s">
+        <v>46</v>
+      </c>
+      <c r="I212" t="s">
+        <v>98</v>
+      </c>
+      <c r="J212" t="s">
+        <v>46</v>
+      </c>
+      <c r="K212" t="s">
+        <v>23</v>
+      </c>
+      <c r="L212" t="s">
+        <v>1213</v>
+      </c>
+      <c r="M212" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C213" t="s">
+        <v>28</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E213" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F213" t="s">
+        <v>18</v>
+      </c>
+      <c r="G213" t="s">
+        <v>19</v>
+      </c>
+      <c r="H213" t="s">
+        <v>46</v>
+      </c>
+      <c r="I213" t="s">
+        <v>98</v>
+      </c>
+      <c r="J213" t="s">
+        <v>897</v>
+      </c>
+      <c r="K213" t="s">
+        <v>23</v>
+      </c>
+      <c r="L213" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M213" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C214" t="s">
+        <v>28</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F214" t="s">
+        <v>18</v>
+      </c>
+      <c r="G214" t="s">
+        <v>19</v>
+      </c>
+      <c r="H214" t="s">
+        <v>46</v>
+      </c>
+      <c r="I214" t="s">
+        <v>98</v>
+      </c>
+      <c r="J214" t="s">
+        <v>46</v>
+      </c>
+      <c r="K214" t="s">
+        <v>23</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M214" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C215" t="s">
+        <v>28</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F215" t="s">
+        <v>18</v>
+      </c>
+      <c r="G215" t="s">
+        <v>19</v>
+      </c>
+      <c r="H215" t="s">
+        <v>38</v>
+      </c>
+      <c r="I215" t="s">
+        <v>21</v>
+      </c>
+      <c r="J215" t="s">
+        <v>46</v>
+      </c>
+      <c r="K215" t="s">
+        <v>23</v>
+      </c>
+      <c r="L215" t="s">
+        <v>1228</v>
+      </c>
+      <c r="M215" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C216" t="s">
+        <v>28</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F216" t="s">
+        <v>18</v>
+      </c>
+      <c r="G216" t="s">
+        <v>19</v>
+      </c>
+      <c r="H216" t="s">
+        <v>46</v>
+      </c>
+      <c r="I216" t="s">
+        <v>98</v>
+      </c>
+      <c r="J216" t="s">
+        <v>46</v>
+      </c>
+      <c r="K216" t="s">
+        <v>23</v>
+      </c>
+      <c r="L216" t="s">
+        <v>1233</v>
+      </c>
+      <c r="M216" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C217" t="s">
+        <v>28</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E217" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F217" t="s">
+        <v>18</v>
+      </c>
+      <c r="G217" t="s">
+        <v>19</v>
+      </c>
+      <c r="H217" t="s">
+        <v>547</v>
+      </c>
+      <c r="I217" t="s">
+        <v>21</v>
+      </c>
+      <c r="J217" t="s">
+        <v>391</v>
+      </c>
+      <c r="K217" t="s">
+        <v>23</v>
+      </c>
+      <c r="L217" t="s">
+        <v>1239</v>
+      </c>
+      <c r="M217" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C218" t="s">
+        <v>28</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F218" t="s">
+        <v>18</v>
+      </c>
+      <c r="G218" t="s">
+        <v>19</v>
+      </c>
+      <c r="H218" t="s">
+        <v>59</v>
+      </c>
+      <c r="I218" t="s">
+        <v>21</v>
+      </c>
+      <c r="J218" t="s">
+        <v>391</v>
+      </c>
+      <c r="K218" t="s">
+        <v>23</v>
+      </c>
+      <c r="L218" t="s">
+        <v>1244</v>
+      </c>
+      <c r="M218" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C219" t="s">
+        <v>725</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F219" t="s">
+        <v>18</v>
+      </c>
+      <c r="G219" t="s">
+        <v>19</v>
+      </c>
+      <c r="H219" t="s">
+        <v>38</v>
+      </c>
+      <c r="I219" t="s">
+        <v>260</v>
+      </c>
+      <c r="J219" t="s">
+        <v>1249</v>
+      </c>
+      <c r="K219" t="s">
+        <v>23</v>
+      </c>
+      <c r="L219" t="s">
+        <v>1250</v>
+      </c>
+      <c r="M219" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F220" t="s">
+        <v>18</v>
+      </c>
+      <c r="G220" t="s">
+        <v>19</v>
+      </c>
+      <c r="H220" t="s">
+        <v>30</v>
+      </c>
+      <c r="I220" t="s">
+        <v>21</v>
+      </c>
+      <c r="J220" t="s">
+        <v>374</v>
+      </c>
+      <c r="K220" t="s">
+        <v>23</v>
+      </c>
+      <c r="L220" t="s">
+        <v>1256</v>
+      </c>
+      <c r="M220" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C221" t="s">
+        <v>71</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F221" t="s">
+        <v>18</v>
+      </c>
+      <c r="G221" t="s">
+        <v>19</v>
+      </c>
+      <c r="H221" t="s">
+        <v>92</v>
+      </c>
+      <c r="I221" t="s">
+        <v>21</v>
+      </c>
+      <c r="J221" t="s">
+        <v>603</v>
+      </c>
+      <c r="K221" t="s">
+        <v>23</v>
+      </c>
+      <c r="L221" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M221" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C222" t="s">
+        <v>28</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E222" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F222" t="s">
+        <v>18</v>
+      </c>
+      <c r="G222" t="s">
+        <v>19</v>
+      </c>
+      <c r="H222" t="s">
+        <v>157</v>
+      </c>
+      <c r="I222" t="s">
+        <v>21</v>
+      </c>
+      <c r="J222" t="s">
+        <v>344</v>
+      </c>
+      <c r="K222" t="s">
+        <v>23</v>
+      </c>
+      <c r="L222" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M222" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C223" t="s">
+        <v>28</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F223" t="s">
+        <v>18</v>
+      </c>
+      <c r="G223" t="s">
+        <v>19</v>
+      </c>
+      <c r="H223" t="s">
+        <v>38</v>
+      </c>
+      <c r="I223" t="s">
+        <v>21</v>
+      </c>
+      <c r="J223" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K223" t="s">
+        <v>23</v>
+      </c>
+      <c r="L223" t="s">
+        <v>1273</v>
+      </c>
+      <c r="M223" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E224" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F224" t="s">
+        <v>18</v>
+      </c>
+      <c r="G224" t="s">
+        <v>19</v>
+      </c>
+      <c r="H224" t="s">
+        <v>157</v>
+      </c>
+      <c r="I224" t="s">
+        <v>21</v>
+      </c>
+      <c r="J224" t="s">
+        <v>368</v>
+      </c>
+      <c r="K224" t="s">
+        <v>23</v>
+      </c>
+      <c r="L224" t="s">
+        <v>1278</v>
+      </c>
+      <c r="M224" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C225" t="s">
+        <v>28</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F225" t="s">
+        <v>18</v>
+      </c>
+      <c r="G225" t="s">
+        <v>19</v>
+      </c>
+      <c r="H225" t="s">
+        <v>896</v>
+      </c>
+      <c r="I225" t="s">
+        <v>21</v>
+      </c>
+      <c r="J225" t="s">
+        <v>294</v>
+      </c>
+      <c r="K225" t="s">
+        <v>23</v>
+      </c>
+      <c r="L225" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M225" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C226" t="s">
+        <v>28</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F226" t="s">
+        <v>18</v>
+      </c>
+      <c r="G226" t="s">
+        <v>19</v>
+      </c>
+      <c r="H226" t="s">
+        <v>46</v>
+      </c>
+      <c r="I226" t="s">
+        <v>98</v>
+      </c>
+      <c r="J226" t="s">
+        <v>1288</v>
+      </c>
+      <c r="K226" t="s">
+        <v>23</v>
+      </c>
+      <c r="L226" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M226" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C227" t="s">
+        <v>28</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F227" t="s">
+        <v>18</v>
+      </c>
+      <c r="G227" t="s">
+        <v>19</v>
+      </c>
+      <c r="H227" t="s">
+        <v>38</v>
+      </c>
+      <c r="I227" t="s">
+        <v>21</v>
+      </c>
+      <c r="J227" t="s">
+        <v>46</v>
+      </c>
+      <c r="K227" t="s">
+        <v>23</v>
+      </c>
+      <c r="L227" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M227" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C228" t="s">
+        <v>28</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E228" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F228" t="s">
+        <v>18</v>
+      </c>
+      <c r="G228" t="s">
+        <v>19</v>
+      </c>
+      <c r="H228" t="s">
+        <v>46</v>
+      </c>
+      <c r="I228" t="s">
+        <v>98</v>
+      </c>
+      <c r="J228" t="s">
+        <v>46</v>
+      </c>
+      <c r="K228" t="s">
+        <v>23</v>
+      </c>
+      <c r="L228" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M228" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C229" t="s">
+        <v>28</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E229" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F229" t="s">
+        <v>18</v>
+      </c>
+      <c r="G229" t="s">
+        <v>19</v>
+      </c>
+      <c r="H229" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I229" t="s">
+        <v>21</v>
+      </c>
+      <c r="J229" t="s">
+        <v>46</v>
+      </c>
+      <c r="K229" t="s">
+        <v>23</v>
+      </c>
+      <c r="L229" t="s">
+        <v>1305</v>
+      </c>
+      <c r="M229" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C230" t="s">
+        <v>28</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F230" t="s">
+        <v>18</v>
+      </c>
+      <c r="G230" t="s">
+        <v>19</v>
+      </c>
+      <c r="H230" t="s">
+        <v>46</v>
+      </c>
+      <c r="I230" t="s">
+        <v>98</v>
+      </c>
+      <c r="J230" t="s">
+        <v>46</v>
+      </c>
+      <c r="K230" t="s">
+        <v>23</v>
+      </c>
+      <c r="L230" t="s">
+        <v>1310</v>
+      </c>
+      <c r="M230" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C231" t="s">
+        <v>28</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F231" t="s">
+        <v>18</v>
+      </c>
+      <c r="G231" t="s">
+        <v>19</v>
+      </c>
+      <c r="H231" t="s">
+        <v>46</v>
+      </c>
+      <c r="I231" t="s">
+        <v>98</v>
+      </c>
+      <c r="J231" t="s">
+        <v>46</v>
+      </c>
+      <c r="K231" t="s">
+        <v>23</v>
+      </c>
+      <c r="L231" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M231" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C232" t="s">
+        <v>28</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F232" t="s">
+        <v>18</v>
+      </c>
+      <c r="G232" t="s">
+        <v>19</v>
+      </c>
+      <c r="H232" t="s">
+        <v>157</v>
+      </c>
+      <c r="I232" t="s">
+        <v>21</v>
+      </c>
+      <c r="J232" t="s">
+        <v>46</v>
+      </c>
+      <c r="K232" t="s">
+        <v>23</v>
+      </c>
+      <c r="L232" t="s">
+        <v>1320</v>
+      </c>
+      <c r="M232" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C233" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F233" t="s">
+        <v>18</v>
+      </c>
+      <c r="G233" t="s">
+        <v>19</v>
+      </c>
+      <c r="H233" t="s">
+        <v>38</v>
+      </c>
+      <c r="I233" t="s">
+        <v>21</v>
+      </c>
+      <c r="J233" t="s">
+        <v>1326</v>
+      </c>
+      <c r="K233" t="s">
+        <v>23</v>
+      </c>
+      <c r="L233" t="s">
+        <v>1327</v>
+      </c>
+      <c r="M233" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C234" t="s">
+        <v>28</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E234" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F234" t="s">
+        <v>18</v>
+      </c>
+      <c r="G234" t="s">
+        <v>19</v>
+      </c>
+      <c r="H234" t="s">
+        <v>46</v>
+      </c>
+      <c r="I234" t="s">
+        <v>98</v>
+      </c>
+      <c r="J234" t="s">
+        <v>46</v>
+      </c>
+      <c r="K234" t="s">
+        <v>23</v>
+      </c>
+      <c r="L234" t="s">
+        <v>1332</v>
+      </c>
+      <c r="M234" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C235" t="s">
+        <v>15</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E235" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F235" t="s">
+        <v>18</v>
+      </c>
+      <c r="G235" t="s">
+        <v>19</v>
+      </c>
+      <c r="H235" t="s">
+        <v>46</v>
+      </c>
+      <c r="I235" t="s">
+        <v>98</v>
+      </c>
+      <c r="J235" t="s">
+        <v>501</v>
+      </c>
+      <c r="K235" t="s">
+        <v>23</v>
+      </c>
+      <c r="L235" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M235" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C236" t="s">
+        <v>15</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E236" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F236" t="s">
+        <v>18</v>
+      </c>
+      <c r="G236" t="s">
+        <v>19</v>
+      </c>
+      <c r="H236" t="s">
+        <v>73</v>
+      </c>
+      <c r="I236" t="s">
+        <v>21</v>
+      </c>
+      <c r="J236" t="s">
+        <v>930</v>
+      </c>
+      <c r="K236" t="s">
+        <v>23</v>
+      </c>
+      <c r="L236" t="s">
+        <v>1343</v>
+      </c>
+      <c r="M236" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C237" t="s">
+        <v>15</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E237" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F237" t="s">
+        <v>18</v>
+      </c>
+      <c r="G237" t="s">
+        <v>19</v>
+      </c>
+      <c r="H237" t="s">
+        <v>30</v>
+      </c>
+      <c r="I237" t="s">
+        <v>21</v>
+      </c>
+      <c r="J237" t="s">
+        <v>374</v>
+      </c>
+      <c r="K237" t="s">
+        <v>23</v>
+      </c>
+      <c r="L237" t="s">
+        <v>1348</v>
+      </c>
+      <c r="M237" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C238" t="s">
+        <v>28</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E238" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F238" t="s">
+        <v>18</v>
+      </c>
+      <c r="G238" t="s">
+        <v>19</v>
+      </c>
+      <c r="H238" t="s">
+        <v>38</v>
+      </c>
+      <c r="I238" t="s">
+        <v>21</v>
+      </c>
+      <c r="J238" t="s">
+        <v>374</v>
+      </c>
+      <c r="K238" t="s">
+        <v>23</v>
+      </c>
+      <c r="L238" t="s">
+        <v>1354</v>
+      </c>
+      <c r="M238" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C239" t="s">
+        <v>15</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E239" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F239" t="s">
+        <v>18</v>
+      </c>
+      <c r="G239" t="s">
+        <v>19</v>
+      </c>
+      <c r="H239" t="s">
+        <v>73</v>
+      </c>
+      <c r="I239" t="s">
+        <v>21</v>
+      </c>
+      <c r="J239" t="s">
+        <v>684</v>
+      </c>
+      <c r="K239" t="s">
+        <v>23</v>
+      </c>
+      <c r="L239" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M239" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C240" t="s">
+        <v>643</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E240" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F240" t="s">
+        <v>18</v>
+      </c>
+      <c r="G240" t="s">
+        <v>19</v>
+      </c>
+      <c r="H240" t="s">
+        <v>20</v>
+      </c>
+      <c r="I240" t="s">
+        <v>21</v>
+      </c>
+      <c r="J240" t="s">
+        <v>338</v>
+      </c>
+      <c r="K240" t="s">
+        <v>23</v>
+      </c>
+      <c r="L240" t="s">
+        <v>1364</v>
+      </c>
+      <c r="M240" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C241" t="s">
+        <v>28</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E241" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F241" t="s">
+        <v>18</v>
+      </c>
+      <c r="G241" t="s">
+        <v>19</v>
+      </c>
+      <c r="H241" t="s">
+        <v>52</v>
+      </c>
+      <c r="I241" t="s">
+        <v>21</v>
+      </c>
+      <c r="J241" t="s">
+        <v>1369</v>
+      </c>
+      <c r="K241" t="s">
+        <v>23</v>
+      </c>
+      <c r="L241" t="s">
+        <v>1370</v>
+      </c>
+      <c r="M241" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C242" t="s">
+        <v>121</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E242" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F242" t="s">
+        <v>18</v>
+      </c>
+      <c r="G242" t="s">
+        <v>19</v>
+      </c>
+      <c r="H242" t="s">
+        <v>38</v>
+      </c>
+      <c r="I242" t="s">
+        <v>21</v>
+      </c>
+      <c r="J242" t="s">
+        <v>46</v>
+      </c>
+      <c r="K242" t="s">
+        <v>23</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1375</v>
+      </c>
+      <c r="M242" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C243" t="s">
+        <v>28</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E243" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F243" t="s">
+        <v>18</v>
+      </c>
+      <c r="G243" t="s">
+        <v>19</v>
+      </c>
+      <c r="H243" t="s">
+        <v>38</v>
+      </c>
+      <c r="I243" t="s">
+        <v>21</v>
+      </c>
+      <c r="J243" t="s">
+        <v>46</v>
+      </c>
+      <c r="K243" t="s">
+        <v>23</v>
+      </c>
+      <c r="L243" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M243" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C244" t="s">
+        <v>28</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E244" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F244" t="s">
+        <v>18</v>
+      </c>
+      <c r="G244" t="s">
+        <v>19</v>
+      </c>
+      <c r="H244" t="s">
+        <v>38</v>
+      </c>
+      <c r="I244" t="s">
+        <v>21</v>
+      </c>
+      <c r="J244" t="s">
+        <v>344</v>
+      </c>
+      <c r="K244" t="s">
+        <v>23</v>
+      </c>
+      <c r="L244" t="s">
+        <v>1385</v>
+      </c>
+      <c r="M244" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C245" t="s">
+        <v>28</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E245" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F245" t="s">
+        <v>18</v>
+      </c>
+      <c r="G245" t="s">
+        <v>19</v>
+      </c>
+      <c r="H245" t="s">
+        <v>139</v>
+      </c>
+      <c r="I245" t="s">
+        <v>21</v>
+      </c>
+      <c r="J245" t="s">
+        <v>1288</v>
+      </c>
+      <c r="K245" t="s">
+        <v>23</v>
+      </c>
+      <c r="L245" t="s">
+        <v>1390</v>
+      </c>
+      <c r="M245" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C246" t="s">
+        <v>28</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E246" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F246" t="s">
+        <v>18</v>
+      </c>
+      <c r="G246" t="s">
+        <v>19</v>
+      </c>
+      <c r="H246" t="s">
+        <v>38</v>
+      </c>
+      <c r="I246" t="s">
+        <v>21</v>
+      </c>
+      <c r="J246" t="s">
+        <v>1395</v>
+      </c>
+      <c r="K246" t="s">
+        <v>23</v>
+      </c>
+      <c r="L246" t="s">
+        <v>1396</v>
+      </c>
+      <c r="M246" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C247" t="s">
+        <v>28</v>
+      </c>
+      <c r="D247" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E247" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F247" t="s">
+        <v>18</v>
+      </c>
+      <c r="G247" t="s">
+        <v>19</v>
+      </c>
+      <c r="H247" t="s">
+        <v>139</v>
+      </c>
+      <c r="I247" t="s">
+        <v>21</v>
+      </c>
+      <c r="J247" t="s">
+        <v>344</v>
+      </c>
+      <c r="K247" t="s">
+        <v>23</v>
+      </c>
+      <c r="L247" t="s">
+        <v>1402</v>
+      </c>
+      <c r="M247" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C248" t="s">
+        <v>28</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E248" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F248" t="s">
+        <v>18</v>
+      </c>
+      <c r="G248" t="s">
+        <v>19</v>
+      </c>
+      <c r="H248" t="s">
+        <v>38</v>
+      </c>
+      <c r="I248" t="s">
+        <v>21</v>
+      </c>
+      <c r="J248" t="s">
+        <v>485</v>
+      </c>
+      <c r="K248" t="s">
+        <v>23</v>
+      </c>
+      <c r="L248" t="s">
+        <v>1407</v>
+      </c>
+      <c r="M248" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C249" t="s">
+        <v>28</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E249" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F249" t="s">
+        <v>18</v>
+      </c>
+      <c r="G249" t="s">
+        <v>19</v>
+      </c>
+      <c r="H249" t="s">
+        <v>73</v>
+      </c>
+      <c r="I249" t="s">
+        <v>21</v>
+      </c>
+      <c r="J249" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K249" t="s">
+        <v>23</v>
+      </c>
+      <c r="L249" t="s">
+        <v>1413</v>
+      </c>
+      <c r="M249" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C250" t="s">
+        <v>803</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E250" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F250" t="s">
+        <v>18</v>
+      </c>
+      <c r="G250" t="s">
+        <v>19</v>
+      </c>
+      <c r="H250" t="s">
+        <v>38</v>
+      </c>
+      <c r="I250" t="s">
+        <v>21</v>
+      </c>
+      <c r="J250" t="s">
+        <v>294</v>
+      </c>
+      <c r="K250" t="s">
+        <v>23</v>
+      </c>
+      <c r="L250" t="s">
+        <v>1418</v>
+      </c>
+      <c r="M250" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C251" t="s">
+        <v>15</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E251" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F251" t="s">
+        <v>18</v>
+      </c>
+      <c r="G251" t="s">
+        <v>19</v>
+      </c>
+      <c r="H251" t="s">
+        <v>46</v>
+      </c>
+      <c r="I251" t="s">
+        <v>98</v>
+      </c>
+      <c r="J251" t="s">
+        <v>897</v>
+      </c>
+      <c r="K251" t="s">
+        <v>23</v>
+      </c>
+      <c r="L251" t="s">
+        <v>1424</v>
+      </c>
+      <c r="M251" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C252" t="s">
+        <v>28</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E252" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F252" t="s">
+        <v>18</v>
+      </c>
+      <c r="G252" t="s">
+        <v>19</v>
+      </c>
+      <c r="H252" t="s">
+        <v>157</v>
+      </c>
+      <c r="I252" t="s">
+        <v>21</v>
+      </c>
+      <c r="J252" t="s">
+        <v>46</v>
+      </c>
+      <c r="K252" t="s">
+        <v>23</v>
+      </c>
+      <c r="L252" t="s">
+        <v>1429</v>
+      </c>
+      <c r="M252" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C253" t="s">
+        <v>803</v>
+      </c>
+      <c r="D253" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E253" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F253" t="s">
+        <v>18</v>
+      </c>
+      <c r="G253" t="s">
+        <v>19</v>
+      </c>
+      <c r="H253" t="s">
+        <v>46</v>
+      </c>
+      <c r="I253" t="s">
+        <v>98</v>
+      </c>
+      <c r="J253" t="s">
+        <v>294</v>
+      </c>
+      <c r="K253" t="s">
+        <v>23</v>
+      </c>
+      <c r="L253" t="s">
+        <v>1434</v>
+      </c>
+      <c r="M253" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C254" t="s">
+        <v>28</v>
+      </c>
+      <c r="D254" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E254" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F254" t="s">
+        <v>18</v>
+      </c>
+      <c r="G254" t="s">
+        <v>19</v>
+      </c>
+      <c r="H254" t="s">
+        <v>38</v>
+      </c>
+      <c r="I254" t="s">
+        <v>21</v>
+      </c>
+      <c r="J254" t="s">
+        <v>46</v>
+      </c>
+      <c r="K254" t="s">
+        <v>23</v>
+      </c>
+      <c r="L254" t="s">
+        <v>1439</v>
+      </c>
+      <c r="M254" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C255" t="s">
+        <v>803</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E255" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F255" t="s">
+        <v>18</v>
+      </c>
+      <c r="G255" t="s">
+        <v>19</v>
+      </c>
+      <c r="H255" t="s">
+        <v>46</v>
+      </c>
+      <c r="I255" t="s">
+        <v>98</v>
+      </c>
+      <c r="J255" t="s">
+        <v>46</v>
+      </c>
+      <c r="K255" t="s">
+        <v>23</v>
+      </c>
+      <c r="L255" t="s">
+        <v>1444</v>
+      </c>
+      <c r="M255" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C256" t="s">
+        <v>28</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F256" t="s">
+        <v>18</v>
+      </c>
+      <c r="G256" t="s">
+        <v>19</v>
+      </c>
+      <c r="H256" t="s">
+        <v>46</v>
+      </c>
+      <c r="I256" t="s">
+        <v>98</v>
+      </c>
+      <c r="J256" t="s">
+        <v>46</v>
+      </c>
+      <c r="K256" t="s">
+        <v>23</v>
+      </c>
+      <c r="L256" t="s">
+        <v>1449</v>
+      </c>
+      <c r="M256" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E257" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F257" t="s">
+        <v>18</v>
+      </c>
+      <c r="G257" t="s">
+        <v>19</v>
+      </c>
+      <c r="H257" t="s">
+        <v>811</v>
+      </c>
+      <c r="I257" t="s">
+        <v>21</v>
+      </c>
+      <c r="J257" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K257" t="s">
+        <v>23</v>
+      </c>
+      <c r="L257" t="s">
+        <v>1456</v>
+      </c>
+      <c r="M257" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C258" t="s">
+        <v>28</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E258" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F258" t="s">
+        <v>18</v>
+      </c>
+      <c r="G258" t="s">
+        <v>19</v>
+      </c>
+      <c r="H258" t="s">
+        <v>46</v>
+      </c>
+      <c r="I258" t="s">
+        <v>98</v>
+      </c>
+      <c r="J258" t="s">
+        <v>46</v>
+      </c>
+      <c r="K258" t="s">
+        <v>23</v>
+      </c>
+      <c r="L258" t="s">
+        <v>1461</v>
+      </c>
+      <c r="M258" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C259" t="s">
+        <v>79</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E259" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F259" t="s">
+        <v>18</v>
+      </c>
+      <c r="G259" t="s">
+        <v>19</v>
+      </c>
+      <c r="H259" t="s">
+        <v>46</v>
+      </c>
+      <c r="I259" t="s">
+        <v>98</v>
+      </c>
+      <c r="J259" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K259" t="s">
+        <v>23</v>
+      </c>
+      <c r="L259" t="s">
+        <v>1467</v>
+      </c>
+      <c r="M259" t="s">
+        <v>1468</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
